--- a/游戏设计王/老虎机数学专题-二项分配机率.xlsx
+++ b/游戏设计王/老虎机数学专题-二项分配机率.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760" activeTab="2"/>
+    <workbookView windowHeight="16760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="说明" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="191">
   <si>
     <t>二项分配机率（Binomial Distribution）计算模型</t>
   </si>
@@ -346,12 +346,18 @@
     <t>图案</t>
   </si>
   <si>
+    <t>Table 1</t>
+  </si>
+  <si>
     <t>机率</t>
   </si>
   <si>
     <t>个数k</t>
   </si>
   <si>
+    <t>Table 2</t>
+  </si>
+  <si>
     <t>合计</t>
   </si>
   <si>
@@ -359,12 +365,6 @@
   </si>
   <si>
     <t>问2：各等级奖励机率（BINOM.DIST.RANGE）</t>
-  </si>
-  <si>
-    <t>Table 1</t>
-  </si>
-  <si>
-    <t>Table 2</t>
   </si>
   <si>
     <t>Table 3</t>
@@ -608,11 +608,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -843,7 +844,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -865,6 +866,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1073,12 +1080,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1203,7 +1262,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1215,119 +1274,119 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1378,9 +1437,23 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1391,21 +1464,52 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2050,1383 +2154,1383 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A3" s="35"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
     </row>
     <row r="5" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A5" s="35"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="51" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
     </row>
     <row r="10" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A10" s="35"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A13" s="35"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
+      <c r="A13" s="52"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A15" s="35"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
+      <c r="A15" s="52"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:10">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="55"/>
     </row>
     <row r="18" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A18" s="39"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
+      <c r="A18" s="56"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="55"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
     </row>
     <row r="22" ht="33" customHeight="1" spans="1:10">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
     </row>
     <row r="24" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A24" s="39"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
+      <c r="A24" s="56"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="55"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="55"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="55"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:10">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="38"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="64"/>
+      <c r="J31" s="55"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="38"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="38"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A34" s="46" t="s">
+      <c r="A34" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="64" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
     </row>
     <row r="35" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A35" s="39"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
+      <c r="A35" s="56"/>
+      <c r="B35" s="55"/>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
     </row>
     <row r="37" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A37" s="39"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
+      <c r="A37" s="56"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:10">
-      <c r="A39" s="44" t="s">
+      <c r="A39" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="45" t="s">
+      <c r="C39" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A40" s="46" t="s">
+      <c r="A40" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="48">
+      <c r="B40" s="65">
         <v>0.1</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="65">
         <v>0.15</v>
       </c>
-      <c r="D40" s="48">
+      <c r="D40" s="65">
         <v>0.2</v>
       </c>
-      <c r="E40" s="48">
+      <c r="E40" s="65">
         <v>0.25</v>
       </c>
-      <c r="F40" s="48">
+      <c r="F40" s="65">
         <v>0.3</v>
       </c>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
-      <c r="J40" s="38"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
     </row>
     <row r="41" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A41" s="39"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
+      <c r="A41" s="56"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
-      <c r="J42" s="38"/>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A43" s="42" t="s">
+      <c r="A43" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
     </row>
     <row r="44" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A44" s="39"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
+      <c r="A44" s="56"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="55"/>
     </row>
     <row r="45" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="55"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
+      <c r="B46" s="55"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="55"/>
     </row>
     <row r="48" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="66"/>
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A49" s="42" t="s">
+      <c r="A49" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="55"/>
     </row>
     <row r="50" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A50" s="39"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
+      <c r="A50" s="56"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="55"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="55"/>
+      <c r="J50" s="55"/>
     </row>
     <row r="51" ht="33" customHeight="1" spans="1:10">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="41"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="38"/>
-      <c r="J51" s="38"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="55"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="38"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="55"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="55"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="55"/>
+      <c r="J54" s="55"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
+      <c r="B55" s="55"/>
+      <c r="C55" s="55"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="55"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="55"/>
+      <c r="J55" s="55"/>
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A56" s="42" t="s">
+      <c r="A56" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="38"/>
-      <c r="C56" s="38"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="55"/>
+      <c r="E56" s="55"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="55"/>
+      <c r="J56" s="55"/>
     </row>
     <row r="57" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A57" s="39"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="38"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
+      <c r="A57" s="56"/>
+      <c r="B57" s="55"/>
+      <c r="C57" s="55"/>
+      <c r="D57" s="55"/>
+      <c r="E57" s="55"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="55"/>
     </row>
     <row r="58" ht="33" customHeight="1" spans="1:10">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-      <c r="J58" s="38"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
+      <c r="J58" s="55"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A59" s="43" t="s">
+      <c r="A59" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
+      <c r="B59" s="55"/>
+      <c r="C59" s="55"/>
+      <c r="D59" s="55"/>
+      <c r="E59" s="55"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="55"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="55"/>
+      <c r="J59" s="55"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="41"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="55"/>
+      <c r="E60" s="55"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="55"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A61" s="43" t="s">
+      <c r="A61" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="38"/>
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="55"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="55"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="55"/>
+      <c r="J61" s="55"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A62" s="43" t="s">
+      <c r="A62" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="B62" s="38"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
+      <c r="B62" s="55"/>
+      <c r="C62" s="55"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="55"/>
+      <c r="F62" s="55"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="55"/>
+      <c r="I62" s="55"/>
+      <c r="J62" s="55"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
+      <c r="B63" s="55"/>
+      <c r="C63" s="55"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="55"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="55"/>
+      <c r="J63" s="55"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A64" s="43" t="s">
+      <c r="A64" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
+      <c r="B64" s="55"/>
+      <c r="C64" s="55"/>
+      <c r="D64" s="55"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="55"/>
+      <c r="H64" s="55"/>
+      <c r="I64" s="55"/>
+      <c r="J64" s="55"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A65" s="43" t="s">
+      <c r="A65" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
+      <c r="B65" s="55"/>
+      <c r="C65" s="55"/>
+      <c r="D65" s="55"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="55"/>
+      <c r="G65" s="55"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="55"/>
+      <c r="J65" s="55"/>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:22">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="67" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A67" s="43" t="s">
+      <c r="A67" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="B67" s="38"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
+      <c r="B67" s="55"/>
+      <c r="C67" s="55"/>
+      <c r="D67" s="55"/>
+      <c r="E67" s="55"/>
+      <c r="F67" s="55"/>
+      <c r="G67" s="55"/>
+      <c r="H67" s="55"/>
+      <c r="I67" s="55"/>
+      <c r="J67" s="55"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A68" s="43" t="s">
+      <c r="A68" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
+      <c r="B68" s="55"/>
+      <c r="C68" s="55"/>
+      <c r="D68" s="55"/>
+      <c r="E68" s="55"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="55"/>
+      <c r="H68" s="55"/>
+      <c r="I68" s="55"/>
+      <c r="J68" s="55"/>
     </row>
     <row r="69" ht="33" customHeight="1" spans="1:22">
-      <c r="A69" s="41" t="s">
+      <c r="A69" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
+      <c r="B69" s="58"/>
+      <c r="C69" s="58"/>
+      <c r="D69" s="58"/>
+      <c r="E69" s="58"/>
+      <c r="F69" s="58"/>
+      <c r="G69" s="55"/>
+      <c r="H69" s="55"/>
+      <c r="I69" s="55"/>
+      <c r="J69" s="55"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A70" s="43" t="s">
+      <c r="A70" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="38"/>
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
+      <c r="B70" s="55"/>
+      <c r="C70" s="55"/>
+      <c r="D70" s="55"/>
+      <c r="E70" s="55"/>
+      <c r="F70" s="55"/>
+      <c r="G70" s="55"/>
+      <c r="H70" s="55"/>
+      <c r="I70" s="55"/>
+      <c r="J70" s="55"/>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:22">
-      <c r="A71" s="51" t="s">
+      <c r="A71" s="68" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A72" s="42" t="s">
+      <c r="A72" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="38"/>
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="38"/>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="55"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="55"/>
     </row>
     <row r="73" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A73" s="39"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
+      <c r="A73" s="56"/>
+      <c r="B73" s="55"/>
+      <c r="C73" s="55"/>
+      <c r="D73" s="55"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="55"/>
+      <c r="G73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
+      <c r="J73" s="55"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A74" s="43" t="s">
+      <c r="A74" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="38"/>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
+      <c r="B74" s="55"/>
+      <c r="C74" s="55"/>
+      <c r="D74" s="55"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="55"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="55"/>
+      <c r="I74" s="55"/>
+      <c r="J74" s="55"/>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:22">
-      <c r="A75" s="44" t="s">
+      <c r="A75" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="45" t="s">
+      <c r="B75" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
+      <c r="C75" s="55"/>
+      <c r="D75" s="55"/>
+      <c r="E75" s="55"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="55"/>
+      <c r="J75" s="55"/>
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:22">
-      <c r="A76" s="46" t="s">
+      <c r="A76" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="B76" s="47" t="s">
+      <c r="B76" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="C76" s="47"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
+      <c r="C76" s="64"/>
+      <c r="D76" s="55"/>
+      <c r="E76" s="55"/>
+      <c r="F76" s="55"/>
+      <c r="G76" s="55"/>
+      <c r="H76" s="55"/>
+      <c r="I76" s="55"/>
+      <c r="J76" s="55"/>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:22">
-      <c r="A77" s="46" t="s">
+      <c r="A77" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="52" t="s">
+      <c r="B77" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="52"/>
-      <c r="H77" s="52"/>
-      <c r="I77" s="52"/>
-      <c r="J77" s="52"/>
-      <c r="K77" s="52"/>
-      <c r="L77" s="52"/>
-      <c r="M77" s="52"/>
-      <c r="N77" s="52"/>
-      <c r="O77" s="52"/>
-      <c r="P77" s="52"/>
-      <c r="Q77" s="52"/>
-      <c r="R77" s="52"/>
-      <c r="S77" s="52"/>
-      <c r="T77" s="52"/>
-      <c r="U77" s="52"/>
-      <c r="V77" s="52"/>
+      <c r="C77" s="69"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="69"/>
+      <c r="F77" s="69"/>
+      <c r="G77" s="69"/>
+      <c r="H77" s="69"/>
+      <c r="I77" s="69"/>
+      <c r="J77" s="69"/>
+      <c r="K77" s="69"/>
+      <c r="L77" s="69"/>
+      <c r="M77" s="69"/>
+      <c r="N77" s="69"/>
+      <c r="O77" s="69"/>
+      <c r="P77" s="69"/>
+      <c r="Q77" s="69"/>
+      <c r="R77" s="69"/>
+      <c r="S77" s="69"/>
+      <c r="T77" s="69"/>
+      <c r="U77" s="69"/>
+      <c r="V77" s="69"/>
     </row>
     <row r="78" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A78" s="39"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="38"/>
-      <c r="J78" s="38"/>
+      <c r="A78" s="56"/>
+      <c r="B78" s="55"/>
+      <c r="C78" s="55"/>
+      <c r="D78" s="55"/>
+      <c r="E78" s="55"/>
+      <c r="F78" s="55"/>
+      <c r="G78" s="55"/>
+      <c r="H78" s="55"/>
+      <c r="I78" s="55"/>
+      <c r="J78" s="55"/>
     </row>
     <row r="79" ht="33" customHeight="1" spans="1:22">
-      <c r="A79" s="41" t="s">
+      <c r="A79" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="41"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
+      <c r="B79" s="58"/>
+      <c r="C79" s="58"/>
+      <c r="D79" s="58"/>
+      <c r="E79" s="58"/>
+      <c r="F79" s="55"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="55"/>
+      <c r="I79" s="55"/>
+      <c r="J79" s="55"/>
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A80" s="42" t="s">
+      <c r="A80" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
-      <c r="J80" s="38"/>
+      <c r="B80" s="55"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="55"/>
+      <c r="E80" s="55"/>
+      <c r="F80" s="55"/>
+      <c r="G80" s="55"/>
+      <c r="H80" s="55"/>
+      <c r="I80" s="55"/>
+      <c r="J80" s="55"/>
     </row>
     <row r="81" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A81" s="39"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="38"/>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
+      <c r="A81" s="56"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="55"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="55"/>
+      <c r="F81" s="55"/>
+      <c r="G81" s="55"/>
+      <c r="H81" s="55"/>
+      <c r="I81" s="55"/>
+      <c r="J81" s="55"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A82" s="43" t="s">
+      <c r="A82" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="38"/>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
+      <c r="B82" s="55"/>
+      <c r="C82" s="55"/>
+      <c r="D82" s="55"/>
+      <c r="E82" s="55"/>
+      <c r="F82" s="55"/>
+      <c r="G82" s="55"/>
+      <c r="H82" s="55"/>
+      <c r="I82" s="55"/>
+      <c r="J82" s="55"/>
     </row>
     <row r="83" ht="33" customHeight="1" spans="1:10">
-      <c r="A83" s="41" t="s">
+      <c r="A83" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="B83" s="41"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="38"/>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
+      <c r="B83" s="58"/>
+      <c r="C83" s="58"/>
+      <c r="D83" s="58"/>
+      <c r="E83" s="55"/>
+      <c r="F83" s="55"/>
+      <c r="G83" s="55"/>
+      <c r="H83" s="55"/>
+      <c r="I83" s="55"/>
+      <c r="J83" s="55"/>
     </row>
     <row r="84" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A84" s="41" t="s">
+      <c r="A84" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="B84" s="41"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="41"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="41"/>
-      <c r="I84" s="41"/>
-      <c r="J84" s="38"/>
+      <c r="B84" s="58"/>
+      <c r="C84" s="58"/>
+      <c r="D84" s="58"/>
+      <c r="E84" s="58"/>
+      <c r="F84" s="58"/>
+      <c r="G84" s="58"/>
+      <c r="H84" s="58"/>
+      <c r="I84" s="58"/>
+      <c r="J84" s="55"/>
     </row>
     <row r="85" ht="33" customHeight="1" spans="1:10">
-      <c r="A85" s="41" t="s">
+      <c r="A85" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="B85" s="41"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
+      <c r="B85" s="58"/>
+      <c r="C85" s="58"/>
+      <c r="D85" s="58"/>
+      <c r="E85" s="58"/>
+      <c r="F85" s="58"/>
+      <c r="G85" s="58"/>
+      <c r="H85" s="55"/>
+      <c r="I85" s="55"/>
+      <c r="J85" s="55"/>
     </row>
     <row r="86" ht="33" customHeight="1" spans="1:10">
-      <c r="A86" s="41" t="s">
+      <c r="A86" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="B86" s="41"/>
-      <c r="C86" s="41"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="38"/>
-      <c r="G86" s="38"/>
-      <c r="H86" s="38"/>
-      <c r="I86" s="38"/>
-      <c r="J86" s="38"/>
+      <c r="B86" s="58"/>
+      <c r="C86" s="58"/>
+      <c r="D86" s="58"/>
+      <c r="E86" s="55"/>
+      <c r="F86" s="55"/>
+      <c r="G86" s="55"/>
+      <c r="H86" s="55"/>
+      <c r="I86" s="55"/>
+      <c r="J86" s="55"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A87" s="42" t="s">
+      <c r="A87" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="B87" s="38"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="38"/>
-      <c r="F87" s="38"/>
-      <c r="G87" s="38"/>
-      <c r="H87" s="38"/>
-      <c r="I87" s="38"/>
-      <c r="J87" s="38"/>
+      <c r="B87" s="55"/>
+      <c r="C87" s="55"/>
+      <c r="D87" s="55"/>
+      <c r="E87" s="55"/>
+      <c r="F87" s="55"/>
+      <c r="G87" s="55"/>
+      <c r="H87" s="55"/>
+      <c r="I87" s="55"/>
+      <c r="J87" s="55"/>
     </row>
     <row r="88" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A88" s="39"/>
-      <c r="B88" s="38"/>
-      <c r="C88" s="38"/>
-      <c r="D88" s="38"/>
-      <c r="E88" s="38"/>
-      <c r="F88" s="38"/>
-      <c r="G88" s="38"/>
-      <c r="H88" s="38"/>
-      <c r="I88" s="38"/>
-      <c r="J88" s="38"/>
+      <c r="A88" s="56"/>
+      <c r="B88" s="55"/>
+      <c r="C88" s="55"/>
+      <c r="D88" s="55"/>
+      <c r="E88" s="55"/>
+      <c r="F88" s="55"/>
+      <c r="G88" s="55"/>
+      <c r="H88" s="55"/>
+      <c r="I88" s="55"/>
+      <c r="J88" s="55"/>
     </row>
     <row r="89" ht="18" customHeight="1" spans="1:10">
-      <c r="A89" s="44" t="s">
+      <c r="A89" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="45" t="s">
+      <c r="B89" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="C89" s="38"/>
-      <c r="D89" s="38"/>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38"/>
-      <c r="G89" s="38"/>
-      <c r="H89" s="38"/>
-      <c r="I89" s="38"/>
-      <c r="J89" s="38"/>
+      <c r="C89" s="55"/>
+      <c r="D89" s="55"/>
+      <c r="E89" s="55"/>
+      <c r="F89" s="55"/>
+      <c r="G89" s="55"/>
+      <c r="H89" s="55"/>
+      <c r="I89" s="55"/>
+      <c r="J89" s="55"/>
     </row>
     <row r="90" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A90" s="46" t="s">
+      <c r="A90" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="53" t="s">
+      <c r="B90" s="70" t="s">
         <v>85</v>
       </c>
-      <c r="C90" s="38"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="38"/>
-      <c r="G90" s="38"/>
-      <c r="H90" s="38"/>
-      <c r="I90" s="38"/>
-      <c r="J90" s="38"/>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55"/>
+      <c r="E90" s="55"/>
+      <c r="F90" s="55"/>
+      <c r="G90" s="55"/>
+      <c r="H90" s="55"/>
+      <c r="I90" s="55"/>
+      <c r="J90" s="55"/>
     </row>
     <row r="91" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A91" s="46" t="s">
+      <c r="A91" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="B91" s="47" t="s">
+      <c r="B91" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="C91" s="47"/>
-      <c r="D91" s="38"/>
-      <c r="E91" s="38"/>
-      <c r="F91" s="38"/>
-      <c r="G91" s="38"/>
-      <c r="H91" s="38"/>
-      <c r="I91" s="38"/>
-      <c r="J91" s="38"/>
+      <c r="C91" s="64"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="55"/>
+      <c r="F91" s="55"/>
+      <c r="G91" s="55"/>
+      <c r="H91" s="55"/>
+      <c r="I91" s="55"/>
+      <c r="J91" s="55"/>
     </row>
     <row r="92" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A92" s="46" t="s">
+      <c r="A92" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="47" t="s">
+      <c r="B92" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="47"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="38"/>
-      <c r="G92" s="38"/>
-      <c r="H92" s="38"/>
-      <c r="I92" s="38"/>
-      <c r="J92" s="38"/>
+      <c r="C92" s="64"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55"/>
+      <c r="J92" s="55"/>
     </row>
     <row r="93" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A93" s="46" t="s">
+      <c r="A93" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="B93" s="47" t="s">
+      <c r="B93" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="47"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
-      <c r="G93" s="38"/>
-      <c r="H93" s="38"/>
-      <c r="I93" s="38"/>
-      <c r="J93" s="38"/>
+      <c r="C93" s="64"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55"/>
+      <c r="J93" s="55"/>
     </row>
     <row r="94" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A94" s="46" t="s">
+      <c r="A94" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="47" t="s">
+      <c r="B94" s="64" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="47"/>
-      <c r="D94" s="38"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="38"/>
-      <c r="G94" s="38"/>
-      <c r="H94" s="38"/>
-      <c r="I94" s="38"/>
-      <c r="J94" s="38"/>
+      <c r="C94" s="64"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55"/>
+      <c r="J94" s="55"/>
     </row>
     <row r="95" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A95" s="46" t="s">
+      <c r="A95" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="47" t="s">
+      <c r="B95" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="47"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="38"/>
-      <c r="F95" s="38"/>
-      <c r="G95" s="38"/>
-      <c r="H95" s="38"/>
-      <c r="I95" s="38"/>
-      <c r="J95" s="38"/>
+      <c r="C95" s="64"/>
+      <c r="D95" s="55"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55"/>
+      <c r="J95" s="55"/>
     </row>
     <row r="96" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A96" s="46" t="s">
+      <c r="A96" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="47" t="s">
+      <c r="B96" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="47"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="38"/>
-      <c r="F96" s="38"/>
-      <c r="G96" s="38"/>
-      <c r="H96" s="38"/>
-      <c r="I96" s="38"/>
-      <c r="J96" s="38"/>
+      <c r="C96" s="64"/>
+      <c r="D96" s="55"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55"/>
+      <c r="J96" s="55"/>
     </row>
     <row r="97" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A97" s="46" t="s">
+      <c r="A97" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="B97" s="47" t="s">
+      <c r="B97" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="C97" s="47"/>
-      <c r="D97" s="38"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38"/>
-      <c r="G97" s="38"/>
-      <c r="H97" s="38"/>
-      <c r="I97" s="38"/>
-      <c r="J97" s="38"/>
+      <c r="C97" s="64"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55"/>
+      <c r="J97" s="55"/>
     </row>
     <row r="98" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A98" s="46" t="s">
+      <c r="A98" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="47" t="s">
+      <c r="B98" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C98" s="47"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="38"/>
-      <c r="H98" s="38"/>
-      <c r="I98" s="38"/>
-      <c r="J98" s="38"/>
+      <c r="C98" s="64"/>
+      <c r="D98" s="55"/>
+      <c r="E98" s="55"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55"/>
+      <c r="J98" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -3465,7 +3569,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:V98" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:V1 B2:V2 A3:V98" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3480,9 +3584,9 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="28.2857142857143" customWidth="1"/>
     <col min="3" max="3" width="17.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="15.8571428571429" customWidth="1"/>
-    <col min="6" max="6" width="14.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="19.7857142857143" customWidth="1"/>
+    <col min="5" max="5" width="18.5982142857143" customWidth="1"/>
+    <col min="6" max="6" width="21.5714285714286" customWidth="1"/>
     <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="21.4285714285714" customWidth="1"/>
@@ -3608,7 +3712,9 @@
       <c r="F4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="16"/>
+      <c r="G4" s="18" t="s">
+        <v>105</v>
+      </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
       <c r="J4" s="16"/>
@@ -3629,25 +3735,25 @@
       <c r="Y4" s="16"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A5" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="18">
+      <c r="A5" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="20">
         <v>0.1</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="20">
         <v>0.15</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>0.2</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="20">
         <v>0.25</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="20">
         <v>0.3</v>
       </c>
-      <c r="G5" s="16"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -3668,15 +3774,17 @@
       <c r="Y5" s="16"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A6" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="16"/>
+      <c r="A6" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24" t="s">
+        <v>108</v>
+      </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
       <c r="J6" s="16"/>
@@ -3697,30 +3805,30 @@
       <c r="Y6" s="16"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A7" s="16">
+      <c r="A7" s="21">
         <v>0</v>
       </c>
-      <c r="B7" s="20">
-        <f t="shared" ref="B7:B22" si="0">BINOMDIST($A7,15,B$5,FALSE())</f>
+      <c r="B7" s="25">
+        <f>BINOMDIST($A7,15,B$5,FALSE())</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="C7" s="20">
-        <f t="shared" ref="C7:C22" si="1">BINOMDIST($A7,15,C$5,FALSE())</f>
+      <c r="C7" s="25">
+        <f t="shared" ref="C7:C22" si="0">BINOMDIST($A7,15,C$5,FALSE())</f>
         <v>0.0873542191012517</v>
       </c>
-      <c r="D7" s="20">
-        <f t="shared" ref="D7:D22" si="2">BINOMDIST($A7,15,D$5,FALSE())</f>
+      <c r="D7" s="25">
+        <f t="shared" ref="D7:D22" si="1">BINOMDIST($A7,15,D$5,FALSE())</f>
         <v>0.035184372088832</v>
       </c>
-      <c r="E7" s="20">
-        <f t="shared" ref="E7:E22" si="3">BINOMDIST($A7,15,E$5,FALSE())</f>
+      <c r="E7" s="25">
+        <f t="shared" ref="E7:E22" si="2">BINOMDIST($A7,15,E$5,FALSE())</f>
         <v>0.0133634610101581</v>
       </c>
-      <c r="F7" s="20">
-        <f t="shared" ref="F7:F22" si="4">BINOMDIST($A7,15,F$5,FALSE())</f>
+      <c r="F7" s="25">
+        <f t="shared" ref="F7:F22" si="3">BINOMDIST($A7,15,F$5,FALSE())</f>
         <v>0.00474756150994299</v>
       </c>
-      <c r="G7" s="16"/>
+      <c r="G7" s="24"/>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
@@ -3741,30 +3849,30 @@
       <c r="Y7" s="16"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A8" s="16">
+      <c r="A8" s="21">
         <v>1</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="25">
+        <f t="shared" ref="B7:B22" si="4">BINOMDIST($A8,15,B$5,FALSE())</f>
+        <v>0.343151886824415</v>
+      </c>
+      <c r="C8" s="25">
         <f t="shared" si="0"/>
-        <v>0.343151886824415</v>
-      </c>
-      <c r="C8" s="20">
+        <v>0.23123175644449</v>
+      </c>
+      <c r="D8" s="25">
         <f t="shared" si="1"/>
-        <v>0.23123175644449</v>
-      </c>
-      <c r="D8" s="20">
+        <v>0.13194139533312</v>
+      </c>
+      <c r="E8" s="25">
         <f t="shared" si="2"/>
-        <v>0.13194139533312</v>
-      </c>
-      <c r="E8" s="20">
+        <v>0.0668173050507903</v>
+      </c>
+      <c r="F8" s="25">
         <f t="shared" si="3"/>
-        <v>0.0668173050507903</v>
-      </c>
-      <c r="F8" s="20">
-        <f t="shared" si="4"/>
         <v>0.030520038278205</v>
       </c>
-      <c r="G8" s="16"/>
+      <c r="G8" s="24"/>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
@@ -3785,30 +3893,30 @@
       <c r="Y8" s="16"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A9" s="16">
+      <c r="A9" s="21">
         <v>2</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="25">
+        <f t="shared" si="4"/>
+        <v>0.266895911974545</v>
+      </c>
+      <c r="C9" s="25">
         <f t="shared" si="0"/>
-        <v>0.266895911974545</v>
-      </c>
-      <c r="C9" s="20">
+        <v>0.285639228549076</v>
+      </c>
+      <c r="D9" s="25">
         <f t="shared" si="1"/>
-        <v>0.285639228549076</v>
-      </c>
-      <c r="D9" s="20">
+        <v>0.23089744183296</v>
+      </c>
+      <c r="E9" s="25">
         <f t="shared" si="2"/>
-        <v>0.23089744183296</v>
-      </c>
-      <c r="E9" s="20">
+        <v>0.155907045118511</v>
+      </c>
+      <c r="F9" s="25">
         <f t="shared" si="3"/>
-        <v>0.155907045118511</v>
-      </c>
-      <c r="F9" s="20">
-        <f t="shared" si="4"/>
         <v>0.0915601148346149</v>
       </c>
-      <c r="G9" s="16"/>
+      <c r="G9" s="24"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
@@ -3829,30 +3937,30 @@
       <c r="Y9" s="16"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A10" s="16">
+      <c r="A10" s="21">
         <v>3</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="25">
+        <f t="shared" si="4"/>
+        <v>0.128505439098855</v>
+      </c>
+      <c r="C10" s="25">
         <f t="shared" si="0"/>
-        <v>0.128505439098855</v>
-      </c>
-      <c r="C10" s="20">
+        <v>0.218429998302234</v>
+      </c>
+      <c r="D10" s="25">
         <f t="shared" si="1"/>
-        <v>0.218429998302234</v>
-      </c>
-      <c r="D10" s="20">
+        <v>0.25013889531904</v>
+      </c>
+      <c r="E10" s="25">
         <f t="shared" si="2"/>
-        <v>0.25013889531904</v>
-      </c>
-      <c r="E10" s="20">
+        <v>0.225199065171182</v>
+      </c>
+      <c r="F10" s="25">
         <f t="shared" si="3"/>
-        <v>0.225199065171182</v>
-      </c>
-      <c r="F10" s="20">
-        <f t="shared" si="4"/>
         <v>0.170040213264285</v>
       </c>
-      <c r="G10" s="16"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
@@ -3873,30 +3981,30 @@
       <c r="Y10" s="16"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A11" s="16">
+      <c r="A11" s="21">
         <v>4</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="25">
+        <f t="shared" si="4"/>
+        <v>0.0428351463662851</v>
+      </c>
+      <c r="C11" s="25">
         <f t="shared" si="0"/>
-        <v>0.0428351463662851</v>
-      </c>
-      <c r="C11" s="20">
+        <v>0.115639410865889</v>
+      </c>
+      <c r="D11" s="25">
         <f t="shared" si="1"/>
-        <v>0.115639410865889</v>
-      </c>
-      <c r="D11" s="20">
+        <v>0.18760417148928</v>
+      </c>
+      <c r="E11" s="25">
         <f t="shared" si="2"/>
-        <v>0.18760417148928</v>
-      </c>
-      <c r="E11" s="20">
+        <v>0.225199065171182</v>
+      </c>
+      <c r="F11" s="25">
         <f t="shared" si="3"/>
-        <v>0.225199065171182</v>
-      </c>
-      <c r="F11" s="20">
-        <f t="shared" si="4"/>
         <v>0.218623131339795</v>
       </c>
-      <c r="G11" s="16"/>
+      <c r="G11" s="24"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
@@ -3917,30 +4025,30 @@
       <c r="Y11" s="16"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A12" s="16">
+      <c r="A12" s="21">
         <v>5</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="25">
+        <f t="shared" si="4"/>
+        <v>0.010470813556203</v>
+      </c>
+      <c r="C12" s="25">
         <f t="shared" si="0"/>
-        <v>0.010470813556203</v>
-      </c>
-      <c r="C12" s="20">
+        <v>0.0448953006891097</v>
+      </c>
+      <c r="D12" s="25">
         <f t="shared" si="1"/>
-        <v>0.0448953006891097</v>
-      </c>
-      <c r="D12" s="20">
+        <v>0.103182294319104</v>
+      </c>
+      <c r="E12" s="25">
         <f t="shared" si="2"/>
-        <v>0.103182294319104</v>
-      </c>
-      <c r="E12" s="20">
+        <v>0.165145981125534</v>
+      </c>
+      <c r="F12" s="25">
         <f t="shared" si="3"/>
-        <v>0.165145981125534</v>
-      </c>
-      <c r="F12" s="20">
-        <f t="shared" si="4"/>
         <v>0.206130380977521</v>
       </c>
-      <c r="G12" s="16"/>
+      <c r="G12" s="24"/>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
@@ -3961,30 +4069,30 @@
       <c r="Y12" s="16"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A13" s="16">
+      <c r="A13" s="21">
         <v>6</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="25">
+        <f t="shared" si="4"/>
+        <v>0.001939039547445</v>
+      </c>
+      <c r="C13" s="25">
         <f t="shared" si="0"/>
-        <v>0.001939039547445</v>
-      </c>
-      <c r="C13" s="20">
+        <v>0.0132045002026793</v>
+      </c>
+      <c r="D13" s="25">
         <f t="shared" si="1"/>
-        <v>0.0132045002026793</v>
-      </c>
-      <c r="D13" s="20">
+        <v>0.04299262263296</v>
+      </c>
+      <c r="E13" s="25">
         <f t="shared" si="2"/>
-        <v>0.04299262263296</v>
-      </c>
-      <c r="E13" s="20">
+        <v>0.0917477672919629</v>
+      </c>
+      <c r="F13" s="25">
         <f t="shared" si="3"/>
-        <v>0.0917477672919629</v>
-      </c>
-      <c r="F13" s="20">
-        <f t="shared" si="4"/>
         <v>0.147235986412515</v>
       </c>
-      <c r="G13" s="16"/>
+      <c r="G13" s="24"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
@@ -4005,30 +4113,30 @@
       <c r="Y13" s="16"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A14" s="16">
+      <c r="A14" s="21">
         <v>7</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="25">
+        <f t="shared" si="4"/>
+        <v>0.000277005649635</v>
+      </c>
+      <c r="C14" s="25">
         <f t="shared" si="0"/>
-        <v>0.000277005649635</v>
-      </c>
-      <c r="C14" s="20">
+        <v>0.00299597903758271</v>
+      </c>
+      <c r="D14" s="25">
         <f t="shared" si="1"/>
-        <v>0.00299597903758271</v>
-      </c>
-      <c r="D14" s="20">
+        <v>0.01381905727488</v>
+      </c>
+      <c r="E14" s="25">
         <f t="shared" si="2"/>
-        <v>0.01381905727488</v>
-      </c>
-      <c r="E14" s="20">
+        <v>0.0393204716965555</v>
+      </c>
+      <c r="F14" s="25">
         <f t="shared" si="3"/>
-        <v>0.0393204716965555</v>
-      </c>
-      <c r="F14" s="20">
-        <f t="shared" si="4"/>
         <v>0.0811300333293451</v>
       </c>
-      <c r="G14" s="16"/>
+      <c r="G14" s="24"/>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
@@ -4049,30 +4157,30 @@
       <c r="Y14" s="16"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A15" s="16">
+      <c r="A15" s="21">
         <v>8</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="25">
+        <f t="shared" si="4"/>
+        <v>3.0778405515e-5</v>
+      </c>
+      <c r="C15" s="25">
         <f t="shared" si="0"/>
-        <v>3.0778405515e-5</v>
-      </c>
-      <c r="C15" s="20">
+        <v>0.00052870218310283</v>
+      </c>
+      <c r="D15" s="25">
         <f t="shared" si="1"/>
-        <v>0.00052870218310283</v>
-      </c>
-      <c r="D15" s="20">
+        <v>0.00345476431872</v>
+      </c>
+      <c r="E15" s="25">
         <f t="shared" si="2"/>
-        <v>0.00345476431872</v>
-      </c>
-      <c r="E15" s="20">
+        <v>0.0131068238988519</v>
+      </c>
+      <c r="F15" s="25">
         <f t="shared" si="3"/>
-        <v>0.0131068238988519</v>
-      </c>
-      <c r="F15" s="20">
-        <f t="shared" si="4"/>
         <v>0.034770014284005</v>
       </c>
-      <c r="G15" s="16"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
@@ -4093,30 +4201,30 @@
       <c r="Y15" s="16"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A16" s="16">
+      <c r="A16" s="21">
         <v>9</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="25">
+        <f t="shared" si="4"/>
+        <v>2.659862205e-6</v>
+      </c>
+      <c r="C16" s="25">
         <f t="shared" si="0"/>
-        <v>2.659862205e-6</v>
-      </c>
-      <c r="C16" s="20">
+        <v>7.25669663082317e-5</v>
+      </c>
+      <c r="D16" s="25">
         <f t="shared" si="1"/>
-        <v>7.25669663082317e-5</v>
-      </c>
-      <c r="D16" s="20">
+        <v>0.00067175972864</v>
+      </c>
+      <c r="E16" s="25">
         <f t="shared" si="2"/>
-        <v>0.00067175972864</v>
-      </c>
-      <c r="E16" s="20">
+        <v>0.00339806545525789</v>
+      </c>
+      <c r="F16" s="25">
         <f t="shared" si="3"/>
-        <v>0.00339806545525789</v>
-      </c>
-      <c r="F16" s="20">
-        <f t="shared" si="4"/>
         <v>0.011590004761335</v>
       </c>
-      <c r="G16" s="16"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
@@ -4137,30 +4245,30 @@
       <c r="Y16" s="16"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A17" s="16">
+      <c r="A17" s="21">
         <v>10</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="25">
+        <f t="shared" si="4"/>
+        <v>1.77324147e-7</v>
+      </c>
+      <c r="C17" s="25">
         <f t="shared" si="0"/>
-        <v>1.77324147e-7</v>
-      </c>
-      <c r="C17" s="20">
+        <v>7.68356113851866e-6</v>
+      </c>
+      <c r="D17" s="25">
         <f t="shared" si="1"/>
-        <v>7.68356113851866e-6</v>
-      </c>
-      <c r="D17" s="20">
+        <v>0.000100763959296</v>
+      </c>
+      <c r="E17" s="25">
         <f t="shared" si="2"/>
-        <v>0.000100763959296</v>
-      </c>
-      <c r="E17" s="20">
+        <v>0.000679613091051579</v>
+      </c>
+      <c r="F17" s="25">
         <f t="shared" si="3"/>
-        <v>0.000679613091051579</v>
-      </c>
-      <c r="F17" s="20">
-        <f t="shared" si="4"/>
         <v>0.002980286938629</v>
       </c>
-      <c r="G17" s="16"/>
+      <c r="G17" s="24"/>
       <c r="H17" s="16"/>
       <c r="I17" s="16"/>
       <c r="J17" s="16"/>
@@ -4181,30 +4289,30 @@
       <c r="Y17" s="16"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A18" s="16">
+      <c r="A18" s="21">
         <v>11</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="25">
+        <f t="shared" si="4"/>
+        <v>8.95576499999999e-9</v>
+      </c>
+      <c r="C18" s="25">
         <f t="shared" si="0"/>
-        <v>8.95576499999999e-9</v>
-      </c>
-      <c r="C18" s="20">
+        <v>6.16328433571014e-7</v>
+      </c>
+      <c r="D18" s="25">
         <f t="shared" si="1"/>
-        <v>6.16328433571014e-7</v>
-      </c>
-      <c r="D18" s="20">
+        <v>1.145044992e-5</v>
+      </c>
+      <c r="E18" s="25">
         <f t="shared" si="2"/>
-        <v>1.145044992e-5</v>
-      </c>
-      <c r="E18" s="20">
+        <v>0.000102971680462361</v>
+      </c>
+      <c r="F18" s="25">
         <f t="shared" si="3"/>
-        <v>0.000102971680462361</v>
-      </c>
-      <c r="F18" s="20">
-        <f t="shared" si="4"/>
         <v>0.000580575377655</v>
       </c>
-      <c r="G18" s="16"/>
+      <c r="G18" s="24"/>
       <c r="H18" s="16"/>
       <c r="I18" s="16"/>
       <c r="J18" s="16"/>
@@ -4225,30 +4333,30 @@
       <c r="Y18" s="16"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A19" s="16">
+      <c r="A19" s="21">
         <v>12</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="25">
+        <f t="shared" si="4"/>
+        <v>3.31695000000002e-10</v>
+      </c>
+      <c r="C19" s="25">
         <f t="shared" si="0"/>
-        <v>3.31695000000002e-10</v>
-      </c>
-      <c r="C19" s="20">
+        <v>3.62546137394715e-8</v>
+      </c>
+      <c r="D19" s="25">
         <f t="shared" si="1"/>
-        <v>3.62546137394715e-8</v>
-      </c>
-      <c r="D19" s="20">
+        <v>9.54204160000001e-7</v>
+      </c>
+      <c r="E19" s="25">
         <f t="shared" si="2"/>
-        <v>9.54204160000001e-7</v>
-      </c>
-      <c r="E19" s="20">
+        <v>1.14412978291512e-5</v>
+      </c>
+      <c r="F19" s="25">
         <f t="shared" si="3"/>
-        <v>1.14412978291512e-5</v>
-      </c>
-      <c r="F19" s="20">
-        <f t="shared" si="4"/>
         <v>8.29393396650001e-5</v>
       </c>
-      <c r="G19" s="16"/>
+      <c r="G19" s="24"/>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
@@ -4269,30 +4377,30 @@
       <c r="Y19" s="16"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A20" s="16">
+      <c r="A20" s="21">
         <v>13</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="25">
+        <f t="shared" si="4"/>
+        <v>8.50500000000002e-12</v>
+      </c>
+      <c r="C20" s="25">
         <f t="shared" si="0"/>
-        <v>8.50500000000002e-12</v>
-      </c>
-      <c r="C20" s="20">
+        <v>1.47643223373413e-9</v>
+      </c>
+      <c r="D20" s="25">
         <f t="shared" si="1"/>
-        <v>1.47643223373413e-9</v>
-      </c>
-      <c r="D20" s="20">
+        <v>5.505024e-8</v>
+      </c>
+      <c r="E20" s="25">
         <f t="shared" si="2"/>
-        <v>5.505024e-8</v>
-      </c>
-      <c r="E20" s="20">
+        <v>8.80099833011629e-7</v>
+      </c>
+      <c r="F20" s="25">
         <f t="shared" si="3"/>
-        <v>8.80099833011629e-7</v>
-      </c>
-      <c r="F20" s="20">
-        <f t="shared" si="4"/>
         <v>8.20279183500003e-6</v>
       </c>
-      <c r="G20" s="16"/>
+      <c r="G20" s="24"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
       <c r="J20" s="16"/>
@@ -4313,30 +4421,30 @@
       <c r="Y20" s="16"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A21" s="16">
+      <c r="A21" s="21">
         <v>14</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="25">
+        <f t="shared" si="4"/>
+        <v>1.35e-13</v>
+      </c>
+      <c r="C21" s="25">
         <f t="shared" si="0"/>
-        <v>1.35e-13</v>
-      </c>
-      <c r="C21" s="20">
+        <v>3.7220980682373e-11</v>
+      </c>
+      <c r="D21" s="25">
         <f t="shared" si="1"/>
-        <v>3.7220980682373e-11</v>
-      </c>
-      <c r="D21" s="20">
+        <v>1.96607999999999e-9</v>
+      </c>
+      <c r="E21" s="25">
         <f t="shared" si="2"/>
-        <v>1.96607999999999e-9</v>
-      </c>
-      <c r="E21" s="20">
+        <v>4.19095158576965e-8</v>
+      </c>
+      <c r="F21" s="25">
         <f t="shared" si="3"/>
-        <v>4.19095158576965e-8</v>
-      </c>
-      <c r="F21" s="20">
-        <f t="shared" si="4"/>
         <v>5.02211745e-7</v>
       </c>
-      <c r="G21" s="16"/>
+      <c r="G21" s="24"/>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
       <c r="J21" s="16"/>
@@ -4357,30 +4465,30 @@
       <c r="Y21" s="16"/>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A22" s="16">
+      <c r="A22" s="21">
         <v>15</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="25">
+        <f t="shared" si="4"/>
+        <v>1e-15</v>
+      </c>
+      <c r="C22" s="25">
         <f t="shared" si="0"/>
-        <v>1e-15</v>
-      </c>
-      <c r="C22" s="20">
+        <v>4.3789389038086e-13</v>
+      </c>
+      <c r="D22" s="25">
         <f t="shared" si="1"/>
-        <v>4.3789389038086e-13</v>
-      </c>
-      <c r="D22" s="20">
+        <v>3.2768e-11</v>
+      </c>
+      <c r="E22" s="25">
         <f t="shared" si="2"/>
-        <v>3.2768e-11</v>
-      </c>
-      <c r="E22" s="20">
+        <v>9.31322574615479e-10</v>
+      </c>
+      <c r="F22" s="25">
         <f t="shared" si="3"/>
-        <v>9.31322574615479e-10</v>
-      </c>
-      <c r="F22" s="20">
-        <f t="shared" si="4"/>
         <v>1.4348907e-8</v>
       </c>
-      <c r="G22" s="16"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
@@ -4401,30 +4509,30 @@
       <c r="Y22" s="16"/>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A23" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="21">
+      <c r="A23" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="27">
         <f>SUM(B7:B22)</f>
         <v>1</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="27">
         <f>SUM(C7:C22)</f>
         <v>1</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="27">
         <f>SUM(D7:D22)</f>
         <v>1</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="27">
         <f>SUM(E7:E22)</f>
         <v>1</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="27">
         <f>SUM(F7:F22)</f>
         <v>1</v>
       </c>
-      <c r="G23" s="16"/>
+      <c r="G23" s="24"/>
       <c r="H23" s="16"/>
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
@@ -4473,25 +4581,25 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:25">
       <c r="A25" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="28"/>
+      <c r="R25" s="28"/>
       <c r="S25" s="16"/>
       <c r="T25" s="16"/>
       <c r="U25" s="16"/>
@@ -4501,14 +4609,14 @@
       <c r="Y25" s="16"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A26" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
+      <c r="A26" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
-      <c r="F26" s="24"/>
+      <c r="F26" s="30"/>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
       <c r="I26" s="16"/>
@@ -4535,7 +4643,7 @@
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
-      <c r="F27" s="24"/>
+      <c r="F27" s="30"/>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
@@ -4558,29 +4666,24 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:25">
       <c r="A28" s="17"/>
-      <c r="B28" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25" t="s">
+      <c r="B28" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="32"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="34"/>
+      <c r="H28" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="N28" s="25"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="38"/>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
       <c r="U28" s="16"/>
@@ -4591,39 +4694,34 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:25">
       <c r="A29" s="16"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24" t="s">
+      <c r="B29" s="39"/>
+      <c r="C29" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="39" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="16"/>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="40" t="s">
         <v>114</v>
       </c>
       <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="24" t="s">
+      <c r="H29" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="N29" s="24" t="s">
+      <c r="I29" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="O29" s="24" t="s">
+      <c r="J29" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="P29" s="24" t="s">
+      <c r="K29" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="Q29" s="24" t="s">
+      <c r="L29" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="R29" s="24" t="s">
+      <c r="M29" s="40" t="s">
         <v>38</v>
       </c>
       <c r="S29" s="16"/>
@@ -4636,46 +4734,41 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:25">
       <c r="A30" s="16"/>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="39">
         <v>10</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="41">
         <v>0.1</v>
       </c>
       <c r="E30" s="16"/>
-      <c r="F30" s="24">
+      <c r="F30" s="40">
         <v>0</v>
       </c>
       <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="24">
+      <c r="H30" s="40">
         <v>0</v>
       </c>
-      <c r="N30" s="26">
-        <f t="shared" ref="N30:N35" si="5">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(N$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(N$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="I30" s="42">
+        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.987279516358749</v>
       </c>
-      <c r="O30" s="26">
-        <f t="shared" ref="O30:O35" si="6">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(O$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(O$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="J30" s="42">
+        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.93829461326294</v>
       </c>
-      <c r="P30" s="26">
-        <f t="shared" ref="P30:P35" si="7">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(P$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(P$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="K30" s="42">
+        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.835766276063232</v>
       </c>
-      <c r="Q30" s="26">
-        <f t="shared" ref="Q30:Q35" si="8">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(Q$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(Q$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="L30" s="42">
+        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.686485941521823</v>
       </c>
-      <c r="R30" s="26">
-        <f t="shared" ref="R30:R35" si="9">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(R$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(R$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="M30" s="42">
+        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.515491059226843</v>
       </c>
       <c r="S30" s="16"/>
@@ -4688,46 +4781,41 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:25">
       <c r="A31" s="16"/>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="39">
         <v>15</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="41">
         <v>0.15</v>
       </c>
       <c r="E31" s="16"/>
-      <c r="F31" s="24">
+      <c r="F31" s="40">
         <v>1</v>
       </c>
       <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="24">
+      <c r="H31" s="40">
         <v>5</v>
       </c>
-      <c r="N31" s="26">
-        <f t="shared" si="5"/>
+      <c r="I31" s="42">
+        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.012717637158798</v>
       </c>
-      <c r="O31" s="26">
-        <f t="shared" si="6"/>
+      <c r="J31" s="42">
+        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.0616244821124745</v>
       </c>
-      <c r="P31" s="26">
-        <f t="shared" si="7"/>
+      <c r="K31" s="42">
+        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.163448738545664</v>
       </c>
-      <c r="Q31" s="26">
-        <f t="shared" si="8"/>
+      <c r="L31" s="42">
+        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.309321044012904</v>
       </c>
-      <c r="R31" s="26">
-        <f t="shared" si="9"/>
+      <c r="M31" s="42">
+        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.469266415003386</v>
       </c>
       <c r="S31" s="16"/>
@@ -4740,46 +4828,41 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:25">
       <c r="A32" s="16"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="39">
         <v>20</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="41">
         <v>0.2</v>
       </c>
       <c r="E32" s="16"/>
-      <c r="F32" s="24">
+      <c r="F32" s="40">
         <v>2</v>
       </c>
       <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="24">
+      <c r="H32" s="40">
         <v>9</v>
       </c>
-      <c r="N32" s="26">
-        <f t="shared" si="5"/>
+      <c r="I32" s="42">
+        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>2.84614211698564e-6</v>
       </c>
-      <c r="O32" s="26">
-        <f t="shared" si="6"/>
+      <c r="J32" s="42">
+        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>8.08668558803793e-5</v>
       </c>
-      <c r="P32" s="26">
-        <f t="shared" si="7"/>
+      <c r="K32" s="42">
+        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.000783974137856025</v>
       </c>
-      <c r="Q32" s="26">
-        <f t="shared" si="8"/>
+      <c r="L32" s="42">
+        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.00418065022677183</v>
       </c>
-      <c r="R32" s="26">
-        <f t="shared" si="9"/>
+      <c r="M32" s="42">
+        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.015150867077619</v>
       </c>
       <c r="S32" s="16"/>
@@ -4792,46 +4875,41 @@
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:25">
       <c r="A33" s="16"/>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="39">
         <v>25</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="41">
         <v>0.25</v>
       </c>
       <c r="E33" s="16"/>
-      <c r="F33" s="24">
+      <c r="F33" s="40">
         <v>3</v>
       </c>
       <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="24">
+      <c r="H33" s="40">
         <v>12</v>
       </c>
-      <c r="N33" s="26">
-        <f t="shared" si="5"/>
+      <c r="I33" s="42">
+        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>3.40199979298461e-10</v>
       </c>
-      <c r="O33" s="26">
-        <f t="shared" si="6"/>
+      <c r="J33" s="42">
+        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>3.77310459542812e-8</v>
       </c>
-      <c r="P33" s="26">
-        <f t="shared" si="7"/>
+      <c r="K33" s="42">
+        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>1.00925440005284e-6</v>
       </c>
-      <c r="Q33" s="26">
-        <f t="shared" si="8"/>
+      <c r="L33" s="42">
+        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>1.23213976621628e-5</v>
       </c>
-      <c r="R33" s="26">
-        <f t="shared" si="9"/>
+      <c r="M33" s="42">
+        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>9.11421314999661e-5</v>
       </c>
       <c r="S33" s="16"/>
@@ -4844,46 +4922,41 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:25">
       <c r="A34" s="16"/>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="39">
         <v>30</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="41">
         <v>0.3</v>
       </c>
       <c r="E34" s="16"/>
-      <c r="F34" s="24">
+      <c r="F34" s="40">
         <v>4</v>
       </c>
       <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="24">
+      <c r="H34" s="40">
         <v>14</v>
       </c>
-      <c r="N34" s="26">
-        <f t="shared" si="5"/>
+      <c r="I34" s="42">
+        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>1.35003119794419e-13</v>
       </c>
-      <c r="O34" s="26">
-        <f t="shared" si="6"/>
+      <c r="J34" s="42">
+        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>3.72210040566756e-11</v>
       </c>
-      <c r="P34" s="26">
-        <f t="shared" si="7"/>
+      <c r="K34" s="42">
+        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>1.96607996549858e-9</v>
       </c>
-      <c r="Q34" s="26">
-        <f t="shared" si="8"/>
+      <c r="L34" s="42">
+        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>4.19095158576965e-8</v>
       </c>
-      <c r="R34" s="26">
-        <f t="shared" si="9"/>
+      <c r="M34" s="42">
+        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>5.02211745079251e-7</v>
       </c>
       <c r="S34" s="16"/>
@@ -4896,44 +4969,39 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:25">
       <c r="A35" s="16"/>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="39">
         <v>100</v>
       </c>
-      <c r="D35" s="24"/>
+      <c r="D35" s="39"/>
       <c r="E35" s="16"/>
-      <c r="F35" s="24">
+      <c r="F35" s="40">
         <v>5</v>
       </c>
       <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="24">
+      <c r="H35" s="40">
         <v>15</v>
       </c>
-      <c r="N35" s="26">
-        <f t="shared" si="5"/>
+      <c r="I35" s="42">
+        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0</v>
       </c>
-      <c r="O35" s="26">
-        <f t="shared" si="6"/>
+      <c r="J35" s="42">
+        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>4.37871960912162e-13</v>
       </c>
-      <c r="P35" s="26">
-        <f t="shared" si="7"/>
+      <c r="K35" s="42">
+        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>3.27680105272066e-11</v>
       </c>
-      <c r="Q35" s="26">
-        <f t="shared" si="8"/>
+      <c r="L35" s="42">
+        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>9.31322574615479e-10</v>
       </c>
-      <c r="R35" s="26">
-        <f t="shared" si="9"/>
+      <c r="M35" s="42">
+        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>1.43489069515113e-8</v>
       </c>
       <c r="S35" s="16"/>
@@ -4950,7 +5018,7 @@
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
-      <c r="F36" s="24">
+      <c r="F36" s="40">
         <v>6</v>
       </c>
       <c r="G36" s="16"/>
@@ -4979,7 +5047,7 @@
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
-      <c r="F37" s="24">
+      <c r="F37" s="40">
         <v>7</v>
       </c>
       <c r="G37" s="16"/>
@@ -5008,7 +5076,7 @@
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
-      <c r="F38" s="24">
+      <c r="F38" s="40">
         <v>8</v>
       </c>
       <c r="G38" s="16"/>
@@ -5037,7 +5105,7 @@
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
-      <c r="F39" s="24">
+      <c r="F39" s="40">
         <v>9</v>
       </c>
       <c r="G39" s="16"/>
@@ -5066,7 +5134,7 @@
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
-      <c r="F40" s="24">
+      <c r="F40" s="40">
         <v>10</v>
       </c>
       <c r="G40" s="16"/>
@@ -5095,7 +5163,7 @@
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
-      <c r="F41" s="24">
+      <c r="F41" s="40">
         <v>11</v>
       </c>
       <c r="G41" s="16"/>
@@ -5124,7 +5192,7 @@
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
-      <c r="F42" s="24">
+      <c r="F42" s="40">
         <v>12</v>
       </c>
       <c r="G42" s="16"/>
@@ -5153,7 +5221,7 @@
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
-      <c r="F43" s="24">
+      <c r="F43" s="40">
         <v>13</v>
       </c>
       <c r="G43" s="16"/>
@@ -5182,7 +5250,7 @@
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
-      <c r="F44" s="24">
+      <c r="F44" s="40">
         <v>14</v>
       </c>
       <c r="G44" s="16"/>
@@ -5211,7 +5279,7 @@
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
-      <c r="F45" s="24">
+      <c r="F45" s="40">
         <v>15</v>
       </c>
       <c r="G45" s="16"/>
@@ -5240,7 +5308,7 @@
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
-      <c r="F46" s="24"/>
+      <c r="F46" s="30"/>
       <c r="G46" s="16"/>
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
@@ -5267,7 +5335,7 @@
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
-      <c r="F47" s="24"/>
+      <c r="F47" s="30"/>
       <c r="G47" s="16"/>
       <c r="H47" s="16"/>
       <c r="I47" s="16"/>
@@ -5294,7 +5362,7 @@
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
-      <c r="F48" s="24"/>
+      <c r="F48" s="30"/>
       <c r="G48" s="16"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
@@ -5321,7 +5389,7 @@
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
-      <c r="F49" s="24"/>
+      <c r="F49" s="30"/>
       <c r="G49" s="16"/>
       <c r="H49" s="16"/>
       <c r="I49" s="16"/>
@@ -5348,7 +5416,7 @@
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
-      <c r="F50" s="24"/>
+      <c r="F50" s="30"/>
       <c r="G50" s="16"/>
       <c r="H50" s="16"/>
       <c r="I50" s="16"/>
@@ -5375,7 +5443,7 @@
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
-      <c r="F51" s="24"/>
+      <c r="F51" s="30"/>
       <c r="G51" s="16"/>
       <c r="H51" s="16"/>
       <c r="I51" s="16"/>
@@ -5402,7 +5470,7 @@
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
-      <c r="F52" s="24"/>
+      <c r="F52" s="30"/>
       <c r="G52" s="16"/>
       <c r="H52" s="16"/>
       <c r="I52" s="16"/>
@@ -5429,7 +5497,7 @@
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
-      <c r="F53" s="24"/>
+      <c r="F53" s="30"/>
       <c r="G53" s="16"/>
       <c r="H53" s="16"/>
       <c r="I53" s="16"/>
@@ -5451,15 +5519,15 @@
       <c r="Y53" s="16"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
       <c r="H54" s="16"/>
       <c r="I54" s="16"/>
       <c r="J54" s="16"/>
@@ -5480,18 +5548,18 @@
       <c r="Y54" s="16"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="43"/>
+      <c r="H55" s="43"/>
+      <c r="I55" s="43"/>
+      <c r="J55" s="43"/>
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
@@ -5509,14 +5577,14 @@
       <c r="Y55" s="16"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
+      <c r="B56" s="43"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
       <c r="G56" s="16"/>
       <c r="H56" s="16"/>
       <c r="I56" s="16"/>
@@ -5573,33 +5641,33 @@
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="22"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="22"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="22"/>
-      <c r="R58" s="22"/>
-      <c r="S58" s="22"/>
-      <c r="T58" s="22"/>
-      <c r="U58" s="22"/>
-      <c r="V58" s="22"/>
-      <c r="W58" s="22"/>
-      <c r="X58" s="22"/>
-      <c r="Y58" s="22"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="28"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
+      <c r="X58" s="28"/>
+      <c r="Y58" s="28"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
       <c r="G59" s="16"/>
@@ -5641,22 +5709,22 @@
       <c r="L60" s="9"/>
       <c r="M60" s="9"/>
       <c r="N60" s="9"/>
-      <c r="O60" s="25"/>
-      <c r="P60" s="25"/>
-      <c r="Q60" s="25"/>
-      <c r="R60" s="25"/>
-      <c r="S60" s="25"/>
-      <c r="T60" s="25"/>
-      <c r="U60" s="25"/>
-      <c r="V60" s="25"/>
-      <c r="W60" s="25"/>
-      <c r="X60" s="25"/>
-      <c r="Y60" s="25"/>
+      <c r="O60" s="34"/>
+      <c r="P60" s="34"/>
+      <c r="Q60" s="34"/>
+      <c r="R60" s="34"/>
+      <c r="S60" s="34"/>
+      <c r="T60" s="34"/>
+      <c r="U60" s="34"/>
+      <c r="V60" s="34"/>
+      <c r="W60" s="34"/>
+      <c r="X60" s="34"/>
+      <c r="Y60" s="34"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:25">
       <c r="A61" s="16"/>
-      <c r="B61" s="19" t="s">
-        <v>110</v>
+      <c r="B61" s="26" t="s">
+        <v>105</v>
       </c>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
@@ -5685,10 +5753,10 @@
     <row r="62" ht="16.5" customHeight="1" spans="1:25">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="24" t="s">
+      <c r="D62" s="30" t="s">
         <v>39</v>
       </c>
       <c r="E62" s="16"/>
@@ -5696,58 +5764,58 @@
         <v>104</v>
       </c>
       <c r="G62" s="16"/>
-      <c r="H62" s="24" t="s">
+      <c r="H62" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="I62" s="24">
+      <c r="I62" s="30">
         <v>0</v>
       </c>
-      <c r="J62" s="24">
+      <c r="J62" s="30">
         <v>1</v>
       </c>
-      <c r="K62" s="24">
+      <c r="K62" s="30">
         <v>2</v>
       </c>
-      <c r="L62" s="24">
+      <c r="L62" s="30">
         <v>3</v>
       </c>
-      <c r="M62" s="24">
+      <c r="M62" s="30">
         <v>4</v>
       </c>
-      <c r="N62" s="24">
+      <c r="N62" s="30">
         <v>5</v>
       </c>
-      <c r="O62" s="24">
+      <c r="O62" s="30">
         <v>6</v>
       </c>
-      <c r="P62" s="24">
+      <c r="P62" s="30">
         <v>7</v>
       </c>
-      <c r="Q62" s="24">
+      <c r="Q62" s="30">
         <v>8</v>
       </c>
-      <c r="R62" s="24">
+      <c r="R62" s="30">
         <v>9</v>
       </c>
-      <c r="S62" s="24">
+      <c r="S62" s="30">
         <v>10</v>
       </c>
-      <c r="T62" s="24">
+      <c r="T62" s="30">
         <v>11</v>
       </c>
-      <c r="U62" s="24">
+      <c r="U62" s="30">
         <v>12</v>
       </c>
-      <c r="V62" s="24">
+      <c r="V62" s="30">
         <v>13</v>
       </c>
-      <c r="W62" s="24">
+      <c r="W62" s="30">
         <v>14</v>
       </c>
-      <c r="X62" s="24">
+      <c r="X62" s="30">
         <v>15</v>
       </c>
-      <c r="Y62" s="24"/>
+      <c r="Y62" s="30"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:25">
       <c r="A63" s="16"/>
@@ -5757,7 +5825,7 @@
       <c r="C63" s="16">
         <v>10</v>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="44">
         <v>0.1</v>
       </c>
       <c r="E63" s="16"/>
@@ -5765,75 +5833,75 @@
         <v>34</v>
       </c>
       <c r="G63" s="16"/>
-      <c r="H63" s="24">
+      <c r="H63" s="30">
         <v>0</v>
       </c>
-      <c r="I63" s="20">
-        <f t="shared" ref="I63:Y63" si="10">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I63" s="44">
+        <f t="shared" ref="I63:Y63" si="5">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="L63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="N63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="O63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="Q63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="R63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="S63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="T63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="U63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="V63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="W63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="X63" s="20" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="Y63" s="20">
-        <f t="shared" si="10"/>
+      <c r="J63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="K63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="L63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="M63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="N63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="R63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="S63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="T63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="V63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="W63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="X63" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Y63" s="44">
+        <f t="shared" si="5"/>
         <v>0.205891132094649</v>
       </c>
     </row>
@@ -5845,81 +5913,81 @@
       <c r="C64" s="16">
         <v>15</v>
       </c>
-      <c r="D64" s="20">
+      <c r="D64" s="44">
         <v>0.15</v>
       </c>
       <c r="E64" s="16"/>
       <c r="F64" s="16"/>
       <c r="G64" s="16"/>
-      <c r="H64" s="24">
+      <c r="H64" s="30">
         <v>1</v>
       </c>
-      <c r="I64" s="20">
-        <f t="shared" ref="I64:Y64" si="11">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I64" s="44">
+        <f t="shared" ref="I64:Y64" si="6">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.343151886824415</v>
       </c>
-      <c r="J64" s="20">
-        <f t="shared" si="11"/>
+      <c r="J64" s="44">
+        <f t="shared" si="6"/>
         <v>0.22876792454961</v>
       </c>
-      <c r="K64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="L64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="M64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="N64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="O64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="P64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="R64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="S64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="T64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="U64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="W64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="X64" s="20" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Y64" s="20">
-        <f t="shared" si="11"/>
+      <c r="K64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="L64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="N64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="O64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="P64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Q64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="R64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="S64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="T64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="U64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="V64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="W64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="X64" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Y64" s="44">
+        <f t="shared" si="6"/>
         <v>0.343151886824415</v>
       </c>
     </row>
@@ -5931,81 +5999,81 @@
       <c r="C65" s="16">
         <v>20</v>
       </c>
-      <c r="D65" s="20">
+      <c r="D65" s="44">
         <v>0.2</v>
       </c>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
       <c r="G65" s="16"/>
-      <c r="H65" s="24">
+      <c r="H65" s="30">
         <v>2</v>
       </c>
-      <c r="I65" s="20">
-        <f t="shared" ref="I65:Y65" si="12">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I65" s="44">
+        <f t="shared" ref="I65:Y65" si="7">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.266895911974545</v>
       </c>
-      <c r="J65" s="20">
-        <f t="shared" si="12"/>
+      <c r="J65" s="44">
+        <f t="shared" si="7"/>
         <v>0.35586121596606</v>
       </c>
-      <c r="K65" s="20">
-        <f t="shared" si="12"/>
+      <c r="K65" s="44">
+        <f t="shared" si="7"/>
         <v>0.2541865828329</v>
       </c>
-      <c r="L65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="M65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="N65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="O65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="Q65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="R65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="S65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="T65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="U65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="V65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="X65" s="20" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="Y65" s="20">
-        <f t="shared" si="12"/>
+      <c r="L65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="M65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="N65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="O65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="P65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="Q65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="R65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="S65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="T65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="U65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="V65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="W65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="X65" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="Y65" s="44">
+        <f t="shared" si="7"/>
         <v>0.266895911974545</v>
       </c>
     </row>
@@ -6017,81 +6085,81 @@
       <c r="C66" s="16">
         <v>25</v>
       </c>
-      <c r="D66" s="20">
+      <c r="D66" s="44">
         <v>0.25</v>
       </c>
       <c r="E66" s="16"/>
       <c r="F66" s="16"/>
       <c r="G66" s="16"/>
-      <c r="H66" s="24">
+      <c r="H66" s="30">
         <v>3</v>
       </c>
-      <c r="I66" s="20">
-        <f t="shared" ref="I66:Y66" si="13">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I66" s="44">
+        <f t="shared" ref="I66:Y66" si="8">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.128505439098855</v>
       </c>
-      <c r="J66" s="20">
-        <f t="shared" si="13"/>
+      <c r="J66" s="44">
+        <f t="shared" si="8"/>
         <v>0.25701087819771</v>
       </c>
-      <c r="K66" s="20">
-        <f t="shared" si="13"/>
+      <c r="K66" s="44">
+        <f t="shared" si="8"/>
         <v>0.3671583974253</v>
       </c>
-      <c r="L66" s="20">
-        <f t="shared" si="13"/>
+      <c r="L66" s="44">
+        <f t="shared" si="8"/>
         <v>0.282429536481</v>
       </c>
-      <c r="M66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="N66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="O66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="P66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Q66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="R66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="S66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="T66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="V66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="W66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X66" s="20" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Y66" s="20">
-        <f t="shared" si="13"/>
+      <c r="M66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="N66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="O66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="P66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Q66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="R66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="S66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="T66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="U66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="V66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="W66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="X66" s="44" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="Y66" s="44">
+        <f t="shared" si="8"/>
         <v>0.128505439098855</v>
       </c>
     </row>
@@ -6103,81 +6171,81 @@
       <c r="C67" s="16">
         <v>30</v>
       </c>
-      <c r="D67" s="20">
+      <c r="D67" s="44">
         <v>0.3</v>
       </c>
       <c r="E67" s="16"/>
       <c r="F67" s="16"/>
       <c r="G67" s="16"/>
-      <c r="H67" s="24">
+      <c r="H67" s="30">
         <v>4</v>
       </c>
-      <c r="I67" s="20">
-        <f t="shared" ref="I67:Y67" si="14">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I67" s="44">
+        <f t="shared" ref="I67:Y67" si="9">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J67" s="20">
-        <f t="shared" si="14"/>
+      <c r="J67" s="44">
+        <f t="shared" si="9"/>
         <v>0.11422705697676</v>
       </c>
-      <c r="K67" s="20">
-        <f t="shared" si="14"/>
+      <c r="K67" s="44">
+        <f t="shared" si="9"/>
         <v>0.2447722649502</v>
       </c>
-      <c r="L67" s="20">
-        <f t="shared" si="14"/>
+      <c r="L67" s="44">
+        <f t="shared" si="9"/>
         <v>0.376572715308</v>
       </c>
-      <c r="M67" s="20">
-        <f t="shared" si="14"/>
+      <c r="M67" s="44">
+        <f t="shared" si="9"/>
         <v>0.31381059609</v>
       </c>
-      <c r="N67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="O67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="P67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Q67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="R67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="S67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="T67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="U67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="V67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="W67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="X67" s="20" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y67" s="20">
-        <f t="shared" si="14"/>
+      <c r="N67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="O67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="P67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="Q67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="R67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="S67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="T67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="U67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="V67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="W67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="X67" s="44" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="Y67" s="44">
+        <f t="shared" si="9"/>
         <v>0.0428351463662851</v>
       </c>
     </row>
@@ -6193,75 +6261,75 @@
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
-      <c r="H68" s="24">
+      <c r="H68" s="30">
         <v>5</v>
       </c>
-      <c r="I68" s="28">
-        <f t="shared" ref="I68:Y68" si="15">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I68" s="45">
+        <f t="shared" ref="I68:Y68" si="10">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.010470813556203</v>
       </c>
-      <c r="J68" s="28">
-        <f t="shared" si="15"/>
+      <c r="J68" s="45">
+        <f t="shared" si="10"/>
         <v>0.03490271185401</v>
       </c>
-      <c r="K68" s="28">
-        <f t="shared" si="15"/>
+      <c r="K68" s="45">
+        <f t="shared" si="10"/>
         <v>0.0997220338686001</v>
       </c>
-      <c r="L68" s="28">
-        <f t="shared" si="15"/>
+      <c r="L68" s="45">
+        <f t="shared" si="10"/>
         <v>0.230127770466</v>
       </c>
-      <c r="M68" s="28">
-        <f t="shared" si="15"/>
+      <c r="M68" s="45">
+        <f t="shared" si="10"/>
         <v>0.38354628411</v>
       </c>
-      <c r="N68" s="28">
-        <f t="shared" si="15"/>
+      <c r="N68" s="45">
+        <f t="shared" si="10"/>
         <v>0.3486784401</v>
       </c>
-      <c r="O68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="P68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Q68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="R68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="S68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="T68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="U68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="V68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="W68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X68" s="20" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Y68" s="20">
-        <f t="shared" si="15"/>
+      <c r="O68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Q68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="R68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="S68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="T68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="V68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="W68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="X68" s="44" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Y68" s="44">
+        <f t="shared" si="10"/>
         <v>0.010470813556203</v>
       </c>
     </row>
@@ -6273,75 +6341,75 @@
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
       <c r="G69" s="16"/>
-      <c r="H69" s="24">
+      <c r="H69" s="30">
         <v>6</v>
       </c>
-      <c r="I69" s="20">
-        <f t="shared" ref="I69:Y69" si="16">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I69" s="44">
+        <f t="shared" ref="I69:Y69" si="11">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.001939039547445</v>
       </c>
-      <c r="J69" s="20">
-        <f t="shared" si="16"/>
+      <c r="J69" s="44">
+        <f t="shared" si="11"/>
         <v>0.00775615818978</v>
       </c>
-      <c r="K69" s="20">
-        <f t="shared" si="16"/>
+      <c r="K69" s="44">
+        <f t="shared" si="11"/>
         <v>0.0277005649635</v>
       </c>
-      <c r="L69" s="20">
-        <f t="shared" si="16"/>
+      <c r="L69" s="44">
+        <f t="shared" si="11"/>
         <v>0.08523250758</v>
       </c>
-      <c r="M69" s="20">
-        <f t="shared" si="16"/>
+      <c r="M69" s="44">
+        <f t="shared" si="11"/>
         <v>0.21308126895</v>
       </c>
-      <c r="N69" s="20">
-        <f t="shared" si="16"/>
+      <c r="N69" s="44">
+        <f t="shared" si="11"/>
         <v>0.387420489</v>
       </c>
-      <c r="O69" s="20">
-        <f t="shared" si="16"/>
+      <c r="O69" s="44">
+        <f t="shared" si="11"/>
         <v>0.387420489</v>
       </c>
-      <c r="P69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="Q69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="R69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="S69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="T69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="U69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="V69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="W69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="X69" s="20" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="Y69" s="20">
-        <f t="shared" si="16"/>
+      <c r="P69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="Q69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="S69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="T69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="U69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="V69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="W69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="X69" s="44" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="Y69" s="44">
+        <f t="shared" si="11"/>
         <v>0.001939039547445</v>
       </c>
     </row>
@@ -6353,75 +6421,75 @@
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
       <c r="G70" s="16"/>
-      <c r="H70" s="24">
+      <c r="H70" s="30">
         <v>7</v>
       </c>
-      <c r="I70" s="20">
-        <f t="shared" ref="I70:Y70" si="17">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I70" s="44">
+        <f t="shared" ref="I70:Y70" si="12">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.000277005649635</v>
       </c>
-      <c r="J70" s="20">
-        <f t="shared" si="17"/>
+      <c r="J70" s="44">
+        <f t="shared" si="12"/>
         <v>0.00129269303163</v>
       </c>
-      <c r="K70" s="20">
-        <f t="shared" si="17"/>
+      <c r="K70" s="44">
+        <f t="shared" si="12"/>
         <v>0.0055401129927</v>
       </c>
-      <c r="L70" s="20">
-        <f t="shared" si="17"/>
+      <c r="L70" s="44">
+        <f t="shared" si="12"/>
         <v>0.021308126895</v>
       </c>
-      <c r="M70" s="20">
-        <f t="shared" si="17"/>
+      <c r="M70" s="44">
+        <f t="shared" si="12"/>
         <v>0.07102708965</v>
       </c>
-      <c r="N70" s="20">
-        <f t="shared" si="17"/>
+      <c r="N70" s="44">
+        <f t="shared" si="12"/>
         <v>0.1937102445</v>
       </c>
-      <c r="O70" s="20">
-        <f t="shared" si="17"/>
+      <c r="O70" s="44">
+        <f t="shared" si="12"/>
         <v>0.387420489</v>
       </c>
-      <c r="P70" s="20">
-        <f t="shared" si="17"/>
+      <c r="P70" s="44">
+        <f t="shared" si="12"/>
         <v>0.43046721</v>
       </c>
-      <c r="Q70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="R70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="S70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="T70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="U70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="V70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="W70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="X70" s="20" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="Y70" s="20">
-        <f t="shared" si="17"/>
+      <c r="Q70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="R70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="T70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="V70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="W70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X70" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Y70" s="44">
+        <f t="shared" si="12"/>
         <v>0.000277005649635</v>
       </c>
     </row>
@@ -6433,75 +6501,75 @@
       <c r="E71" s="16"/>
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
-      <c r="H71" s="24">
+      <c r="H71" s="30">
         <v>8</v>
       </c>
-      <c r="I71" s="20">
-        <f t="shared" ref="I71:Y71" si="18">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I71" s="44">
+        <f t="shared" ref="I71:Y71" si="13">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J71" s="20">
-        <f t="shared" si="18"/>
+      <c r="J71" s="44">
+        <f t="shared" si="13"/>
         <v>0.00016415149608</v>
       </c>
-      <c r="K71" s="20">
-        <f t="shared" si="18"/>
+      <c r="K71" s="44">
+        <f t="shared" si="13"/>
         <v>0.0008207574804</v>
       </c>
-      <c r="L71" s="20">
-        <f t="shared" si="18"/>
+      <c r="L71" s="44">
+        <f t="shared" si="13"/>
         <v>0.003788111448</v>
       </c>
-      <c r="M71" s="20">
-        <f t="shared" si="18"/>
+      <c r="M71" s="44">
+        <f t="shared" si="13"/>
         <v>0.0157837977</v>
       </c>
-      <c r="N71" s="20">
-        <f t="shared" si="18"/>
+      <c r="N71" s="44">
+        <f t="shared" si="13"/>
         <v>0.057395628</v>
       </c>
-      <c r="O71" s="20">
-        <f t="shared" si="18"/>
+      <c r="O71" s="44">
+        <f t="shared" si="13"/>
         <v>0.172186884</v>
       </c>
-      <c r="P71" s="20">
-        <f t="shared" si="18"/>
+      <c r="P71" s="44">
+        <f t="shared" si="13"/>
         <v>0.38263752</v>
       </c>
-      <c r="Q71" s="20">
-        <f t="shared" si="18"/>
+      <c r="Q71" s="44">
+        <f t="shared" si="13"/>
         <v>0.4782969</v>
       </c>
-      <c r="R71" s="20" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="S71" s="20" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="T71" s="20" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="U71" s="20" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="V71" s="20" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="W71" s="20" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="X71" s="20" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Y71" s="20">
-        <f t="shared" si="18"/>
+      <c r="R71" s="44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="S71" s="44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="T71" s="44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="U71" s="44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V71" s="44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="W71" s="44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X71" s="44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y71" s="44">
+        <f t="shared" si="13"/>
         <v>3.0778405515e-5</v>
       </c>
     </row>
@@ -6513,75 +6581,75 @@
       <c r="E72" s="16"/>
       <c r="F72" s="16"/>
       <c r="G72" s="16"/>
-      <c r="H72" s="24">
+      <c r="H72" s="30">
         <v>9</v>
       </c>
-      <c r="I72" s="20">
-        <f t="shared" ref="I72:Y72" si="19">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I72" s="44">
+        <f t="shared" ref="I72:Y72" si="14">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J72" s="20">
-        <f t="shared" si="19"/>
+      <c r="J72" s="44">
+        <f t="shared" si="14"/>
         <v>1.595917323e-5</v>
       </c>
-      <c r="K72" s="20">
-        <f t="shared" si="19"/>
+      <c r="K72" s="44">
+        <f t="shared" si="14"/>
         <v>9.11952756e-5</v>
       </c>
-      <c r="L72" s="20">
-        <f t="shared" si="19"/>
+      <c r="L72" s="44">
+        <f t="shared" si="14"/>
         <v>0.000491051484000001</v>
       </c>
-      <c r="M72" s="20">
-        <f t="shared" si="19"/>
+      <c r="M72" s="44">
+        <f t="shared" si="14"/>
         <v>0.00245525742</v>
       </c>
-      <c r="N72" s="20">
-        <f t="shared" si="19"/>
+      <c r="N72" s="44">
+        <f t="shared" si="14"/>
         <v>0.011160261</v>
       </c>
-      <c r="O72" s="20">
-        <f t="shared" si="19"/>
+      <c r="O72" s="44">
+        <f t="shared" si="14"/>
         <v>0.044641044</v>
       </c>
-      <c r="P72" s="20">
-        <f t="shared" si="19"/>
+      <c r="P72" s="44">
+        <f t="shared" si="14"/>
         <v>0.14880348</v>
       </c>
-      <c r="Q72" s="20">
-        <f t="shared" si="19"/>
+      <c r="Q72" s="44">
+        <f t="shared" si="14"/>
         <v>0.3720087</v>
       </c>
-      <c r="R72" s="20">
-        <f t="shared" si="19"/>
+      <c r="R72" s="44">
+        <f t="shared" si="14"/>
         <v>0.531441</v>
       </c>
-      <c r="S72" s="20" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="T72" s="20" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="U72" s="20" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="V72" s="20" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="W72" s="20" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="X72" s="20" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="Y72" s="20">
-        <f t="shared" si="19"/>
+      <c r="S72" s="44" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="T72" s="44" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U72" s="44" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="V72" s="44" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="W72" s="44" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="X72" s="44" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Y72" s="44">
+        <f t="shared" si="14"/>
         <v>2.659862205e-6</v>
       </c>
     </row>
@@ -6593,75 +6661,75 @@
       <c r="E73" s="16"/>
       <c r="F73" s="16"/>
       <c r="G73" s="16"/>
-      <c r="H73" s="24">
+      <c r="H73" s="30">
         <v>10</v>
       </c>
-      <c r="I73" s="20">
-        <f t="shared" ref="I73:Y73" si="20">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I73" s="44">
+        <f t="shared" ref="I73:Y73" si="15">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J73" s="20">
-        <f t="shared" si="20"/>
+      <c r="J73" s="44">
+        <f t="shared" si="15"/>
         <v>1.18216098e-6</v>
       </c>
-      <c r="K73" s="20">
-        <f t="shared" si="20"/>
+      <c r="K73" s="44">
+        <f t="shared" si="15"/>
         <v>7.5996063e-6</v>
       </c>
-      <c r="L73" s="20">
-        <f t="shared" si="20"/>
+      <c r="L73" s="44">
+        <f t="shared" si="15"/>
         <v>4.6766808e-5</v>
       </c>
-      <c r="M73" s="20">
-        <f t="shared" si="20"/>
+      <c r="M73" s="44">
+        <f t="shared" si="15"/>
         <v>0.00027280638</v>
       </c>
-      <c r="N73" s="20">
-        <f t="shared" si="20"/>
+      <c r="N73" s="44">
+        <f t="shared" si="15"/>
         <v>0.0014880348</v>
       </c>
-      <c r="O73" s="20">
-        <f t="shared" si="20"/>
+      <c r="O73" s="44">
+        <f t="shared" si="15"/>
         <v>0.00744017399999999</v>
       </c>
-      <c r="P73" s="20">
-        <f t="shared" si="20"/>
+      <c r="P73" s="44">
+        <f t="shared" si="15"/>
         <v>0.03306744</v>
       </c>
-      <c r="Q73" s="20">
-        <f t="shared" si="20"/>
+      <c r="Q73" s="44">
+        <f t="shared" si="15"/>
         <v>0.1240029</v>
       </c>
-      <c r="R73" s="20">
-        <f t="shared" si="20"/>
+      <c r="R73" s="44">
+        <f t="shared" si="15"/>
         <v>0.354294</v>
       </c>
-      <c r="S73" s="20">
-        <f t="shared" si="20"/>
+      <c r="S73" s="44">
+        <f t="shared" si="15"/>
         <v>0.59049</v>
       </c>
-      <c r="T73" s="20" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="U73" s="20" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="V73" s="20" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="W73" s="20" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="X73" s="20" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="Y73" s="20">
-        <f t="shared" si="20"/>
+      <c r="T73" s="44" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="U73" s="44" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V73" s="44" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="W73" s="44" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="X73" s="44" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="Y73" s="44">
+        <f t="shared" si="15"/>
         <v>1.77324147e-7</v>
       </c>
     </row>
@@ -6673,75 +6741,75 @@
       <c r="E74" s="16"/>
       <c r="F74" s="16"/>
       <c r="G74" s="16"/>
-      <c r="H74" s="24">
+      <c r="H74" s="30">
         <v>11</v>
       </c>
-      <c r="I74" s="20">
-        <f t="shared" ref="I74:Y74" si="21">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I74" s="44">
+        <f t="shared" ref="I74:Y74" si="16">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J74" s="20">
-        <f t="shared" si="21"/>
+      <c r="J74" s="44">
+        <f t="shared" si="16"/>
         <v>6.56756100000002e-8</v>
       </c>
-      <c r="K74" s="20">
-        <f t="shared" si="21"/>
+      <c r="K74" s="44">
+        <f t="shared" si="16"/>
         <v>4.69111499999999e-7</v>
       </c>
-      <c r="L74" s="20">
-        <f t="shared" si="21"/>
+      <c r="L74" s="44">
+        <f t="shared" si="16"/>
         <v>3.247695e-6</v>
       </c>
-      <c r="M74" s="20">
-        <f t="shared" si="21"/>
+      <c r="M74" s="44">
+        <f t="shared" si="16"/>
         <v>2.16512999999999e-5</v>
       </c>
-      <c r="N74" s="20">
-        <f t="shared" si="21"/>
+      <c r="N74" s="44">
+        <f t="shared" si="16"/>
         <v>0.000137781</v>
       </c>
-      <c r="O74" s="20">
-        <f t="shared" si="21"/>
+      <c r="O74" s="44">
+        <f t="shared" si="16"/>
         <v>0.000826686</v>
       </c>
-      <c r="P74" s="20">
-        <f t="shared" si="21"/>
+      <c r="P74" s="44">
+        <f t="shared" si="16"/>
         <v>0.0045927</v>
       </c>
-      <c r="Q74" s="20">
-        <f t="shared" si="21"/>
+      <c r="Q74" s="44">
+        <f t="shared" si="16"/>
         <v>0.0229635</v>
       </c>
-      <c r="R74" s="20">
-        <f t="shared" si="21"/>
+      <c r="R74" s="44">
+        <f t="shared" si="16"/>
         <v>0.0984150000000001</v>
       </c>
-      <c r="S74" s="20">
-        <f t="shared" si="21"/>
+      <c r="S74" s="44">
+        <f t="shared" si="16"/>
         <v>0.32805</v>
       </c>
-      <c r="T74" s="20">
-        <f t="shared" si="21"/>
+      <c r="T74" s="44">
+        <f t="shared" si="16"/>
         <v>0.6561</v>
       </c>
-      <c r="U74" s="20" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="V74" s="20" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="W74" s="20" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="X74" s="20" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="Y74" s="20">
-        <f t="shared" si="21"/>
+      <c r="U74" s="44" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="V74" s="44" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W74" s="44" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="X74" s="44" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y74" s="44">
+        <f t="shared" si="16"/>
         <v>8.95576499999999e-9</v>
       </c>
     </row>
@@ -6753,75 +6821,75 @@
       <c r="E75" s="16"/>
       <c r="F75" s="16"/>
       <c r="G75" s="16"/>
-      <c r="H75" s="24">
+      <c r="H75" s="30">
         <v>12</v>
       </c>
-      <c r="I75" s="20">
-        <f t="shared" ref="I75:Y75" si="22">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I75" s="44">
+        <f t="shared" ref="I75:Y75" si="17">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J75" s="20">
-        <f t="shared" si="22"/>
+      <c r="J75" s="44">
+        <f t="shared" si="17"/>
         <v>2.65356e-9</v>
       </c>
-      <c r="K75" s="20">
-        <f t="shared" si="22"/>
+      <c r="K75" s="44">
+        <f t="shared" si="17"/>
         <v>2.08494e-8</v>
       </c>
-      <c r="L75" s="20">
-        <f t="shared" si="22"/>
+      <c r="L75" s="44">
+        <f t="shared" si="17"/>
         <v>1.6038e-7</v>
       </c>
-      <c r="M75" s="20">
-        <f t="shared" si="22"/>
+      <c r="M75" s="44">
+        <f t="shared" si="17"/>
         <v>1.20285e-6</v>
       </c>
-      <c r="N75" s="20">
-        <f t="shared" si="22"/>
+      <c r="N75" s="44">
+        <f t="shared" si="17"/>
         <v>8.74800000000001e-6</v>
       </c>
-      <c r="O75" s="20">
-        <f t="shared" si="22"/>
+      <c r="O75" s="44">
+        <f t="shared" si="17"/>
         <v>6.1236e-5</v>
       </c>
-      <c r="P75" s="20">
-        <f t="shared" si="22"/>
+      <c r="P75" s="44">
+        <f t="shared" si="17"/>
         <v>0.00040824</v>
       </c>
-      <c r="Q75" s="20">
-        <f t="shared" si="22"/>
+      <c r="Q75" s="44">
+        <f t="shared" si="17"/>
         <v>0.0025515</v>
       </c>
-      <c r="R75" s="20">
-        <f t="shared" si="22"/>
+      <c r="R75" s="44">
+        <f t="shared" si="17"/>
         <v>0.01458</v>
       </c>
-      <c r="S75" s="20">
-        <f t="shared" si="22"/>
+      <c r="S75" s="44">
+        <f t="shared" si="17"/>
         <v>0.0729</v>
       </c>
-      <c r="T75" s="20">
-        <f t="shared" si="22"/>
+      <c r="T75" s="44">
+        <f t="shared" si="17"/>
         <v>0.2916</v>
       </c>
-      <c r="U75" s="20">
-        <f t="shared" si="22"/>
+      <c r="U75" s="44">
+        <f t="shared" si="17"/>
         <v>0.729</v>
       </c>
-      <c r="V75" s="20" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="W75" s="20" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="X75" s="20" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="Y75" s="20">
-        <f t="shared" si="22"/>
+      <c r="V75" s="44" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="W75" s="44" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X75" s="44" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Y75" s="44">
+        <f t="shared" si="17"/>
         <v>3.31695000000002e-10</v>
       </c>
     </row>
@@ -6833,75 +6901,75 @@
       <c r="E76" s="16"/>
       <c r="F76" s="16"/>
       <c r="G76" s="16"/>
-      <c r="H76" s="24">
+      <c r="H76" s="30">
         <v>13</v>
       </c>
-      <c r="I76" s="20">
-        <f t="shared" ref="I76:Y76" si="23">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I76" s="44">
+        <f t="shared" ref="I76:Y76" si="18">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J76" s="20">
-        <f t="shared" si="23"/>
+      <c r="J76" s="44">
+        <f t="shared" si="18"/>
         <v>7.37100000000002e-11</v>
       </c>
-      <c r="K76" s="20">
-        <f t="shared" si="23"/>
+      <c r="K76" s="44">
+        <f t="shared" si="18"/>
         <v>6.318e-10</v>
       </c>
-      <c r="L76" s="20">
-        <f t="shared" si="23"/>
+      <c r="L76" s="44">
+        <f t="shared" si="18"/>
         <v>5.34599999999998e-9</v>
       </c>
-      <c r="M76" s="20">
-        <f t="shared" si="23"/>
+      <c r="M76" s="44">
+        <f t="shared" si="18"/>
         <v>4.455e-8</v>
       </c>
-      <c r="N76" s="20">
-        <f t="shared" si="23"/>
+      <c r="N76" s="44">
+        <f t="shared" si="18"/>
         <v>3.64500000000001e-7</v>
       </c>
-      <c r="O76" s="20">
-        <f t="shared" si="23"/>
+      <c r="O76" s="44">
+        <f t="shared" si="18"/>
         <v>2.916e-6</v>
       </c>
-      <c r="P76" s="20">
-        <f t="shared" si="23"/>
+      <c r="P76" s="44">
+        <f t="shared" si="18"/>
         <v>2.268e-5</v>
       </c>
-      <c r="Q76" s="20">
-        <f t="shared" si="23"/>
+      <c r="Q76" s="44">
+        <f t="shared" si="18"/>
         <v>0.0001701</v>
       </c>
-      <c r="R76" s="20">
-        <f t="shared" si="23"/>
+      <c r="R76" s="44">
+        <f t="shared" si="18"/>
         <v>0.001215</v>
       </c>
-      <c r="S76" s="20">
-        <f t="shared" si="23"/>
+      <c r="S76" s="44">
+        <f t="shared" si="18"/>
         <v>0.0081</v>
       </c>
-      <c r="T76" s="20">
-        <f t="shared" si="23"/>
+      <c r="T76" s="44">
+        <f t="shared" si="18"/>
         <v>0.0486</v>
       </c>
-      <c r="U76" s="20">
-        <f t="shared" si="23"/>
+      <c r="U76" s="44">
+        <f t="shared" si="18"/>
         <v>0.243</v>
       </c>
-      <c r="V76" s="20">
-        <f t="shared" si="23"/>
+      <c r="V76" s="44">
+        <f t="shared" si="18"/>
         <v>0.81</v>
       </c>
-      <c r="W76" s="20" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="X76" s="20" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="Y76" s="20">
-        <f t="shared" si="23"/>
+      <c r="W76" s="44" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="X76" s="44" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="Y76" s="44">
+        <f t="shared" si="18"/>
         <v>8.50500000000002e-12</v>
       </c>
     </row>
@@ -6913,75 +6981,75 @@
       <c r="E77" s="16"/>
       <c r="F77" s="16"/>
       <c r="G77" s="16"/>
-      <c r="H77" s="24">
+      <c r="H77" s="30">
         <v>14</v>
       </c>
-      <c r="I77" s="20">
-        <f t="shared" ref="I77:Y77" si="24">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I77" s="44">
+        <f t="shared" ref="I77:Y77" si="19">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.35e-13</v>
       </c>
-      <c r="J77" s="20">
-        <f t="shared" si="24"/>
+      <c r="J77" s="44">
+        <f t="shared" si="19"/>
         <v>1.26000000000001e-12</v>
       </c>
-      <c r="K77" s="20">
-        <f t="shared" si="24"/>
+      <c r="K77" s="44">
+        <f t="shared" si="19"/>
         <v>1.17e-11</v>
       </c>
-      <c r="L77" s="20">
-        <f t="shared" si="24"/>
+      <c r="L77" s="44">
+        <f t="shared" si="19"/>
         <v>1.08e-10</v>
       </c>
-      <c r="M77" s="20">
-        <f t="shared" si="24"/>
+      <c r="M77" s="44">
+        <f t="shared" si="19"/>
         <v>9.89999999999998e-10</v>
       </c>
-      <c r="N77" s="20">
-        <f t="shared" si="24"/>
+      <c r="N77" s="44">
+        <f t="shared" si="19"/>
         <v>9e-9</v>
       </c>
-      <c r="O77" s="20">
-        <f t="shared" si="24"/>
+      <c r="O77" s="44">
+        <f t="shared" si="19"/>
         <v>8.10000000000002e-8</v>
       </c>
-      <c r="P77" s="20">
-        <f t="shared" si="24"/>
+      <c r="P77" s="44">
+        <f t="shared" si="19"/>
         <v>7.19999999999999e-7</v>
       </c>
-      <c r="Q77" s="20">
-        <f t="shared" si="24"/>
+      <c r="Q77" s="44">
+        <f t="shared" si="19"/>
         <v>6.30000000000001e-6</v>
       </c>
-      <c r="R77" s="20">
-        <f t="shared" si="24"/>
+      <c r="R77" s="44">
+        <f t="shared" si="19"/>
         <v>5.39999999999999e-5</v>
       </c>
-      <c r="S77" s="20">
-        <f t="shared" si="24"/>
+      <c r="S77" s="44">
+        <f t="shared" si="19"/>
         <v>0.000450000000000001</v>
       </c>
-      <c r="T77" s="20">
-        <f t="shared" si="24"/>
+      <c r="T77" s="44">
+        <f t="shared" si="19"/>
         <v>0.0036</v>
       </c>
-      <c r="U77" s="20">
-        <f t="shared" si="24"/>
+      <c r="U77" s="44">
+        <f t="shared" si="19"/>
         <v>0.027</v>
       </c>
-      <c r="V77" s="20">
-        <f t="shared" si="24"/>
+      <c r="V77" s="44">
+        <f t="shared" si="19"/>
         <v>0.18</v>
       </c>
-      <c r="W77" s="20">
-        <f t="shared" si="24"/>
+      <c r="W77" s="44">
+        <f t="shared" si="19"/>
         <v>0.9</v>
       </c>
-      <c r="X77" s="20" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="Y77" s="20">
-        <f t="shared" si="24"/>
+      <c r="X77" s="44" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Y77" s="44">
+        <f t="shared" si="19"/>
         <v>1.35e-13</v>
       </c>
     </row>
@@ -6993,75 +7061,75 @@
       <c r="E78" s="16"/>
       <c r="F78" s="16"/>
       <c r="G78" s="16"/>
-      <c r="H78" s="24">
+      <c r="H78" s="30">
         <v>15</v>
       </c>
-      <c r="I78" s="20">
-        <f t="shared" ref="I78:Y78" si="25">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I78" s="44">
+        <f t="shared" ref="I78:Y78" si="20">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1e-15</v>
       </c>
-      <c r="J78" s="20">
-        <f t="shared" si="25"/>
+      <c r="J78" s="44">
+        <f t="shared" si="20"/>
         <v>1.00000000000001e-14</v>
       </c>
-      <c r="K78" s="20">
-        <f t="shared" si="25"/>
+      <c r="K78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-13</v>
       </c>
-      <c r="L78" s="20">
-        <f t="shared" si="25"/>
+      <c r="L78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-12</v>
       </c>
-      <c r="M78" s="20">
-        <f t="shared" si="25"/>
+      <c r="M78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-11</v>
       </c>
-      <c r="N78" s="20">
-        <f t="shared" si="25"/>
+      <c r="N78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-10</v>
       </c>
-      <c r="O78" s="20">
-        <f t="shared" si="25"/>
+      <c r="O78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-9</v>
       </c>
-      <c r="P78" s="20">
-        <f t="shared" si="25"/>
+      <c r="P78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-8</v>
       </c>
-      <c r="Q78" s="20">
-        <f t="shared" si="25"/>
+      <c r="Q78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-7</v>
       </c>
-      <c r="R78" s="20">
-        <f t="shared" si="25"/>
+      <c r="R78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-6</v>
       </c>
-      <c r="S78" s="20">
-        <f t="shared" si="25"/>
+      <c r="S78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-5</v>
       </c>
-      <c r="T78" s="20">
-        <f t="shared" si="25"/>
+      <c r="T78" s="44">
+        <f t="shared" si="20"/>
         <v>0.0001</v>
       </c>
-      <c r="U78" s="20">
-        <f t="shared" si="25"/>
+      <c r="U78" s="44">
+        <f t="shared" si="20"/>
         <v>0.001</v>
       </c>
-      <c r="V78" s="20">
-        <f t="shared" si="25"/>
+      <c r="V78" s="44">
+        <f t="shared" si="20"/>
         <v>0.01</v>
       </c>
-      <c r="W78" s="20">
-        <f t="shared" si="25"/>
+      <c r="W78" s="44">
+        <f t="shared" si="20"/>
         <v>0.1</v>
       </c>
-      <c r="X78" s="20">
-        <f t="shared" si="25"/>
+      <c r="X78" s="44">
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
-      <c r="Y78" s="20">
-        <f t="shared" si="25"/>
+      <c r="Y78" s="44">
+        <f t="shared" si="20"/>
         <v>1e-15</v>
       </c>
     </row>
@@ -7099,16 +7167,16 @@
       <c r="D80" s="16"/>
       <c r="E80" s="16"/>
       <c r="F80" s="16"/>
-      <c r="G80" s="29" t="s">
+      <c r="G80" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="H80" s="29"/>
-      <c r="I80" s="29"/>
-      <c r="J80" s="29"/>
-      <c r="K80" s="29"/>
-      <c r="L80" s="29"/>
-      <c r="M80" s="29"/>
-      <c r="N80" s="29"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="46"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
+      <c r="L80" s="46"/>
+      <c r="M80" s="46"/>
+      <c r="N80" s="46"/>
       <c r="O80" s="16"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="16"/>
@@ -7156,22 +7224,22 @@
       <c r="E82" s="16"/>
       <c r="F82" s="16"/>
       <c r="G82" s="16"/>
-      <c r="H82" s="24" t="s">
+      <c r="H82" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="I82" s="24">
+      <c r="I82" s="30">
         <v>1</v>
       </c>
-      <c r="J82" s="24">
+      <c r="J82" s="30">
         <v>2</v>
       </c>
-      <c r="K82" s="24">
+      <c r="K82" s="30">
         <v>3</v>
       </c>
-      <c r="L82" s="24">
+      <c r="L82" s="30">
         <v>4</v>
       </c>
-      <c r="M82" s="24">
+      <c r="M82" s="30">
         <v>5</v>
       </c>
       <c r="N82" s="16"/>
@@ -7195,28 +7263,28 @@
       <c r="E83" s="16"/>
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
-      <c r="H83" s="24">
+      <c r="H83" s="30">
         <v>0</v>
       </c>
-      <c r="I83" s="30">
-        <f t="shared" ref="I83:I98" si="26">I63</f>
+      <c r="I83" s="47">
+        <f t="shared" ref="I83:I98" si="21">I63</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J83" s="20">
-        <f ca="1" t="shared" ref="J83:J98" si="27">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,J$82-2,$H83+1,1))</f>
+      <c r="J83" s="44">
+        <f ca="1" t="shared" ref="J83:J98" si="22">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,J$82-2,$H83+1,1))</f>
         <v>0.0423911582752162</v>
       </c>
-      <c r="K83" s="20">
-        <f ca="1" t="shared" ref="K83:K98" si="28">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,K$82-2,$H83+1,1))</f>
-        <v>0.00872796356808772</v>
-      </c>
-      <c r="L83" s="20">
-        <f ca="1" t="shared" ref="L83:L98" si="29">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,L$82-2,$H83+1,1))</f>
+      <c r="K83" s="44">
+        <f ca="1" t="shared" ref="K83:K98" si="23">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,K$82-2,$H83+1,1))</f>
+        <v>0.00872796356808771</v>
+      </c>
+      <c r="L83" s="44">
+        <f ca="1" t="shared" ref="L83:L98" si="24">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,L$82-2,$H83+1,1))</f>
         <v>0.00179701029991443</v>
       </c>
-      <c r="M83" s="20">
-        <f ca="1" t="shared" ref="M83:M98" si="30">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,M$82-2,$H83+1,1))</f>
-        <v>0.000369988485035128</v>
+      <c r="M83" s="44">
+        <f ca="1" t="shared" ref="M83:M98" si="25">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,M$82-2,$H83+1,1))</f>
+        <v>0.000369988485035127</v>
       </c>
       <c r="N83" s="16"/>
       <c r="O83" s="16"/>
@@ -7239,28 +7307,28 @@
       <c r="E84" s="16"/>
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
-      <c r="H84" s="24">
+      <c r="H84" s="30">
         <v>1</v>
       </c>
-      <c r="I84" s="30">
-        <f t="shared" si="26"/>
+      <c r="I84" s="47">
+        <f t="shared" si="21"/>
         <v>0.343151886824415</v>
       </c>
-      <c r="J84" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J84" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.149154075412798</v>
       </c>
-      <c r="K84" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K84" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.0486682742171146</v>
       </c>
-      <c r="L84" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L84" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.0141287572505847</v>
       </c>
-      <c r="M84" s="20">
-        <f ca="1" t="shared" si="30"/>
-        <v>0.00384885394774006</v>
+      <c r="M84" s="44">
+        <f ca="1" t="shared" si="25"/>
+        <v>0.00384885394774005</v>
       </c>
       <c r="N84" s="16"/>
       <c r="O84" s="16"/>
@@ -7283,27 +7351,27 @@
       <c r="E85" s="16"/>
       <c r="F85" s="16"/>
       <c r="G85" s="16"/>
-      <c r="H85" s="24">
+      <c r="H85" s="30">
         <v>2</v>
       </c>
-      <c r="I85" s="30">
-        <f t="shared" si="26"/>
+      <c r="I85" s="47">
+        <f t="shared" si="21"/>
         <v>0.266895911974545</v>
       </c>
-      <c r="J85" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J85" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.244907309011137</v>
       </c>
-      <c r="K85" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K85" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.126644329478555</v>
       </c>
-      <c r="L85" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L85" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.0518398983833752</v>
       </c>
-      <c r="M85" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M85" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.0186844980625806</v>
       </c>
       <c r="N85" s="16"/>
@@ -7327,28 +7395,28 @@
       <c r="E86" s="16"/>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
-      <c r="H86" s="24">
+      <c r="H86" s="30">
         <v>3</v>
       </c>
-      <c r="I86" s="30">
-        <f t="shared" si="26"/>
+      <c r="I86" s="47">
+        <f t="shared" si="21"/>
         <v>0.128505439098855</v>
       </c>
-      <c r="J86" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J86" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.248938705044242</v>
       </c>
-      <c r="K86" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K86" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.204009132488774</v>
       </c>
-      <c r="L86" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L86" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.117746600468707</v>
       </c>
-      <c r="M86" s="20">
-        <f ca="1" t="shared" si="30"/>
-        <v>0.0561507417121915</v>
+      <c r="M86" s="44">
+        <f ca="1" t="shared" si="25"/>
+        <v>0.0561507417121914</v>
       </c>
       <c r="N86" s="16"/>
       <c r="O86" s="16"/>
@@ -7371,27 +7439,27 @@
       <c r="E87" s="16"/>
       <c r="F87" s="16"/>
       <c r="G87" s="16"/>
-      <c r="H87" s="24">
+      <c r="H87" s="30">
         <v>4</v>
       </c>
-      <c r="I87" s="30">
-        <f t="shared" si="26"/>
+      <c r="I87" s="47">
+        <f t="shared" si="21"/>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J87" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J87" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.175179088734837</v>
       </c>
-      <c r="K87" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K87" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.227516357631513</v>
       </c>
-      <c r="L87" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L87" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.185153433475941</v>
       </c>
-      <c r="M87" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M87" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.116823097284761</v>
       </c>
       <c r="N87" s="16"/>
@@ -7415,27 +7483,27 @@
       <c r="E88" s="16"/>
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
-      <c r="H88" s="24">
+      <c r="H88" s="30">
         <v>5</v>
       </c>
-      <c r="I88" s="30">
-        <f t="shared" si="26"/>
+      <c r="I88" s="47">
+        <f t="shared" si="21"/>
         <v>0.010470813556203</v>
       </c>
-      <c r="J88" s="31">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J88" s="48">
+        <f ca="1" t="shared" si="22"/>
         <v>0.0904010606063728</v>
       </c>
-      <c r="K88" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K88" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.186070305102755</v>
       </c>
-      <c r="L88" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L88" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.213509197834518</v>
       </c>
-      <c r="M88" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M88" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.178239256298975</v>
       </c>
       <c r="N88" s="16"/>
@@ -7459,27 +7527,27 @@
       <c r="E89" s="16"/>
       <c r="F89" s="16"/>
       <c r="G89" s="16"/>
-      <c r="H89" s="24">
+      <c r="H89" s="30">
         <v>6</v>
       </c>
-      <c r="I89" s="20">
-        <f t="shared" si="26"/>
+      <c r="I89" s="44">
+        <f t="shared" si="21"/>
         <v>0.001939039547445</v>
       </c>
-      <c r="J89" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J89" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.0353419784263597</v>
       </c>
-      <c r="K89" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K89" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.115283613815378</v>
       </c>
-      <c r="L89" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L89" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.186520888927731</v>
       </c>
-      <c r="M89" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M89" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.206017482223783</v>
       </c>
       <c r="N89" s="16"/>
@@ -7503,27 +7571,27 @@
       <c r="E90" s="16"/>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
-      <c r="H90" s="24">
+      <c r="H90" s="30">
         <v>7</v>
       </c>
-      <c r="I90" s="20">
-        <f t="shared" si="26"/>
+      <c r="I90" s="44">
+        <f t="shared" si="21"/>
         <v>0.000277005649635</v>
       </c>
-      <c r="J90" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J90" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.0106586919063625</v>
       </c>
-      <c r="K90" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K90" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.0551002810299252</v>
       </c>
-      <c r="L90" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L90" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.125699654521354</v>
       </c>
-      <c r="M90" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M90" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.183696342337757</v>
       </c>
       <c r="N90" s="16"/>
@@ -7547,27 +7615,27 @@
       <c r="E91" s="16"/>
       <c r="F91" s="16"/>
       <c r="G91" s="16"/>
-      <c r="H91" s="24">
+      <c r="H91" s="30">
         <v>8</v>
       </c>
-      <c r="I91" s="20">
-        <f t="shared" si="26"/>
+      <c r="I91" s="44">
+        <f t="shared" si="21"/>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J91" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J91" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.00250018699038132</v>
       </c>
-      <c r="K91" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K91" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.0204830948684633</v>
       </c>
-      <c r="L91" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L91" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.0658864672914092</v>
       </c>
-      <c r="M91" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M91" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.127395026419981</v>
       </c>
       <c r="N91" s="16"/>
@@ -7591,27 +7659,27 @@
       <c r="E92" s="16"/>
       <c r="F92" s="16"/>
       <c r="G92" s="16"/>
-      <c r="H92" s="24">
+      <c r="H92" s="30">
         <v>9</v>
       </c>
-      <c r="I92" s="20">
-        <f t="shared" si="26"/>
+      <c r="I92" s="44">
+        <f t="shared" si="21"/>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J92" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J92" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>0.00045613836724378</v>
       </c>
-      <c r="K92" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K92" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.00592233363290273</v>
       </c>
-      <c r="L92" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L92" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.0268604875121694</v>
       </c>
-      <c r="M92" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M92" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.0687163318006563</v>
       </c>
       <c r="N92" s="16"/>
@@ -7635,27 +7703,27 @@
       <c r="E93" s="16"/>
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
-      <c r="H93" s="24">
+      <c r="H93" s="30">
         <v>10</v>
       </c>
-      <c r="I93" s="20">
-        <f t="shared" si="26"/>
+      <c r="I93" s="44">
+        <f t="shared" si="21"/>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J93" s="20">
-        <f ca="1" t="shared" si="27"/>
-        <v>6.41972516861616e-5</v>
-      </c>
-      <c r="K93" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="J93" s="44">
+        <f ca="1" t="shared" si="22"/>
+        <v>6.41972516861615e-5</v>
+      </c>
+      <c r="K93" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.00132094848931411</v>
       </c>
-      <c r="L93" s="20">
-        <f ca="1" t="shared" si="29"/>
-        <v>0.00844748208087341</v>
-      </c>
-      <c r="M93" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="L93" s="44">
+        <f ca="1" t="shared" si="24"/>
+        <v>0.0084474820808734</v>
+      </c>
+      <c r="M93" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.0285932276946469</v>
       </c>
       <c r="N93" s="16"/>
@@ -7679,28 +7747,28 @@
       <c r="E94" s="16"/>
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
-      <c r="H94" s="24">
+      <c r="H94" s="30">
         <v>11</v>
       </c>
-      <c r="I94" s="20">
-        <f t="shared" si="26"/>
+      <c r="I94" s="44">
+        <f t="shared" si="21"/>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J94" s="20">
-        <f ca="1" t="shared" si="27"/>
-        <v>6.84482481502284e-6</v>
-      </c>
-      <c r="K94" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="J94" s="44">
+        <f ca="1" t="shared" si="22"/>
+        <v>6.84482481502283e-6</v>
+      </c>
+      <c r="K94" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>0.000223205537226664</v>
       </c>
-      <c r="L94" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L94" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.00201264295050115</v>
       </c>
-      <c r="M94" s="20">
-        <f ca="1" t="shared" si="30"/>
-        <v>0.0090134793085826</v>
+      <c r="M94" s="44">
+        <f ca="1" t="shared" si="25"/>
+        <v>0.00901347930858259</v>
       </c>
       <c r="N94" s="16"/>
       <c r="O94" s="16"/>
@@ -7723,27 +7791,27 @@
       <c r="E95" s="16"/>
       <c r="F95" s="16"/>
       <c r="G95" s="16"/>
-      <c r="H95" s="24">
+      <c r="H95" s="30">
         <v>12</v>
       </c>
-      <c r="I95" s="20">
-        <f t="shared" si="26"/>
+      <c r="I95" s="44">
+        <f t="shared" si="21"/>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J95" s="20">
-        <f ca="1" t="shared" si="27"/>
-        <v>5.35192063726066e-7</v>
-      </c>
-      <c r="K95" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="J95" s="44">
+        <f ca="1" t="shared" si="22"/>
+        <v>5.35192063726065e-7</v>
+      </c>
+      <c r="K95" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>2.76582993088367e-5</v>
       </c>
-      <c r="L95" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L95" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>0.000351647569312272</v>
       </c>
-      <c r="M95" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M95" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.00208364234881633</v>
       </c>
       <c r="N95" s="16"/>
@@ -7767,27 +7835,27 @@
       <c r="E96" s="16"/>
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
-      <c r="H96" s="24">
+      <c r="H96" s="30">
         <v>13</v>
       </c>
-      <c r="I96" s="20">
-        <f t="shared" si="26"/>
+      <c r="I96" s="44">
+        <f t="shared" si="21"/>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J96" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J96" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>2.89705105720662e-8</v>
       </c>
-      <c r="K96" s="20">
-        <f ca="1" t="shared" si="28"/>
-        <v>2.37271260294231e-6</v>
-      </c>
-      <c r="L96" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="K96" s="44">
+        <f ca="1" t="shared" si="23"/>
+        <v>2.3727126029423e-6</v>
+      </c>
+      <c r="L96" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>4.25351197940594e-5</v>
       </c>
-      <c r="M96" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M96" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>0.000333467138086273</v>
       </c>
       <c r="N96" s="16"/>
@@ -7811,27 +7879,27 @@
       <c r="E97" s="16"/>
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
-      <c r="H97" s="24">
+      <c r="H97" s="30">
         <v>14</v>
       </c>
-      <c r="I97" s="20">
-        <f t="shared" si="26"/>
+      <c r="I97" s="44">
+        <f t="shared" si="21"/>
         <v>1.35e-13</v>
       </c>
-      <c r="J97" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J97" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>9.70793123226205e-10</v>
       </c>
-      <c r="K97" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K97" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>1.26005313618923e-7</v>
       </c>
-      <c r="L97" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L97" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>3.18501702640648e-6</v>
       </c>
-      <c r="M97" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M97" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>3.30374840550607e-5</v>
       </c>
       <c r="N97" s="16"/>
@@ -7855,27 +7923,27 @@
       <c r="E98" s="16"/>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
-      <c r="H98" s="24">
+      <c r="H98" s="30">
         <v>15</v>
       </c>
-      <c r="I98" s="20">
-        <f t="shared" si="26"/>
+      <c r="I98" s="44">
+        <f t="shared" si="21"/>
         <v>1e-15</v>
       </c>
-      <c r="J98" s="20">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J98" s="44">
+        <f ca="1" t="shared" si="22"/>
         <v>1.51811270298748e-11</v>
       </c>
-      <c r="K98" s="20">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K98" s="44">
+        <f ca="1" t="shared" si="23"/>
         <v>3.12276543125086e-9</v>
       </c>
-      <c r="L98" s="20">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L98" s="44">
+        <f ca="1" t="shared" si="24"/>
         <v>1.11296789654137e-7</v>
       </c>
-      <c r="M98" s="20">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M98" s="44">
+        <f ca="1" t="shared" si="25"/>
         <v>1.52745235260974e-6</v>
       </c>
       <c r="N98" s="16"/>
@@ -7899,26 +7967,26 @@
       <c r="E99" s="16"/>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
-      <c r="H99" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="I99" s="20">
+      <c r="H99" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="I99" s="44">
         <f>SUM(I83:I98)</f>
         <v>1</v>
       </c>
-      <c r="J99" s="20">
+      <c r="J99" s="44">
         <f ca="1">SUM(J83:J98)</f>
         <v>1</v>
       </c>
-      <c r="K99" s="20">
+      <c r="K99" s="44">
         <f ca="1">SUM(K83:K98)</f>
         <v>1</v>
       </c>
-      <c r="L99" s="20">
+      <c r="L99" s="44">
         <f ca="1">SUM(L83:L98)</f>
         <v>1</v>
       </c>
-      <c r="M99" s="20">
+      <c r="M99" s="44">
         <f ca="1">SUM(M83:M98)</f>
         <v>1</v>
       </c>
@@ -7963,10 +8031,10 @@
       <c r="Y100" s="16"/>
     </row>
     <row r="101" ht="60" customHeight="1" spans="1:25">
-      <c r="A101" s="32" t="s">
+      <c r="A101" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="B101" s="20">
+      <c r="B101" s="44">
         <f ca="1">SUM(M88:M98)</f>
         <v>0.804122820507692</v>
       </c>
@@ -7995,11 +8063,13 @@
       <c r="Y101" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="16">
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A26:C26"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="H28:M28"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A56:F56"/>
@@ -8008,12 +8078,14 @@
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="G60:N60"/>
     <mergeCell ref="G80:N80"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="G6:G23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Y101" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A36:Y101 A1:Y3 A4:F4 H4:Y4 A5:Y5 A6:F6 H6:Y6 A7 C7:Y7 A8:Y22 A23 C23:Y23 A24:Y27 A28:G34 A35:C35 E35:G35 S28:Y35" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/游戏设计王/老虎机数学专题-二项分配机率.xlsx
+++ b/游戏设计王/老虎机数学专题-二项分配机率.xlsx
@@ -1386,7 +1386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1461,9 +1461,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1491,25 +1488,29 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2154,44 +2155,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A3" s="52"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:10">
       <c r="A4" s="29" t="s">
@@ -2199,56 +2200,56 @@
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A5" s="52"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="54" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2259,64 +2260,64 @@
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A10" s="52"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A13" s="52"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:10">
       <c r="A14" s="29" t="s">
@@ -2327,1210 +2328,1210 @@
       <c r="D14" s="29"/>
       <c r="E14" s="29"/>
       <c r="F14" s="29"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A15" s="52"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:10">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="55"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="18" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A18" s="56"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A19" s="57" t="s">
+      <c r="A19" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
     </row>
     <row r="22" ht="33" customHeight="1" spans="1:10">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
     </row>
     <row r="24" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A24" s="56"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="55"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
+      <c r="A24" s="59"/>
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="55"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="55"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="55"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A28" s="60" t="s">
+      <c r="A28" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="55"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="60" t="s">
+      <c r="A29" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="55"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="55"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:10">
-      <c r="A30" s="61" t="s">
+      <c r="A30" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="64" t="s">
+      <c r="B31" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="64"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="55"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="58"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A32" s="63" t="s">
+      <c r="A32" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="64" t="s">
+      <c r="B32" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="64"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="55"/>
-      <c r="J32" s="55"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="67"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="64" t="s">
+      <c r="B33" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="55"/>
-      <c r="J33" s="55"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A34" s="63" t="s">
+      <c r="A34" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="55"/>
-      <c r="J34" s="55"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
     </row>
     <row r="35" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A35" s="56"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="55"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="55"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A36" s="59" t="s">
+      <c r="A36" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
     </row>
     <row r="37" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A37" s="56"/>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="60" t="s">
+      <c r="A38" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:10">
-      <c r="A39" s="61" t="s">
+      <c r="A39" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="62" t="s">
+      <c r="B39" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="62" t="s">
+      <c r="D39" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="62" t="s">
+      <c r="E39" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="62" t="s">
+      <c r="F39" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A40" s="63" t="s">
+      <c r="A40" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="65">
+      <c r="B40" s="68">
         <v>0.1</v>
       </c>
-      <c r="C40" s="65">
+      <c r="C40" s="68">
         <v>0.15</v>
       </c>
-      <c r="D40" s="65">
+      <c r="D40" s="68">
         <v>0.2</v>
       </c>
-      <c r="E40" s="65">
+      <c r="E40" s="68">
         <v>0.25</v>
       </c>
-      <c r="F40" s="65">
+      <c r="F40" s="68">
         <v>0.3</v>
       </c>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
     </row>
     <row r="41" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A41" s="56"/>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
+      <c r="A41" s="59"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="60" t="s">
+      <c r="A42" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
-      <c r="J42" s="55"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A43" s="59" t="s">
+      <c r="A43" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="55"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="58"/>
     </row>
     <row r="44" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A44" s="56"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="55"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="58"/>
     </row>
     <row r="45" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="58" t="s">
+      <c r="A45" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="55"/>
+      <c r="B45" s="61"/>
+      <c r="C45" s="61"/>
+      <c r="D45" s="61"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="60" t="s">
+      <c r="A46" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="55"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-      <c r="J46" s="55"/>
+      <c r="B46" s="58"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="58"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="63" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="55"/>
-      <c r="C47" s="55"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="55"/>
-      <c r="H47" s="55"/>
-      <c r="I47" s="55"/>
-      <c r="J47" s="55"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="58"/>
     </row>
     <row r="48" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A48" s="66" t="s">
+      <c r="A48" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="66"/>
-      <c r="I48" s="66"/>
-      <c r="J48" s="66"/>
+      <c r="B48" s="69"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A49" s="59" t="s">
+      <c r="A49" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="55"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="55"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="58"/>
+      <c r="I49" s="58"/>
+      <c r="J49" s="58"/>
     </row>
     <row r="50" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A50" s="56"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="55"/>
-      <c r="D50" s="55"/>
-      <c r="E50" s="55"/>
-      <c r="F50" s="55"/>
-      <c r="G50" s="55"/>
-      <c r="H50" s="55"/>
-      <c r="I50" s="55"/>
-      <c r="J50" s="55"/>
+      <c r="A50" s="59"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
+      <c r="J50" s="58"/>
     </row>
     <row r="51" ht="33" customHeight="1" spans="1:10">
-      <c r="A51" s="58" t="s">
+      <c r="A51" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="55"/>
-      <c r="G51" s="55"/>
-      <c r="H51" s="55"/>
-      <c r="I51" s="55"/>
-      <c r="J51" s="55"/>
+      <c r="B51" s="61"/>
+      <c r="C51" s="61"/>
+      <c r="D51" s="61"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
+      <c r="J51" s="58"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="55"/>
-      <c r="H52" s="55"/>
-      <c r="I52" s="55"/>
-      <c r="J52" s="55"/>
+      <c r="B52" s="58"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="58"/>
+      <c r="J52" s="58"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A53" s="60" t="s">
+      <c r="A53" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="55"/>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
-      <c r="F53" s="55"/>
-      <c r="G53" s="55"/>
-      <c r="H53" s="55"/>
-      <c r="I53" s="55"/>
-      <c r="J53" s="55"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="58"/>
+      <c r="I53" s="58"/>
+      <c r="J53" s="58"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A54" s="60" t="s">
+      <c r="A54" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="55"/>
-      <c r="C54" s="55"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="55"/>
-      <c r="H54" s="55"/>
-      <c r="I54" s="55"/>
-      <c r="J54" s="55"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="58"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A55" s="60" t="s">
+      <c r="A55" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="55"/>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="55"/>
-      <c r="G55" s="55"/>
-      <c r="H55" s="55"/>
-      <c r="I55" s="55"/>
-      <c r="J55" s="55"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="58"/>
+      <c r="H55" s="58"/>
+      <c r="I55" s="58"/>
+      <c r="J55" s="58"/>
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A56" s="59" t="s">
+      <c r="A56" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="55"/>
-      <c r="C56" s="55"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="55"/>
-      <c r="F56" s="55"/>
-      <c r="G56" s="55"/>
-      <c r="H56" s="55"/>
-      <c r="I56" s="55"/>
-      <c r="J56" s="55"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
+      <c r="H56" s="58"/>
+      <c r="I56" s="58"/>
+      <c r="J56" s="58"/>
     </row>
     <row r="57" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A57" s="56"/>
-      <c r="B57" s="55"/>
-      <c r="C57" s="55"/>
-      <c r="D57" s="55"/>
-      <c r="E57" s="55"/>
-      <c r="F57" s="55"/>
-      <c r="G57" s="55"/>
-      <c r="H57" s="55"/>
-      <c r="I57" s="55"/>
-      <c r="J57" s="55"/>
+      <c r="A57" s="59"/>
+      <c r="B57" s="58"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="58"/>
+      <c r="G57" s="58"/>
+      <c r="H57" s="58"/>
+      <c r="I57" s="58"/>
+      <c r="J57" s="58"/>
     </row>
     <row r="58" ht="33" customHeight="1" spans="1:10">
-      <c r="A58" s="58" t="s">
+      <c r="A58" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="55"/>
-      <c r="G58" s="55"/>
-      <c r="H58" s="55"/>
-      <c r="I58" s="55"/>
-      <c r="J58" s="55"/>
+      <c r="B58" s="61"/>
+      <c r="C58" s="61"/>
+      <c r="D58" s="61"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+      <c r="H58" s="58"/>
+      <c r="I58" s="58"/>
+      <c r="J58" s="58"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A59" s="60" t="s">
+      <c r="A59" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="55"/>
-      <c r="C59" s="55"/>
-      <c r="D59" s="55"/>
-      <c r="E59" s="55"/>
-      <c r="F59" s="55"/>
-      <c r="G59" s="55"/>
-      <c r="H59" s="55"/>
-      <c r="I59" s="55"/>
-      <c r="J59" s="55"/>
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="58"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="58"/>
+      <c r="J59" s="58"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A60" s="58" t="s">
+      <c r="A60" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="55"/>
-      <c r="E60" s="55"/>
-      <c r="F60" s="55"/>
-      <c r="G60" s="55"/>
-      <c r="H60" s="55"/>
-      <c r="I60" s="55"/>
-      <c r="J60" s="55"/>
+      <c r="B60" s="61"/>
+      <c r="C60" s="61"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A61" s="60" t="s">
+      <c r="A61" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="55"/>
-      <c r="C61" s="55"/>
-      <c r="D61" s="55"/>
-      <c r="E61" s="55"/>
-      <c r="F61" s="55"/>
-      <c r="G61" s="55"/>
-      <c r="H61" s="55"/>
-      <c r="I61" s="55"/>
-      <c r="J61" s="55"/>
+      <c r="B61" s="58"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="58"/>
+      <c r="I61" s="58"/>
+      <c r="J61" s="58"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A62" s="60" t="s">
+      <c r="A62" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="B62" s="55"/>
-      <c r="C62" s="55"/>
-      <c r="D62" s="55"/>
-      <c r="E62" s="55"/>
-      <c r="F62" s="55"/>
-      <c r="G62" s="55"/>
-      <c r="H62" s="55"/>
-      <c r="I62" s="55"/>
-      <c r="J62" s="55"/>
+      <c r="B62" s="58"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="58"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A63" s="60" t="s">
+      <c r="A63" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="55"/>
-      <c r="C63" s="55"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="55"/>
-      <c r="F63" s="55"/>
-      <c r="G63" s="55"/>
-      <c r="H63" s="55"/>
-      <c r="I63" s="55"/>
-      <c r="J63" s="55"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="58"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A64" s="60" t="s">
+      <c r="A64" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B64" s="55"/>
-      <c r="C64" s="55"/>
-      <c r="D64" s="55"/>
-      <c r="E64" s="55"/>
-      <c r="F64" s="55"/>
-      <c r="G64" s="55"/>
-      <c r="H64" s="55"/>
-      <c r="I64" s="55"/>
-      <c r="J64" s="55"/>
+      <c r="B64" s="58"/>
+      <c r="C64" s="58"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="58"/>
+      <c r="G64" s="58"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="58"/>
+      <c r="J64" s="58"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A65" s="60" t="s">
+      <c r="A65" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B65" s="55"/>
-      <c r="C65" s="55"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="55"/>
-      <c r="G65" s="55"/>
-      <c r="H65" s="55"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="55"/>
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
+      <c r="J65" s="58"/>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:22">
-      <c r="A66" s="67" t="s">
+      <c r="A66" s="70" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A67" s="60" t="s">
+      <c r="A67" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="B67" s="55"/>
-      <c r="C67" s="55"/>
-      <c r="D67" s="55"/>
-      <c r="E67" s="55"/>
-      <c r="F67" s="55"/>
-      <c r="G67" s="55"/>
-      <c r="H67" s="55"/>
-      <c r="I67" s="55"/>
-      <c r="J67" s="55"/>
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="58"/>
+      <c r="J67" s="58"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A68" s="60" t="s">
+      <c r="A68" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="B68" s="55"/>
-      <c r="C68" s="55"/>
-      <c r="D68" s="55"/>
-      <c r="E68" s="55"/>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-      <c r="J68" s="55"/>
+      <c r="B68" s="58"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="58"/>
+      <c r="J68" s="58"/>
     </row>
     <row r="69" ht="33" customHeight="1" spans="1:22">
-      <c r="A69" s="58" t="s">
+      <c r="A69" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="55"/>
-      <c r="H69" s="55"/>
-      <c r="I69" s="55"/>
-      <c r="J69" s="55"/>
+      <c r="B69" s="61"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="61"/>
+      <c r="G69" s="58"/>
+      <c r="H69" s="58"/>
+      <c r="I69" s="58"/>
+      <c r="J69" s="58"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A70" s="60" t="s">
+      <c r="A70" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="55"/>
-      <c r="C70" s="55"/>
-      <c r="D70" s="55"/>
-      <c r="E70" s="55"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="55"/>
-      <c r="H70" s="55"/>
-      <c r="I70" s="55"/>
-      <c r="J70" s="55"/>
+      <c r="B70" s="58"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="58"/>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:22">
-      <c r="A71" s="68" t="s">
+      <c r="A71" s="71" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A72" s="59" t="s">
+      <c r="A72" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="55"/>
-      <c r="C72" s="55"/>
-      <c r="D72" s="55"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="55"/>
-      <c r="G72" s="55"/>
-      <c r="H72" s="55"/>
-      <c r="I72" s="55"/>
-      <c r="J72" s="55"/>
+      <c r="B72" s="58"/>
+      <c r="C72" s="58"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="58"/>
+      <c r="F72" s="58"/>
+      <c r="G72" s="58"/>
+      <c r="H72" s="58"/>
+      <c r="I72" s="58"/>
+      <c r="J72" s="58"/>
     </row>
     <row r="73" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A73" s="56"/>
-      <c r="B73" s="55"/>
-      <c r="C73" s="55"/>
-      <c r="D73" s="55"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="55"/>
-      <c r="G73" s="55"/>
-      <c r="H73" s="55"/>
-      <c r="I73" s="55"/>
-      <c r="J73" s="55"/>
+      <c r="A73" s="59"/>
+      <c r="B73" s="58"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="58"/>
+      <c r="E73" s="58"/>
+      <c r="F73" s="58"/>
+      <c r="G73" s="58"/>
+      <c r="H73" s="58"/>
+      <c r="I73" s="58"/>
+      <c r="J73" s="58"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A74" s="60" t="s">
+      <c r="A74" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="55"/>
-      <c r="C74" s="55"/>
-      <c r="D74" s="55"/>
-      <c r="E74" s="55"/>
-      <c r="F74" s="55"/>
-      <c r="G74" s="55"/>
-      <c r="H74" s="55"/>
-      <c r="I74" s="55"/>
-      <c r="J74" s="55"/>
+      <c r="B74" s="58"/>
+      <c r="C74" s="58"/>
+      <c r="D74" s="58"/>
+      <c r="E74" s="58"/>
+      <c r="F74" s="58"/>
+      <c r="G74" s="58"/>
+      <c r="H74" s="58"/>
+      <c r="I74" s="58"/>
+      <c r="J74" s="58"/>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:22">
-      <c r="A75" s="61" t="s">
+      <c r="A75" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="62" t="s">
+      <c r="B75" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="55"/>
-      <c r="D75" s="55"/>
-      <c r="E75" s="55"/>
-      <c r="F75" s="55"/>
-      <c r="G75" s="55"/>
-      <c r="H75" s="55"/>
-      <c r="I75" s="55"/>
-      <c r="J75" s="55"/>
+      <c r="C75" s="58"/>
+      <c r="D75" s="58"/>
+      <c r="E75" s="58"/>
+      <c r="F75" s="58"/>
+      <c r="G75" s="58"/>
+      <c r="H75" s="58"/>
+      <c r="I75" s="58"/>
+      <c r="J75" s="58"/>
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:22">
-      <c r="A76" s="63" t="s">
+      <c r="A76" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="B76" s="64" t="s">
+      <c r="B76" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="C76" s="64"/>
-      <c r="D76" s="55"/>
-      <c r="E76" s="55"/>
-      <c r="F76" s="55"/>
-      <c r="G76" s="55"/>
-      <c r="H76" s="55"/>
-      <c r="I76" s="55"/>
-      <c r="J76" s="55"/>
+      <c r="C76" s="67"/>
+      <c r="D76" s="58"/>
+      <c r="E76" s="58"/>
+      <c r="F76" s="58"/>
+      <c r="G76" s="58"/>
+      <c r="H76" s="58"/>
+      <c r="I76" s="58"/>
+      <c r="J76" s="58"/>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:22">
-      <c r="A77" s="63" t="s">
+      <c r="A77" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="69" t="s">
+      <c r="B77" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="69"/>
-      <c r="D77" s="69"/>
-      <c r="E77" s="69"/>
-      <c r="F77" s="69"/>
-      <c r="G77" s="69"/>
-      <c r="H77" s="69"/>
-      <c r="I77" s="69"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="69"/>
-      <c r="L77" s="69"/>
-      <c r="M77" s="69"/>
-      <c r="N77" s="69"/>
-      <c r="O77" s="69"/>
-      <c r="P77" s="69"/>
-      <c r="Q77" s="69"/>
-      <c r="R77" s="69"/>
-      <c r="S77" s="69"/>
-      <c r="T77" s="69"/>
-      <c r="U77" s="69"/>
-      <c r="V77" s="69"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="72"/>
+      <c r="E77" s="72"/>
+      <c r="F77" s="72"/>
+      <c r="G77" s="72"/>
+      <c r="H77" s="72"/>
+      <c r="I77" s="72"/>
+      <c r="J77" s="72"/>
+      <c r="K77" s="72"/>
+      <c r="L77" s="72"/>
+      <c r="M77" s="72"/>
+      <c r="N77" s="72"/>
+      <c r="O77" s="72"/>
+      <c r="P77" s="72"/>
+      <c r="Q77" s="72"/>
+      <c r="R77" s="72"/>
+      <c r="S77" s="72"/>
+      <c r="T77" s="72"/>
+      <c r="U77" s="72"/>
+      <c r="V77" s="72"/>
     </row>
     <row r="78" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A78" s="56"/>
-      <c r="B78" s="55"/>
-      <c r="C78" s="55"/>
-      <c r="D78" s="55"/>
-      <c r="E78" s="55"/>
-      <c r="F78" s="55"/>
-      <c r="G78" s="55"/>
-      <c r="H78" s="55"/>
-      <c r="I78" s="55"/>
-      <c r="J78" s="55"/>
+      <c r="A78" s="59"/>
+      <c r="B78" s="58"/>
+      <c r="C78" s="58"/>
+      <c r="D78" s="58"/>
+      <c r="E78" s="58"/>
+      <c r="F78" s="58"/>
+      <c r="G78" s="58"/>
+      <c r="H78" s="58"/>
+      <c r="I78" s="58"/>
+      <c r="J78" s="58"/>
     </row>
     <row r="79" ht="33" customHeight="1" spans="1:22">
-      <c r="A79" s="58" t="s">
+      <c r="A79" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="58"/>
-      <c r="C79" s="58"/>
-      <c r="D79" s="58"/>
-      <c r="E79" s="58"/>
-      <c r="F79" s="55"/>
-      <c r="G79" s="55"/>
-      <c r="H79" s="55"/>
-      <c r="I79" s="55"/>
-      <c r="J79" s="55"/>
+      <c r="B79" s="61"/>
+      <c r="C79" s="61"/>
+      <c r="D79" s="61"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="58"/>
+      <c r="G79" s="58"/>
+      <c r="H79" s="58"/>
+      <c r="I79" s="58"/>
+      <c r="J79" s="58"/>
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A80" s="59" t="s">
+      <c r="A80" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="55"/>
-      <c r="C80" s="55"/>
-      <c r="D80" s="55"/>
-      <c r="E80" s="55"/>
-      <c r="F80" s="55"/>
-      <c r="G80" s="55"/>
-      <c r="H80" s="55"/>
-      <c r="I80" s="55"/>
-      <c r="J80" s="55"/>
+      <c r="B80" s="58"/>
+      <c r="C80" s="58"/>
+      <c r="D80" s="58"/>
+      <c r="E80" s="58"/>
+      <c r="F80" s="58"/>
+      <c r="G80" s="58"/>
+      <c r="H80" s="58"/>
+      <c r="I80" s="58"/>
+      <c r="J80" s="58"/>
     </row>
     <row r="81" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A81" s="56"/>
-      <c r="B81" s="55"/>
-      <c r="C81" s="55"/>
-      <c r="D81" s="55"/>
-      <c r="E81" s="55"/>
-      <c r="F81" s="55"/>
-      <c r="G81" s="55"/>
-      <c r="H81" s="55"/>
-      <c r="I81" s="55"/>
-      <c r="J81" s="55"/>
+      <c r="A81" s="59"/>
+      <c r="B81" s="58"/>
+      <c r="C81" s="58"/>
+      <c r="D81" s="58"/>
+      <c r="E81" s="58"/>
+      <c r="F81" s="58"/>
+      <c r="G81" s="58"/>
+      <c r="H81" s="58"/>
+      <c r="I81" s="58"/>
+      <c r="J81" s="58"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A82" s="60" t="s">
+      <c r="A82" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="55"/>
-      <c r="C82" s="55"/>
-      <c r="D82" s="55"/>
-      <c r="E82" s="55"/>
-      <c r="F82" s="55"/>
-      <c r="G82" s="55"/>
-      <c r="H82" s="55"/>
-      <c r="I82" s="55"/>
-      <c r="J82" s="55"/>
+      <c r="B82" s="58"/>
+      <c r="C82" s="58"/>
+      <c r="D82" s="58"/>
+      <c r="E82" s="58"/>
+      <c r="F82" s="58"/>
+      <c r="G82" s="58"/>
+      <c r="H82" s="58"/>
+      <c r="I82" s="58"/>
+      <c r="J82" s="58"/>
     </row>
     <row r="83" ht="33" customHeight="1" spans="1:10">
-      <c r="A83" s="58" t="s">
+      <c r="A83" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="B83" s="58"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="55"/>
-      <c r="F83" s="55"/>
-      <c r="G83" s="55"/>
-      <c r="H83" s="55"/>
-      <c r="I83" s="55"/>
-      <c r="J83" s="55"/>
+      <c r="B83" s="61"/>
+      <c r="C83" s="61"/>
+      <c r="D83" s="61"/>
+      <c r="E83" s="58"/>
+      <c r="F83" s="58"/>
+      <c r="G83" s="58"/>
+      <c r="H83" s="58"/>
+      <c r="I83" s="58"/>
+      <c r="J83" s="58"/>
     </row>
     <row r="84" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A84" s="58" t="s">
+      <c r="A84" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="B84" s="58"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
-      <c r="E84" s="58"/>
-      <c r="F84" s="58"/>
-      <c r="G84" s="58"/>
-      <c r="H84" s="58"/>
-      <c r="I84" s="58"/>
-      <c r="J84" s="55"/>
+      <c r="B84" s="61"/>
+      <c r="C84" s="61"/>
+      <c r="D84" s="61"/>
+      <c r="E84" s="61"/>
+      <c r="F84" s="61"/>
+      <c r="G84" s="61"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="61"/>
+      <c r="J84" s="58"/>
     </row>
     <row r="85" ht="33" customHeight="1" spans="1:10">
-      <c r="A85" s="58" t="s">
+      <c r="A85" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="B85" s="58"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="55"/>
-      <c r="I85" s="55"/>
-      <c r="J85" s="55"/>
+      <c r="B85" s="61"/>
+      <c r="C85" s="61"/>
+      <c r="D85" s="61"/>
+      <c r="E85" s="61"/>
+      <c r="F85" s="61"/>
+      <c r="G85" s="61"/>
+      <c r="H85" s="58"/>
+      <c r="I85" s="58"/>
+      <c r="J85" s="58"/>
     </row>
     <row r="86" ht="33" customHeight="1" spans="1:10">
-      <c r="A86" s="58" t="s">
+      <c r="A86" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="B86" s="58"/>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="55"/>
-      <c r="F86" s="55"/>
-      <c r="G86" s="55"/>
-      <c r="H86" s="55"/>
-      <c r="I86" s="55"/>
-      <c r="J86" s="55"/>
+      <c r="B86" s="61"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="58"/>
+      <c r="F86" s="58"/>
+      <c r="G86" s="58"/>
+      <c r="H86" s="58"/>
+      <c r="I86" s="58"/>
+      <c r="J86" s="58"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A87" s="59" t="s">
+      <c r="A87" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="B87" s="55"/>
-      <c r="C87" s="55"/>
-      <c r="D87" s="55"/>
-      <c r="E87" s="55"/>
-      <c r="F87" s="55"/>
-      <c r="G87" s="55"/>
-      <c r="H87" s="55"/>
-      <c r="I87" s="55"/>
-      <c r="J87" s="55"/>
+      <c r="B87" s="58"/>
+      <c r="C87" s="58"/>
+      <c r="D87" s="58"/>
+      <c r="E87" s="58"/>
+      <c r="F87" s="58"/>
+      <c r="G87" s="58"/>
+      <c r="H87" s="58"/>
+      <c r="I87" s="58"/>
+      <c r="J87" s="58"/>
     </row>
     <row r="88" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A88" s="56"/>
-      <c r="B88" s="55"/>
-      <c r="C88" s="55"/>
-      <c r="D88" s="55"/>
-      <c r="E88" s="55"/>
-      <c r="F88" s="55"/>
-      <c r="G88" s="55"/>
-      <c r="H88" s="55"/>
-      <c r="I88" s="55"/>
-      <c r="J88" s="55"/>
+      <c r="A88" s="59"/>
+      <c r="B88" s="58"/>
+      <c r="C88" s="58"/>
+      <c r="D88" s="58"/>
+      <c r="E88" s="58"/>
+      <c r="F88" s="58"/>
+      <c r="G88" s="58"/>
+      <c r="H88" s="58"/>
+      <c r="I88" s="58"/>
+      <c r="J88" s="58"/>
     </row>
     <row r="89" ht="18" customHeight="1" spans="1:10">
-      <c r="A89" s="61" t="s">
+      <c r="A89" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="62" t="s">
+      <c r="B89" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="C89" s="55"/>
-      <c r="D89" s="55"/>
-      <c r="E89" s="55"/>
-      <c r="F89" s="55"/>
-      <c r="G89" s="55"/>
-      <c r="H89" s="55"/>
-      <c r="I89" s="55"/>
-      <c r="J89" s="55"/>
+      <c r="C89" s="58"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="58"/>
+      <c r="F89" s="58"/>
+      <c r="G89" s="58"/>
+      <c r="H89" s="58"/>
+      <c r="I89" s="58"/>
+      <c r="J89" s="58"/>
     </row>
     <row r="90" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A90" s="63" t="s">
+      <c r="A90" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="70" t="s">
+      <c r="B90" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="C90" s="55"/>
-      <c r="D90" s="55"/>
-      <c r="E90" s="55"/>
-      <c r="F90" s="55"/>
-      <c r="G90" s="55"/>
-      <c r="H90" s="55"/>
-      <c r="I90" s="55"/>
-      <c r="J90" s="55"/>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
+      <c r="E90" s="58"/>
+      <c r="F90" s="58"/>
+      <c r="G90" s="58"/>
+      <c r="H90" s="58"/>
+      <c r="I90" s="58"/>
+      <c r="J90" s="58"/>
     </row>
     <row r="91" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A91" s="63" t="s">
+      <c r="A91" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="B91" s="64" t="s">
+      <c r="B91" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="C91" s="64"/>
-      <c r="D91" s="55"/>
-      <c r="E91" s="55"/>
-      <c r="F91" s="55"/>
-      <c r="G91" s="55"/>
-      <c r="H91" s="55"/>
-      <c r="I91" s="55"/>
-      <c r="J91" s="55"/>
+      <c r="C91" s="67"/>
+      <c r="D91" s="58"/>
+      <c r="E91" s="58"/>
+      <c r="F91" s="58"/>
+      <c r="G91" s="58"/>
+      <c r="H91" s="58"/>
+      <c r="I91" s="58"/>
+      <c r="J91" s="58"/>
     </row>
     <row r="92" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A92" s="63" t="s">
+      <c r="A92" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="64" t="s">
+      <c r="B92" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="64"/>
-      <c r="D92" s="55"/>
-      <c r="E92" s="55"/>
-      <c r="F92" s="55"/>
-      <c r="G92" s="55"/>
-      <c r="H92" s="55"/>
-      <c r="I92" s="55"/>
-      <c r="J92" s="55"/>
+      <c r="C92" s="67"/>
+      <c r="D92" s="58"/>
+      <c r="E92" s="58"/>
+      <c r="F92" s="58"/>
+      <c r="G92" s="58"/>
+      <c r="H92" s="58"/>
+      <c r="I92" s="58"/>
+      <c r="J92" s="58"/>
     </row>
     <row r="93" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A93" s="63" t="s">
+      <c r="A93" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="B93" s="64" t="s">
+      <c r="B93" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="64"/>
-      <c r="D93" s="55"/>
-      <c r="E93" s="55"/>
-      <c r="F93" s="55"/>
-      <c r="G93" s="55"/>
-      <c r="H93" s="55"/>
-      <c r="I93" s="55"/>
-      <c r="J93" s="55"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="58"/>
+      <c r="E93" s="58"/>
+      <c r="F93" s="58"/>
+      <c r="G93" s="58"/>
+      <c r="H93" s="58"/>
+      <c r="I93" s="58"/>
+      <c r="J93" s="58"/>
     </row>
     <row r="94" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A94" s="63" t="s">
+      <c r="A94" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="64" t="s">
+      <c r="B94" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="64"/>
-      <c r="D94" s="55"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="55"/>
-      <c r="I94" s="55"/>
-      <c r="J94" s="55"/>
+      <c r="C94" s="67"/>
+      <c r="D94" s="58"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="58"/>
+      <c r="G94" s="58"/>
+      <c r="H94" s="58"/>
+      <c r="I94" s="58"/>
+      <c r="J94" s="58"/>
     </row>
     <row r="95" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A95" s="63" t="s">
+      <c r="A95" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="64" t="s">
+      <c r="B95" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="64"/>
-      <c r="D95" s="55"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="55"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="55"/>
-      <c r="I95" s="55"/>
-      <c r="J95" s="55"/>
+      <c r="C95" s="67"/>
+      <c r="D95" s="58"/>
+      <c r="E95" s="58"/>
+      <c r="F95" s="58"/>
+      <c r="G95" s="58"/>
+      <c r="H95" s="58"/>
+      <c r="I95" s="58"/>
+      <c r="J95" s="58"/>
     </row>
     <row r="96" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A96" s="63" t="s">
+      <c r="A96" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="64" t="s">
+      <c r="B96" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="64"/>
-      <c r="D96" s="55"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="55"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="55"/>
-      <c r="I96" s="55"/>
-      <c r="J96" s="55"/>
+      <c r="C96" s="67"/>
+      <c r="D96" s="58"/>
+      <c r="E96" s="58"/>
+      <c r="F96" s="58"/>
+      <c r="G96" s="58"/>
+      <c r="H96" s="58"/>
+      <c r="I96" s="58"/>
+      <c r="J96" s="58"/>
     </row>
     <row r="97" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A97" s="63" t="s">
+      <c r="A97" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="B97" s="64" t="s">
+      <c r="B97" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="C97" s="64"/>
-      <c r="D97" s="55"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="55"/>
-      <c r="G97" s="55"/>
-      <c r="H97" s="55"/>
-      <c r="I97" s="55"/>
-      <c r="J97" s="55"/>
+      <c r="C97" s="67"/>
+      <c r="D97" s="58"/>
+      <c r="E97" s="58"/>
+      <c r="F97" s="58"/>
+      <c r="G97" s="58"/>
+      <c r="H97" s="58"/>
+      <c r="I97" s="58"/>
+      <c r="J97" s="58"/>
     </row>
     <row r="98" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A98" s="63" t="s">
+      <c r="A98" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="64" t="s">
+      <c r="B98" s="67" t="s">
         <v>101</v>
       </c>
-      <c r="C98" s="64"/>
-      <c r="D98" s="55"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="55"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="55"/>
-      <c r="I98" s="55"/>
-      <c r="J98" s="55"/>
+      <c r="C98" s="67"/>
+      <c r="D98" s="58"/>
+      <c r="E98" s="58"/>
+      <c r="F98" s="58"/>
+      <c r="G98" s="58"/>
+      <c r="H98" s="58"/>
+      <c r="I98" s="58"/>
+      <c r="J98" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -3569,7 +3570,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:V1 B2:V2 A3:V98" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A3:V98 B2:V2 A1:V1" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4616,7 +4617,7 @@
       <c r="C26" s="29"/>
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
-      <c r="F26" s="30"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
       <c r="I26" s="16"/>
@@ -4643,7 +4644,7 @@
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
-      <c r="F27" s="30"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="16"/>
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
@@ -4666,24 +4667,24 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:25">
       <c r="A28" s="17"/>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="35" t="s">
+      <c r="C28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="G28" s="34"/>
-      <c r="H28" s="36" t="s">
+      <c r="G28" s="33"/>
+      <c r="H28" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="38"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="37"/>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
       <c r="U28" s="16"/>
@@ -4694,34 +4695,34 @@
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:25">
       <c r="A29" s="16"/>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39" t="s">
+      <c r="B29" s="38"/>
+      <c r="C29" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="D29" s="39" t="s">
+      <c r="D29" s="38" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="16"/>
-      <c r="F29" s="40" t="s">
+      <c r="F29" s="21" t="s">
         <v>114</v>
       </c>
       <c r="G29" s="16"/>
-      <c r="H29" s="40" t="s">
+      <c r="H29" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="I29" s="40" t="s">
+      <c r="I29" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="J29" s="40" t="s">
+      <c r="J29" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="40" t="s">
+      <c r="K29" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="L29" s="40" t="s">
+      <c r="L29" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="M29" s="40" t="s">
+      <c r="M29" s="21" t="s">
         <v>38</v>
       </c>
       <c r="S29" s="16"/>
@@ -4734,41 +4735,41 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:25">
       <c r="A30" s="16"/>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="38">
         <v>10</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="39">
         <v>0.1</v>
       </c>
       <c r="E30" s="16"/>
-      <c r="F30" s="40">
+      <c r="F30" s="21">
         <v>0</v>
       </c>
       <c r="G30" s="16"/>
-      <c r="H30" s="40">
+      <c r="H30" s="21">
         <v>0</v>
       </c>
-      <c r="I30" s="42">
-        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>0.987279516358749</v>
-      </c>
-      <c r="J30" s="42">
-        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="I30" s="40">
+        <f t="shared" ref="I30:I35" si="5">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
+        <v>0.98727951635875</v>
+      </c>
+      <c r="J30" s="40">
+        <f t="shared" ref="J30:J35" si="6">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.93829461326294</v>
       </c>
-      <c r="K30" s="42">
-        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="K30" s="40">
+        <f t="shared" ref="K30:K35" si="7">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.835766276063232</v>
       </c>
-      <c r="L30" s="42">
-        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="L30" s="40">
+        <f t="shared" ref="L30:L35" si="8">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.686485941521823</v>
       </c>
-      <c r="M30" s="42">
-        <f>BINOMDIST(IF($H30=15,15,$H31-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H30&lt;=0,0,BINOMDIST($H30-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="M30" s="40">
+        <f t="shared" ref="M30:M35" si="9">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.515491059226843</v>
       </c>
       <c r="S30" s="16"/>
@@ -4781,41 +4782,41 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:25">
       <c r="A31" s="16"/>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="38">
         <v>15</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="39">
         <v>0.15</v>
       </c>
       <c r="E31" s="16"/>
-      <c r="F31" s="40">
+      <c r="F31" s="21">
         <v>1</v>
       </c>
       <c r="G31" s="16"/>
-      <c r="H31" s="40">
+      <c r="H31" s="21">
         <v>5</v>
       </c>
-      <c r="I31" s="42">
-        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="I31" s="40">
+        <f t="shared" si="5"/>
         <v>0.012717637158798</v>
       </c>
-      <c r="J31" s="42">
-        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>0.0616244821124745</v>
-      </c>
-      <c r="K31" s="42">
-        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="J31" s="40">
+        <f t="shared" si="6"/>
+        <v>0.0616244821124746</v>
+      </c>
+      <c r="K31" s="40">
+        <f t="shared" si="7"/>
         <v>0.163448738545664</v>
       </c>
-      <c r="L31" s="42">
-        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="L31" s="40">
+        <f t="shared" si="8"/>
         <v>0.309321044012904</v>
       </c>
-      <c r="M31" s="42">
-        <f>BINOMDIST(IF($H31=15,15,$H32-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H31&lt;=0,0,BINOMDIST($H31-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="M31" s="40">
+        <f t="shared" si="9"/>
         <v>0.469266415003386</v>
       </c>
       <c r="S31" s="16"/>
@@ -4828,41 +4829,41 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" spans="1:25">
       <c r="A32" s="16"/>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="39">
+      <c r="C32" s="38">
         <v>20</v>
       </c>
-      <c r="D32" s="41">
+      <c r="D32" s="39">
         <v>0.2</v>
       </c>
       <c r="E32" s="16"/>
-      <c r="F32" s="40">
+      <c r="F32" s="21">
         <v>2</v>
       </c>
       <c r="G32" s="16"/>
-      <c r="H32" s="40">
+      <c r="H32" s="21">
         <v>9</v>
       </c>
-      <c r="I32" s="42">
-        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>2.84614211698564e-6</v>
-      </c>
-      <c r="J32" s="42">
-        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>8.08668558803793e-5</v>
-      </c>
-      <c r="K32" s="42">
-        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>0.000783974137856025</v>
-      </c>
-      <c r="L32" s="42">
-        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="I32" s="40">
+        <f t="shared" si="5"/>
+        <v>2.846142117e-6</v>
+      </c>
+      <c r="J32" s="40">
+        <f t="shared" si="6"/>
+        <v>8.08668558803214e-5</v>
+      </c>
+      <c r="K32" s="40">
+        <f t="shared" si="7"/>
+        <v>0.000783974137856</v>
+      </c>
+      <c r="L32" s="40">
+        <f t="shared" si="8"/>
         <v>0.00418065022677183</v>
       </c>
-      <c r="M32" s="42">
-        <f>BINOMDIST(IF($H32=15,15,$H33-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H32&lt;=0,0,BINOMDIST($H32-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="M32" s="40">
+        <f t="shared" si="9"/>
         <v>0.015150867077619</v>
       </c>
       <c r="S32" s="16"/>
@@ -4875,42 +4876,42 @@
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:25">
       <c r="A33" s="16"/>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="38">
         <v>25</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="39">
         <v>0.25</v>
       </c>
       <c r="E33" s="16"/>
-      <c r="F33" s="40">
+      <c r="F33" s="21">
         <v>3</v>
       </c>
       <c r="G33" s="16"/>
-      <c r="H33" s="40">
+      <c r="H33" s="21">
         <v>12</v>
       </c>
-      <c r="I33" s="42">
-        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>3.40199979298461e-10</v>
-      </c>
-      <c r="J33" s="42">
-        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>3.77310459542812e-8</v>
-      </c>
-      <c r="K33" s="42">
-        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>1.00925440005284e-6</v>
-      </c>
-      <c r="L33" s="42">
-        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="I33" s="40">
+        <f t="shared" si="5"/>
+        <v>3.40200000000002e-10</v>
+      </c>
+      <c r="J33" s="40">
+        <f t="shared" si="6"/>
+        <v>3.77310459732056e-8</v>
+      </c>
+      <c r="K33" s="40">
+        <f t="shared" si="7"/>
+        <v>1.0092544e-6</v>
+      </c>
+      <c r="L33" s="40">
+        <f t="shared" si="8"/>
         <v>1.23213976621628e-5</v>
       </c>
-      <c r="M33" s="42">
-        <f>BINOMDIST(IF($H33=15,15,$H34-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H33&lt;=0,0,BINOMDIST($H33-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>9.11421314999661e-5</v>
+      <c r="M33" s="40">
+        <f t="shared" si="9"/>
+        <v>9.11421315000001e-5</v>
       </c>
       <c r="S33" s="16"/>
       <c r="T33" s="16"/>
@@ -4922,42 +4923,42 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:25">
       <c r="A34" s="16"/>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="38">
         <v>30</v>
       </c>
-      <c r="D34" s="41">
+      <c r="D34" s="39">
         <v>0.3</v>
       </c>
       <c r="E34" s="16"/>
-      <c r="F34" s="40">
+      <c r="F34" s="21">
         <v>4</v>
       </c>
       <c r="G34" s="16"/>
-      <c r="H34" s="40">
+      <c r="H34" s="21">
         <v>14</v>
       </c>
-      <c r="I34" s="42">
-        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>1.35003119794419e-13</v>
-      </c>
-      <c r="J34" s="42">
-        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>3.72210040566756e-11</v>
-      </c>
-      <c r="K34" s="42">
-        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>1.96607996549858e-9</v>
-      </c>
-      <c r="L34" s="42">
-        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="I34" s="40">
+        <f t="shared" si="5"/>
+        <v>1.35e-13</v>
+      </c>
+      <c r="J34" s="40">
+        <f t="shared" si="6"/>
+        <v>3.7220980682373e-11</v>
+      </c>
+      <c r="K34" s="40">
+        <f t="shared" si="7"/>
+        <v>1.96607999999999e-9</v>
+      </c>
+      <c r="L34" s="40">
+        <f t="shared" si="8"/>
         <v>4.19095158576965e-8</v>
       </c>
-      <c r="M34" s="42">
-        <f>BINOMDIST(IF($H34=15,15,$H35-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H34&lt;=0,0,BINOMDIST($H34-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>5.02211745079251e-7</v>
+      <c r="M34" s="40">
+        <f t="shared" si="9"/>
+        <v>5.02211745e-7</v>
       </c>
       <c r="S34" s="16"/>
       <c r="T34" s="16"/>
@@ -4969,40 +4970,40 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:25">
       <c r="A35" s="16"/>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="38">
         <v>100</v>
       </c>
-      <c r="D35" s="39"/>
+      <c r="D35" s="38"/>
       <c r="E35" s="16"/>
-      <c r="F35" s="40">
+      <c r="F35" s="21">
         <v>5</v>
       </c>
       <c r="G35" s="16"/>
-      <c r="H35" s="40">
+      <c r="H35" s="21">
         <v>15</v>
       </c>
-      <c r="I35" s="42">
-        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="42">
-        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>4.37871960912162e-13</v>
-      </c>
-      <c r="K35" s="42">
-        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>3.27680105272066e-11</v>
-      </c>
-      <c r="L35" s="42">
-        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
+      <c r="I35" s="40">
+        <f t="shared" si="5"/>
+        <v>1e-15</v>
+      </c>
+      <c r="J35" s="40">
+        <f t="shared" si="6"/>
+        <v>4.3789389038086e-13</v>
+      </c>
+      <c r="K35" s="40">
+        <f t="shared" si="7"/>
+        <v>3.2768e-11</v>
+      </c>
+      <c r="L35" s="40">
+        <f t="shared" si="8"/>
         <v>9.31322574615479e-10</v>
       </c>
-      <c r="M35" s="42">
-        <f>BINOMDIST(IF($H35=15,15,$M36-1),$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($H35&lt;=0,0,BINOMDIST($H35-1,$F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
-        <v>1.43489069515113e-8</v>
+      <c r="M35" s="40">
+        <f t="shared" si="9"/>
+        <v>1.4348907e-8</v>
       </c>
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
@@ -5018,7 +5019,7 @@
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
-      <c r="F36" s="40">
+      <c r="F36" s="21">
         <v>6</v>
       </c>
       <c r="G36" s="16"/>
@@ -5047,7 +5048,7 @@
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
-      <c r="F37" s="40">
+      <c r="F37" s="21">
         <v>7</v>
       </c>
       <c r="G37" s="16"/>
@@ -5076,7 +5077,7 @@
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
-      <c r="F38" s="40">
+      <c r="F38" s="21">
         <v>8</v>
       </c>
       <c r="G38" s="16"/>
@@ -5105,7 +5106,7 @@
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
       <c r="E39" s="16"/>
-      <c r="F39" s="40">
+      <c r="F39" s="21">
         <v>9</v>
       </c>
       <c r="G39" s="16"/>
@@ -5134,7 +5135,7 @@
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
-      <c r="F40" s="40">
+      <c r="F40" s="21">
         <v>10</v>
       </c>
       <c r="G40" s="16"/>
@@ -5163,7 +5164,7 @@
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
-      <c r="F41" s="40">
+      <c r="F41" s="21">
         <v>11</v>
       </c>
       <c r="G41" s="16"/>
@@ -5192,7 +5193,7 @@
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
-      <c r="F42" s="40">
+      <c r="F42" s="21">
         <v>12</v>
       </c>
       <c r="G42" s="16"/>
@@ -5221,7 +5222,7 @@
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
-      <c r="F43" s="40">
+      <c r="F43" s="21">
         <v>13</v>
       </c>
       <c r="G43" s="16"/>
@@ -5250,7 +5251,7 @@
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
-      <c r="F44" s="40">
+      <c r="F44" s="21">
         <v>14</v>
       </c>
       <c r="G44" s="16"/>
@@ -5279,7 +5280,7 @@
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
-      <c r="F45" s="40">
+      <c r="F45" s="21">
         <v>15</v>
       </c>
       <c r="G45" s="16"/>
@@ -5308,7 +5309,7 @@
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
       <c r="E46" s="16"/>
-      <c r="F46" s="30"/>
+      <c r="F46" s="19"/>
       <c r="G46" s="16"/>
       <c r="H46" s="16"/>
       <c r="I46" s="16"/>
@@ -5335,7 +5336,7 @@
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
-      <c r="F47" s="30"/>
+      <c r="F47" s="19"/>
       <c r="G47" s="16"/>
       <c r="H47" s="16"/>
       <c r="I47" s="16"/>
@@ -5362,7 +5363,7 @@
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
       <c r="E48" s="16"/>
-      <c r="F48" s="30"/>
+      <c r="F48" s="19"/>
       <c r="G48" s="16"/>
       <c r="H48" s="16"/>
       <c r="I48" s="16"/>
@@ -5389,7 +5390,7 @@
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
-      <c r="F49" s="30"/>
+      <c r="F49" s="19"/>
       <c r="G49" s="16"/>
       <c r="H49" s="16"/>
       <c r="I49" s="16"/>
@@ -5416,7 +5417,7 @@
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
-      <c r="F50" s="30"/>
+      <c r="F50" s="19"/>
       <c r="G50" s="16"/>
       <c r="H50" s="16"/>
       <c r="I50" s="16"/>
@@ -5443,7 +5444,7 @@
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
-      <c r="F51" s="30"/>
+      <c r="F51" s="19"/>
       <c r="G51" s="16"/>
       <c r="H51" s="16"/>
       <c r="I51" s="16"/>
@@ -5470,7 +5471,7 @@
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
-      <c r="F52" s="30"/>
+      <c r="F52" s="19"/>
       <c r="G52" s="16"/>
       <c r="H52" s="16"/>
       <c r="I52" s="16"/>
@@ -5497,7 +5498,7 @@
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
-      <c r="F53" s="30"/>
+      <c r="F53" s="19"/>
       <c r="G53" s="16"/>
       <c r="H53" s="16"/>
       <c r="I53" s="16"/>
@@ -5519,15 +5520,15 @@
       <c r="Y53" s="16"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="B54" s="43"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
       <c r="H54" s="16"/>
       <c r="I54" s="16"/>
       <c r="J54" s="16"/>
@@ -5548,18 +5549,18 @@
       <c r="Y54" s="16"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="B55" s="43"/>
-      <c r="C55" s="43"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="43"/>
-      <c r="I55" s="43"/>
-      <c r="J55" s="43"/>
+      <c r="B55" s="41"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="41"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
@@ -5577,14 +5578,14 @@
       <c r="Y55" s="16"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:25">
-      <c r="A56" s="43" t="s">
+      <c r="A56" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="43"/>
-      <c r="C56" s="43"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
       <c r="G56" s="16"/>
       <c r="H56" s="16"/>
       <c r="I56" s="16"/>
@@ -5709,25 +5710,25 @@
       <c r="L60" s="9"/>
       <c r="M60" s="9"/>
       <c r="N60" s="9"/>
-      <c r="O60" s="34"/>
-      <c r="P60" s="34"/>
-      <c r="Q60" s="34"/>
-      <c r="R60" s="34"/>
-      <c r="S60" s="34"/>
-      <c r="T60" s="34"/>
-      <c r="U60" s="34"/>
-      <c r="V60" s="34"/>
-      <c r="W60" s="34"/>
-      <c r="X60" s="34"/>
-      <c r="Y60" s="34"/>
+      <c r="O60" s="33"/>
+      <c r="P60" s="33"/>
+      <c r="Q60" s="33"/>
+      <c r="R60" s="33"/>
+      <c r="S60" s="33"/>
+      <c r="T60" s="33"/>
+      <c r="U60" s="33"/>
+      <c r="V60" s="33"/>
+      <c r="W60" s="33"/>
+      <c r="X60" s="33"/>
+      <c r="Y60" s="33"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:25">
       <c r="A61" s="16"/>
-      <c r="B61" s="26" t="s">
+      <c r="B61" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="43"/>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16"/>
@@ -5752,11 +5753,11 @@
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:25">
       <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="30" t="s">
+      <c r="B62" s="43"/>
+      <c r="C62" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="30" t="s">
+      <c r="D62" s="44" t="s">
         <v>39</v>
       </c>
       <c r="E62" s="16"/>
@@ -5764,68 +5765,68 @@
         <v>104</v>
       </c>
       <c r="G62" s="16"/>
-      <c r="H62" s="30" t="s">
+      <c r="H62" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I62" s="30">
+      <c r="I62" s="19">
         <v>0</v>
       </c>
-      <c r="J62" s="30">
+      <c r="J62" s="19">
         <v>1</v>
       </c>
-      <c r="K62" s="30">
+      <c r="K62" s="19">
         <v>2</v>
       </c>
-      <c r="L62" s="30">
+      <c r="L62" s="19">
         <v>3</v>
       </c>
-      <c r="M62" s="30">
+      <c r="M62" s="19">
         <v>4</v>
       </c>
-      <c r="N62" s="30">
+      <c r="N62" s="19">
         <v>5</v>
       </c>
-      <c r="O62" s="30">
+      <c r="O62" s="19">
         <v>6</v>
       </c>
-      <c r="P62" s="30">
+      <c r="P62" s="19">
         <v>7</v>
       </c>
-      <c r="Q62" s="30">
+      <c r="Q62" s="19">
         <v>8</v>
       </c>
-      <c r="R62" s="30">
+      <c r="R62" s="19">
         <v>9</v>
       </c>
-      <c r="S62" s="30">
+      <c r="S62" s="19">
         <v>10</v>
       </c>
-      <c r="T62" s="30">
+      <c r="T62" s="19">
         <v>11</v>
       </c>
-      <c r="U62" s="30">
+      <c r="U62" s="19">
         <v>12</v>
       </c>
-      <c r="V62" s="30">
+      <c r="V62" s="19">
         <v>13</v>
       </c>
-      <c r="W62" s="30">
+      <c r="W62" s="19">
         <v>14</v>
       </c>
-      <c r="X62" s="30">
+      <c r="X62" s="19">
         <v>15</v>
       </c>
-      <c r="Y62" s="30"/>
+      <c r="Y62" s="19"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:25">
       <c r="A63" s="16"/>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="43">
         <v>10</v>
       </c>
-      <c r="D63" s="44">
+      <c r="D63" s="45">
         <v>0.1</v>
       </c>
       <c r="E63" s="16"/>
@@ -5833,503 +5834,503 @@
         <v>34</v>
       </c>
       <c r="G63" s="16"/>
-      <c r="H63" s="30">
+      <c r="H63" s="19">
         <v>0</v>
       </c>
-      <c r="I63" s="44">
-        <f t="shared" ref="I63:Y63" si="5">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I63" s="46">
+        <f t="shared" ref="I63:Y63" si="10">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="L63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="M63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="P63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="R63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="S63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="T63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="U63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="V63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="W63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="X63" s="44" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y63" s="44">
-        <f t="shared" si="5"/>
+      <c r="J63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="K63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="M63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="N63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Q63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="R63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="S63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="T63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="V63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="W63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="X63" s="47" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Y63" s="46">
+        <f t="shared" si="10"/>
         <v>0.205891132094649</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:25">
       <c r="A64" s="16"/>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="C64" s="16">
+      <c r="C64" s="43">
         <v>15</v>
       </c>
-      <c r="D64" s="44">
+      <c r="D64" s="45">
         <v>0.15</v>
       </c>
       <c r="E64" s="16"/>
       <c r="F64" s="16"/>
       <c r="G64" s="16"/>
-      <c r="H64" s="30">
+      <c r="H64" s="19">
         <v>1</v>
       </c>
-      <c r="I64" s="44">
-        <f t="shared" ref="I64:Y64" si="6">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I64" s="46">
+        <f t="shared" ref="I64:Y64" si="11">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.343151886824415</v>
       </c>
-      <c r="J64" s="44">
-        <f t="shared" si="6"/>
+      <c r="J64" s="46">
+        <f t="shared" si="11"/>
         <v>0.22876792454961</v>
       </c>
-      <c r="K64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="L64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="M64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="N64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Q64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="R64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="S64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="T64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="U64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="V64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="W64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="X64" s="44" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Y64" s="44">
-        <f t="shared" si="6"/>
+      <c r="K64" s="46" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="L64" s="46" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="M64" s="46" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="N64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="O64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="P64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="Q64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="S64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="T64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="U64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="V64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="W64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="X64" s="47" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="Y64" s="46">
+        <f t="shared" si="11"/>
         <v>0.343151886824415</v>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:25">
       <c r="A65" s="16"/>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="43">
         <v>20</v>
       </c>
-      <c r="D65" s="44">
+      <c r="D65" s="45">
         <v>0.2</v>
       </c>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
       <c r="G65" s="16"/>
-      <c r="H65" s="30">
+      <c r="H65" s="19">
         <v>2</v>
       </c>
-      <c r="I65" s="44">
-        <f t="shared" ref="I65:Y65" si="7">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I65" s="46">
+        <f t="shared" ref="I65:Y65" si="12">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.266895911974545</v>
       </c>
-      <c r="J65" s="44">
-        <f t="shared" si="7"/>
+      <c r="J65" s="46">
+        <f t="shared" si="12"/>
         <v>0.35586121596606</v>
       </c>
-      <c r="K65" s="44">
-        <f t="shared" si="7"/>
+      <c r="K65" s="46">
+        <f t="shared" si="12"/>
         <v>0.2541865828329</v>
       </c>
-      <c r="L65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="N65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="O65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="Q65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="R65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="S65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="T65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="U65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="V65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="W65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="X65" s="44" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="Y65" s="44">
-        <f t="shared" si="7"/>
+      <c r="L65" s="46" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="M65" s="46" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="N65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="O65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Q65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="R65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="T65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="V65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="W65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X65" s="47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Y65" s="46">
+        <f t="shared" si="12"/>
         <v>0.266895911974545</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:25">
       <c r="A66" s="16"/>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="16">
+      <c r="C66" s="43">
         <v>25</v>
       </c>
-      <c r="D66" s="44">
+      <c r="D66" s="45">
         <v>0.25</v>
       </c>
       <c r="E66" s="16"/>
       <c r="F66" s="16"/>
       <c r="G66" s="16"/>
-      <c r="H66" s="30">
+      <c r="H66" s="19">
         <v>3</v>
       </c>
-      <c r="I66" s="44">
-        <f t="shared" ref="I66:Y66" si="8">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I66" s="46">
+        <f t="shared" ref="I66:Y66" si="13">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.128505439098855</v>
       </c>
-      <c r="J66" s="44">
-        <f t="shared" si="8"/>
+      <c r="J66" s="46">
+        <f t="shared" si="13"/>
         <v>0.25701087819771</v>
       </c>
-      <c r="K66" s="44">
-        <f t="shared" si="8"/>
+      <c r="K66" s="46">
+        <f t="shared" si="13"/>
         <v>0.3671583974253</v>
       </c>
-      <c r="L66" s="44">
-        <f t="shared" si="8"/>
+      <c r="L66" s="46">
+        <f t="shared" si="13"/>
         <v>0.282429536481</v>
       </c>
-      <c r="M66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="P66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="R66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="S66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="T66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="U66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="V66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="W66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="X66" s="44" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Y66" s="44">
-        <f t="shared" si="8"/>
+      <c r="M66" s="46" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="N66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="O66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="P66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Q66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="R66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="S66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="T66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="U66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="W66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X66" s="47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y66" s="46">
+        <f t="shared" si="13"/>
         <v>0.128505439098855</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:25">
       <c r="A67" s="16"/>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="43">
         <v>30</v>
       </c>
-      <c r="D67" s="44">
+      <c r="D67" s="45">
         <v>0.3</v>
       </c>
       <c r="E67" s="16"/>
       <c r="F67" s="16"/>
       <c r="G67" s="16"/>
-      <c r="H67" s="30">
+      <c r="H67" s="19">
         <v>4</v>
       </c>
-      <c r="I67" s="44">
-        <f t="shared" ref="I67:Y67" si="9">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I67" s="46">
+        <f t="shared" ref="I67:Y67" si="14">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J67" s="44">
-        <f t="shared" si="9"/>
+      <c r="J67" s="46">
+        <f t="shared" si="14"/>
         <v>0.11422705697676</v>
       </c>
-      <c r="K67" s="44">
-        <f t="shared" si="9"/>
+      <c r="K67" s="46">
+        <f t="shared" si="14"/>
         <v>0.2447722649502</v>
       </c>
-      <c r="L67" s="44">
-        <f t="shared" si="9"/>
+      <c r="L67" s="46">
+        <f t="shared" si="14"/>
         <v>0.376572715308</v>
       </c>
-      <c r="M67" s="44">
-        <f t="shared" si="9"/>
+      <c r="M67" s="46">
+        <f t="shared" si="14"/>
         <v>0.31381059609</v>
       </c>
-      <c r="N67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="P67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="S67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="T67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="U67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="V67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="W67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="X67" s="44" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Y67" s="44">
-        <f t="shared" si="9"/>
+      <c r="N67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="O67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="P67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Q67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="R67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="S67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="T67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="V67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="W67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="X67" s="47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Y67" s="46">
+        <f t="shared" si="14"/>
         <v>0.0428351463662851</v>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:25">
       <c r="A68" s="16"/>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="C68" s="16">
+      <c r="C68" s="43">
         <v>100</v>
       </c>
-      <c r="D68" s="16"/>
+      <c r="D68" s="43"/>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
-      <c r="H68" s="30">
+      <c r="H68" s="19">
         <v>5</v>
       </c>
-      <c r="I68" s="45">
-        <f t="shared" ref="I68:Y68" si="10">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I68" s="48">
+        <f t="shared" ref="I68:Y68" si="15">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.010470813556203</v>
       </c>
-      <c r="J68" s="45">
-        <f t="shared" si="10"/>
+      <c r="J68" s="48">
+        <f t="shared" si="15"/>
         <v>0.03490271185401</v>
       </c>
-      <c r="K68" s="45">
-        <f t="shared" si="10"/>
+      <c r="K68" s="48">
+        <f t="shared" si="15"/>
         <v>0.0997220338686001</v>
       </c>
-      <c r="L68" s="45">
-        <f t="shared" si="10"/>
+      <c r="L68" s="48">
+        <f t="shared" si="15"/>
         <v>0.230127770466</v>
       </c>
-      <c r="M68" s="45">
-        <f t="shared" si="10"/>
+      <c r="M68" s="48">
+        <f t="shared" si="15"/>
         <v>0.38354628411</v>
       </c>
-      <c r="N68" s="45">
-        <f t="shared" si="10"/>
+      <c r="N68" s="48">
+        <f t="shared" si="15"/>
         <v>0.3486784401</v>
       </c>
-      <c r="O68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="P68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="Q68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="R68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="S68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="T68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="U68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="V68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="W68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="X68" s="44" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="Y68" s="44">
-        <f t="shared" si="10"/>
+      <c r="O68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="P68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="Q68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="R68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="S68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="T68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="U68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="V68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="W68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="X68" s="47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="Y68" s="46">
+        <f t="shared" si="15"/>
         <v>0.010470813556203</v>
       </c>
     </row>
@@ -6341,75 +6342,75 @@
       <c r="E69" s="16"/>
       <c r="F69" s="16"/>
       <c r="G69" s="16"/>
-      <c r="H69" s="30">
+      <c r="H69" s="19">
         <v>6</v>
       </c>
-      <c r="I69" s="44">
-        <f t="shared" ref="I69:Y69" si="11">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I69" s="46">
+        <f t="shared" ref="I69:Y69" si="16">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.001939039547445</v>
       </c>
-      <c r="J69" s="44">
-        <f t="shared" si="11"/>
+      <c r="J69" s="46">
+        <f t="shared" si="16"/>
         <v>0.00775615818978</v>
       </c>
-      <c r="K69" s="44">
-        <f t="shared" si="11"/>
+      <c r="K69" s="46">
+        <f t="shared" si="16"/>
         <v>0.0277005649635</v>
       </c>
-      <c r="L69" s="44">
-        <f t="shared" si="11"/>
+      <c r="L69" s="46">
+        <f t="shared" si="16"/>
         <v>0.08523250758</v>
       </c>
-      <c r="M69" s="44">
-        <f t="shared" si="11"/>
+      <c r="M69" s="46">
+        <f t="shared" si="16"/>
         <v>0.21308126895</v>
       </c>
-      <c r="N69" s="44">
-        <f t="shared" si="11"/>
+      <c r="N69" s="46">
+        <f t="shared" si="16"/>
         <v>0.387420489</v>
       </c>
-      <c r="O69" s="44">
-        <f t="shared" si="11"/>
+      <c r="O69" s="46">
+        <f t="shared" si="16"/>
         <v>0.387420489</v>
       </c>
-      <c r="P69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="R69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="S69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="T69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="U69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="W69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="X69" s="44" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Y69" s="44">
-        <f t="shared" si="11"/>
+      <c r="P69" s="46" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Q69" s="46" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="R69" s="46" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="S69" s="46" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="T69" s="47" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="U69" s="47" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="V69" s="47" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="W69" s="47" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="X69" s="47" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="Y69" s="46">
+        <f t="shared" si="16"/>
         <v>0.001939039547445</v>
       </c>
     </row>
@@ -6421,75 +6422,75 @@
       <c r="E70" s="16"/>
       <c r="F70" s="16"/>
       <c r="G70" s="16"/>
-      <c r="H70" s="30">
+      <c r="H70" s="19">
         <v>7</v>
       </c>
-      <c r="I70" s="44">
-        <f t="shared" ref="I70:Y70" si="12">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I70" s="46">
+        <f t="shared" ref="I70:Y70" si="17">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.000277005649635</v>
       </c>
-      <c r="J70" s="44">
-        <f t="shared" si="12"/>
+      <c r="J70" s="46">
+        <f t="shared" si="17"/>
         <v>0.00129269303163</v>
       </c>
-      <c r="K70" s="44">
-        <f t="shared" si="12"/>
+      <c r="K70" s="46">
+        <f t="shared" si="17"/>
         <v>0.0055401129927</v>
       </c>
-      <c r="L70" s="44">
-        <f t="shared" si="12"/>
+      <c r="L70" s="46">
+        <f t="shared" si="17"/>
         <v>0.021308126895</v>
       </c>
-      <c r="M70" s="44">
-        <f t="shared" si="12"/>
+      <c r="M70" s="46">
+        <f t="shared" si="17"/>
         <v>0.07102708965</v>
       </c>
-      <c r="N70" s="44">
-        <f t="shared" si="12"/>
+      <c r="N70" s="46">
+        <f t="shared" si="17"/>
         <v>0.1937102445</v>
       </c>
-      <c r="O70" s="44">
-        <f t="shared" si="12"/>
+      <c r="O70" s="46">
+        <f t="shared" si="17"/>
         <v>0.387420489</v>
       </c>
-      <c r="P70" s="44">
-        <f t="shared" si="12"/>
+      <c r="P70" s="46">
+        <f t="shared" si="17"/>
         <v>0.43046721</v>
       </c>
-      <c r="Q70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="R70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="S70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="T70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="U70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="V70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="X70" s="44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="Y70" s="44">
-        <f t="shared" si="12"/>
+      <c r="Q70" s="46" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="R70" s="46" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="S70" s="46" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T70" s="47" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="U70" s="47" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="V70" s="47" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="W70" s="47" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X70" s="47" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="Y70" s="46">
+        <f t="shared" si="17"/>
         <v>0.000277005649635</v>
       </c>
     </row>
@@ -6501,75 +6502,75 @@
       <c r="E71" s="16"/>
       <c r="F71" s="16"/>
       <c r="G71" s="16"/>
-      <c r="H71" s="30">
+      <c r="H71" s="19">
         <v>8</v>
       </c>
-      <c r="I71" s="44">
-        <f t="shared" ref="I71:Y71" si="13">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I71" s="46">
+        <f t="shared" ref="I71:Y71" si="18">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J71" s="44">
-        <f t="shared" si="13"/>
+      <c r="J71" s="46">
+        <f t="shared" si="18"/>
         <v>0.00016415149608</v>
       </c>
-      <c r="K71" s="44">
-        <f t="shared" si="13"/>
+      <c r="K71" s="46">
+        <f t="shared" si="18"/>
         <v>0.0008207574804</v>
       </c>
-      <c r="L71" s="44">
-        <f t="shared" si="13"/>
+      <c r="L71" s="46">
+        <f t="shared" si="18"/>
         <v>0.003788111448</v>
       </c>
-      <c r="M71" s="44">
-        <f t="shared" si="13"/>
+      <c r="M71" s="46">
+        <f t="shared" si="18"/>
         <v>0.0157837977</v>
       </c>
-      <c r="N71" s="44">
-        <f t="shared" si="13"/>
+      <c r="N71" s="46">
+        <f t="shared" si="18"/>
         <v>0.057395628</v>
       </c>
-      <c r="O71" s="44">
-        <f t="shared" si="13"/>
+      <c r="O71" s="46">
+        <f t="shared" si="18"/>
         <v>0.172186884</v>
       </c>
-      <c r="P71" s="44">
-        <f t="shared" si="13"/>
+      <c r="P71" s="46">
+        <f t="shared" si="18"/>
         <v>0.38263752</v>
       </c>
-      <c r="Q71" s="44">
-        <f t="shared" si="13"/>
+      <c r="Q71" s="46">
+        <f t="shared" si="18"/>
         <v>0.4782969</v>
       </c>
-      <c r="R71" s="44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="S71" s="44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="T71" s="44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="U71" s="44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="V71" s="44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="W71" s="44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X71" s="44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Y71" s="44">
-        <f t="shared" si="13"/>
+      <c r="R71" s="46" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="S71" s="46" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="T71" s="47" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U71" s="47" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="V71" s="47" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="W71" s="47" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="X71" s="47" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="Y71" s="46">
+        <f t="shared" si="18"/>
         <v>3.0778405515e-5</v>
       </c>
     </row>
@@ -6581,75 +6582,75 @@
       <c r="E72" s="16"/>
       <c r="F72" s="16"/>
       <c r="G72" s="16"/>
-      <c r="H72" s="30">
+      <c r="H72" s="19">
         <v>9</v>
       </c>
-      <c r="I72" s="44">
-        <f t="shared" ref="I72:Y72" si="14">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I72" s="46">
+        <f t="shared" ref="I72:Y72" si="19">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J72" s="44">
-        <f t="shared" si="14"/>
+      <c r="J72" s="46">
+        <f t="shared" si="19"/>
         <v>1.595917323e-5</v>
       </c>
-      <c r="K72" s="44">
-        <f t="shared" si="14"/>
+      <c r="K72" s="46">
+        <f t="shared" si="19"/>
         <v>9.11952756e-5</v>
       </c>
-      <c r="L72" s="44">
-        <f t="shared" si="14"/>
+      <c r="L72" s="46">
+        <f t="shared" si="19"/>
         <v>0.000491051484000001</v>
       </c>
-      <c r="M72" s="44">
-        <f t="shared" si="14"/>
+      <c r="M72" s="46">
+        <f t="shared" si="19"/>
         <v>0.00245525742</v>
       </c>
-      <c r="N72" s="44">
-        <f t="shared" si="14"/>
+      <c r="N72" s="46">
+        <f t="shared" si="19"/>
         <v>0.011160261</v>
       </c>
-      <c r="O72" s="44">
-        <f t="shared" si="14"/>
+      <c r="O72" s="46">
+        <f t="shared" si="19"/>
         <v>0.044641044</v>
       </c>
-      <c r="P72" s="44">
-        <f t="shared" si="14"/>
+      <c r="P72" s="46">
+        <f t="shared" si="19"/>
         <v>0.14880348</v>
       </c>
-      <c r="Q72" s="44">
-        <f t="shared" si="14"/>
+      <c r="Q72" s="46">
+        <f t="shared" si="19"/>
         <v>0.3720087</v>
       </c>
-      <c r="R72" s="44">
-        <f t="shared" si="14"/>
+      <c r="R72" s="46">
+        <f t="shared" si="19"/>
         <v>0.531441</v>
       </c>
-      <c r="S72" s="44" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="T72" s="44" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="U72" s="44" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="V72" s="44" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="W72" s="44" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="X72" s="44" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y72" s="44">
-        <f t="shared" si="14"/>
+      <c r="S72" s="46" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="T72" s="47" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="U72" s="47" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V72" s="47" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="W72" s="47" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="X72" s="47" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Y72" s="46">
+        <f t="shared" si="19"/>
         <v>2.659862205e-6</v>
       </c>
     </row>
@@ -6661,75 +6662,75 @@
       <c r="E73" s="16"/>
       <c r="F73" s="16"/>
       <c r="G73" s="16"/>
-      <c r="H73" s="30">
+      <c r="H73" s="19">
         <v>10</v>
       </c>
-      <c r="I73" s="44">
-        <f t="shared" ref="I73:Y73" si="15">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I73" s="46">
+        <f t="shared" ref="I73:Y73" si="20">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J73" s="44">
-        <f t="shared" si="15"/>
+      <c r="J73" s="46">
+        <f t="shared" si="20"/>
         <v>1.18216098e-6</v>
       </c>
-      <c r="K73" s="44">
-        <f t="shared" si="15"/>
+      <c r="K73" s="46">
+        <f t="shared" si="20"/>
         <v>7.5996063e-6</v>
       </c>
-      <c r="L73" s="44">
-        <f t="shared" si="15"/>
+      <c r="L73" s="46">
+        <f t="shared" si="20"/>
         <v>4.6766808e-5</v>
       </c>
-      <c r="M73" s="44">
-        <f t="shared" si="15"/>
+      <c r="M73" s="46">
+        <f t="shared" si="20"/>
         <v>0.00027280638</v>
       </c>
-      <c r="N73" s="44">
-        <f t="shared" si="15"/>
+      <c r="N73" s="46">
+        <f t="shared" si="20"/>
         <v>0.0014880348</v>
       </c>
-      <c r="O73" s="44">
-        <f t="shared" si="15"/>
+      <c r="O73" s="46">
+        <f t="shared" si="20"/>
         <v>0.00744017399999999</v>
       </c>
-      <c r="P73" s="44">
-        <f t="shared" si="15"/>
+      <c r="P73" s="46">
+        <f t="shared" si="20"/>
         <v>0.03306744</v>
       </c>
-      <c r="Q73" s="44">
-        <f t="shared" si="15"/>
+      <c r="Q73" s="46">
+        <f t="shared" si="20"/>
         <v>0.1240029</v>
       </c>
-      <c r="R73" s="44">
-        <f t="shared" si="15"/>
+      <c r="R73" s="46">
+        <f t="shared" si="20"/>
         <v>0.354294</v>
       </c>
-      <c r="S73" s="44">
-        <f t="shared" si="15"/>
+      <c r="S73" s="46">
+        <f t="shared" si="20"/>
         <v>0.59049</v>
       </c>
-      <c r="T73" s="44" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="U73" s="44" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="V73" s="44" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="W73" s="44" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="X73" s="44" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Y73" s="44">
-        <f t="shared" si="15"/>
+      <c r="T73" s="47" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="U73" s="47" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="V73" s="47" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="W73" s="47" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="X73" s="47" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="Y73" s="46">
+        <f t="shared" si="20"/>
         <v>1.77324147e-7</v>
       </c>
     </row>
@@ -6741,75 +6742,75 @@
       <c r="E74" s="16"/>
       <c r="F74" s="16"/>
       <c r="G74" s="16"/>
-      <c r="H74" s="30">
+      <c r="H74" s="19">
         <v>11</v>
       </c>
-      <c r="I74" s="44">
-        <f t="shared" ref="I74:Y74" si="16">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I74" s="46">
+        <f t="shared" ref="I74:Y74" si="21">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J74" s="44">
-        <f t="shared" si="16"/>
+      <c r="J74" s="46">
+        <f t="shared" si="21"/>
         <v>6.56756100000002e-8</v>
       </c>
-      <c r="K74" s="44">
-        <f t="shared" si="16"/>
+      <c r="K74" s="46">
+        <f t="shared" si="21"/>
         <v>4.69111499999999e-7</v>
       </c>
-      <c r="L74" s="44">
-        <f t="shared" si="16"/>
+      <c r="L74" s="46">
+        <f t="shared" si="21"/>
         <v>3.247695e-6</v>
       </c>
-      <c r="M74" s="44">
-        <f t="shared" si="16"/>
+      <c r="M74" s="46">
+        <f t="shared" si="21"/>
         <v>2.16512999999999e-5</v>
       </c>
-      <c r="N74" s="44">
-        <f t="shared" si="16"/>
+      <c r="N74" s="46">
+        <f t="shared" si="21"/>
         <v>0.000137781</v>
       </c>
-      <c r="O74" s="44">
-        <f t="shared" si="16"/>
+      <c r="O74" s="46">
+        <f t="shared" si="21"/>
         <v>0.000826686</v>
       </c>
-      <c r="P74" s="44">
-        <f t="shared" si="16"/>
+      <c r="P74" s="46">
+        <f t="shared" si="21"/>
         <v>0.0045927</v>
       </c>
-      <c r="Q74" s="44">
-        <f t="shared" si="16"/>
+      <c r="Q74" s="46">
+        <f t="shared" si="21"/>
         <v>0.0229635</v>
       </c>
-      <c r="R74" s="44">
-        <f t="shared" si="16"/>
+      <c r="R74" s="46">
+        <f t="shared" si="21"/>
         <v>0.0984150000000001</v>
       </c>
-      <c r="S74" s="44">
-        <f t="shared" si="16"/>
+      <c r="S74" s="46">
+        <f t="shared" si="21"/>
         <v>0.32805</v>
       </c>
-      <c r="T74" s="44">
-        <f t="shared" si="16"/>
+      <c r="T74" s="46">
+        <f t="shared" si="21"/>
         <v>0.6561</v>
       </c>
-      <c r="U74" s="44" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="V74" s="44" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="W74" s="44" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="X74" s="44" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="Y74" s="44">
-        <f t="shared" si="16"/>
+      <c r="U74" s="46" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="V74" s="46" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="W74" s="46" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="X74" s="46" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="Y74" s="46">
+        <f t="shared" si="21"/>
         <v>8.95576499999999e-9</v>
       </c>
     </row>
@@ -6821,75 +6822,75 @@
       <c r="E75" s="16"/>
       <c r="F75" s="16"/>
       <c r="G75" s="16"/>
-      <c r="H75" s="30">
+      <c r="H75" s="19">
         <v>12</v>
       </c>
-      <c r="I75" s="44">
-        <f t="shared" ref="I75:Y75" si="17">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I75" s="46">
+        <f t="shared" ref="I75:Y75" si="22">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J75" s="44">
-        <f t="shared" si="17"/>
+      <c r="J75" s="46">
+        <f t="shared" si="22"/>
         <v>2.65356e-9</v>
       </c>
-      <c r="K75" s="44">
-        <f t="shared" si="17"/>
+      <c r="K75" s="46">
+        <f t="shared" si="22"/>
         <v>2.08494e-8</v>
       </c>
-      <c r="L75" s="44">
-        <f t="shared" si="17"/>
+      <c r="L75" s="46">
+        <f t="shared" si="22"/>
         <v>1.6038e-7</v>
       </c>
-      <c r="M75" s="44">
-        <f t="shared" si="17"/>
+      <c r="M75" s="46">
+        <f t="shared" si="22"/>
         <v>1.20285e-6</v>
       </c>
-      <c r="N75" s="44">
-        <f t="shared" si="17"/>
+      <c r="N75" s="46">
+        <f t="shared" si="22"/>
         <v>8.74800000000001e-6</v>
       </c>
-      <c r="O75" s="44">
-        <f t="shared" si="17"/>
+      <c r="O75" s="46">
+        <f t="shared" si="22"/>
         <v>6.1236e-5</v>
       </c>
-      <c r="P75" s="44">
-        <f t="shared" si="17"/>
+      <c r="P75" s="46">
+        <f t="shared" si="22"/>
         <v>0.00040824</v>
       </c>
-      <c r="Q75" s="44">
-        <f t="shared" si="17"/>
+      <c r="Q75" s="46">
+        <f t="shared" si="22"/>
         <v>0.0025515</v>
       </c>
-      <c r="R75" s="44">
-        <f t="shared" si="17"/>
+      <c r="R75" s="46">
+        <f t="shared" si="22"/>
         <v>0.01458</v>
       </c>
-      <c r="S75" s="44">
-        <f t="shared" si="17"/>
+      <c r="S75" s="46">
+        <f t="shared" si="22"/>
         <v>0.0729</v>
       </c>
-      <c r="T75" s="44">
-        <f t="shared" si="17"/>
+      <c r="T75" s="46">
+        <f t="shared" si="22"/>
         <v>0.2916</v>
       </c>
-      <c r="U75" s="44">
-        <f t="shared" si="17"/>
+      <c r="U75" s="46">
+        <f t="shared" si="22"/>
         <v>0.729</v>
       </c>
-      <c r="V75" s="44" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="W75" s="44" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="X75" s="44" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="Y75" s="44">
-        <f t="shared" si="17"/>
+      <c r="V75" s="46" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="W75" s="46" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="X75" s="46" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Y75" s="46">
+        <f t="shared" si="22"/>
         <v>3.31695000000002e-10</v>
       </c>
     </row>
@@ -6901,75 +6902,75 @@
       <c r="E76" s="16"/>
       <c r="F76" s="16"/>
       <c r="G76" s="16"/>
-      <c r="H76" s="30">
+      <c r="H76" s="19">
         <v>13</v>
       </c>
-      <c r="I76" s="44">
-        <f t="shared" ref="I76:Y76" si="18">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I76" s="46">
+        <f t="shared" ref="I76:Y76" si="23">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J76" s="44">
-        <f t="shared" si="18"/>
+      <c r="J76" s="46">
+        <f t="shared" si="23"/>
         <v>7.37100000000002e-11</v>
       </c>
-      <c r="K76" s="44">
-        <f t="shared" si="18"/>
+      <c r="K76" s="46">
+        <f t="shared" si="23"/>
         <v>6.318e-10</v>
       </c>
-      <c r="L76" s="44">
-        <f t="shared" si="18"/>
+      <c r="L76" s="46">
+        <f t="shared" si="23"/>
         <v>5.34599999999998e-9</v>
       </c>
-      <c r="M76" s="44">
-        <f t="shared" si="18"/>
+      <c r="M76" s="46">
+        <f t="shared" si="23"/>
         <v>4.455e-8</v>
       </c>
-      <c r="N76" s="44">
-        <f t="shared" si="18"/>
+      <c r="N76" s="46">
+        <f t="shared" si="23"/>
         <v>3.64500000000001e-7</v>
       </c>
-      <c r="O76" s="44">
-        <f t="shared" si="18"/>
+      <c r="O76" s="46">
+        <f t="shared" si="23"/>
         <v>2.916e-6</v>
       </c>
-      <c r="P76" s="44">
-        <f t="shared" si="18"/>
+      <c r="P76" s="46">
+        <f t="shared" si="23"/>
         <v>2.268e-5</v>
       </c>
-      <c r="Q76" s="44">
-        <f t="shared" si="18"/>
+      <c r="Q76" s="46">
+        <f t="shared" si="23"/>
         <v>0.0001701</v>
       </c>
-      <c r="R76" s="44">
-        <f t="shared" si="18"/>
+      <c r="R76" s="46">
+        <f t="shared" si="23"/>
         <v>0.001215</v>
       </c>
-      <c r="S76" s="44">
-        <f t="shared" si="18"/>
+      <c r="S76" s="46">
+        <f t="shared" si="23"/>
         <v>0.0081</v>
       </c>
-      <c r="T76" s="44">
-        <f t="shared" si="18"/>
+      <c r="T76" s="46">
+        <f t="shared" si="23"/>
         <v>0.0486</v>
       </c>
-      <c r="U76" s="44">
-        <f t="shared" si="18"/>
+      <c r="U76" s="46">
+        <f t="shared" si="23"/>
         <v>0.243</v>
       </c>
-      <c r="V76" s="44">
-        <f t="shared" si="18"/>
+      <c r="V76" s="46">
+        <f t="shared" si="23"/>
         <v>0.81</v>
       </c>
-      <c r="W76" s="44" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="X76" s="44" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Y76" s="44">
-        <f t="shared" si="18"/>
+      <c r="W76" s="46" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="X76" s="46" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="Y76" s="46">
+        <f t="shared" si="23"/>
         <v>8.50500000000002e-12</v>
       </c>
     </row>
@@ -6981,75 +6982,75 @@
       <c r="E77" s="16"/>
       <c r="F77" s="16"/>
       <c r="G77" s="16"/>
-      <c r="H77" s="30">
+      <c r="H77" s="19">
         <v>14</v>
       </c>
-      <c r="I77" s="44">
-        <f t="shared" ref="I77:Y77" si="19">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I77" s="46">
+        <f t="shared" ref="I77:Y77" si="24">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.35e-13</v>
       </c>
-      <c r="J77" s="44">
-        <f t="shared" si="19"/>
+      <c r="J77" s="46">
+        <f t="shared" si="24"/>
         <v>1.26000000000001e-12</v>
       </c>
-      <c r="K77" s="44">
-        <f t="shared" si="19"/>
+      <c r="K77" s="46">
+        <f t="shared" si="24"/>
         <v>1.17e-11</v>
       </c>
-      <c r="L77" s="44">
-        <f t="shared" si="19"/>
+      <c r="L77" s="46">
+        <f t="shared" si="24"/>
         <v>1.08e-10</v>
       </c>
-      <c r="M77" s="44">
-        <f t="shared" si="19"/>
+      <c r="M77" s="46">
+        <f t="shared" si="24"/>
         <v>9.89999999999998e-10</v>
       </c>
-      <c r="N77" s="44">
-        <f t="shared" si="19"/>
+      <c r="N77" s="46">
+        <f t="shared" si="24"/>
         <v>9e-9</v>
       </c>
-      <c r="O77" s="44">
-        <f t="shared" si="19"/>
+      <c r="O77" s="46">
+        <f t="shared" si="24"/>
         <v>8.10000000000002e-8</v>
       </c>
-      <c r="P77" s="44">
-        <f t="shared" si="19"/>
+      <c r="P77" s="46">
+        <f t="shared" si="24"/>
         <v>7.19999999999999e-7</v>
       </c>
-      <c r="Q77" s="44">
-        <f t="shared" si="19"/>
+      <c r="Q77" s="46">
+        <f t="shared" si="24"/>
         <v>6.30000000000001e-6</v>
       </c>
-      <c r="R77" s="44">
-        <f t="shared" si="19"/>
+      <c r="R77" s="46">
+        <f t="shared" si="24"/>
         <v>5.39999999999999e-5</v>
       </c>
-      <c r="S77" s="44">
-        <f t="shared" si="19"/>
+      <c r="S77" s="46">
+        <f t="shared" si="24"/>
         <v>0.000450000000000001</v>
       </c>
-      <c r="T77" s="44">
-        <f t="shared" si="19"/>
+      <c r="T77" s="46">
+        <f t="shared" si="24"/>
         <v>0.0036</v>
       </c>
-      <c r="U77" s="44">
-        <f t="shared" si="19"/>
+      <c r="U77" s="46">
+        <f t="shared" si="24"/>
         <v>0.027</v>
       </c>
-      <c r="V77" s="44">
-        <f t="shared" si="19"/>
+      <c r="V77" s="46">
+        <f t="shared" si="24"/>
         <v>0.18</v>
       </c>
-      <c r="W77" s="44">
-        <f t="shared" si="19"/>
+      <c r="W77" s="46">
+        <f t="shared" si="24"/>
         <v>0.9</v>
       </c>
-      <c r="X77" s="44" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="Y77" s="44">
-        <f t="shared" si="19"/>
+      <c r="X77" s="46" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="Y77" s="46">
+        <f t="shared" si="24"/>
         <v>1.35e-13</v>
       </c>
     </row>
@@ -7061,75 +7062,75 @@
       <c r="E78" s="16"/>
       <c r="F78" s="16"/>
       <c r="G78" s="16"/>
-      <c r="H78" s="30">
+      <c r="H78" s="19">
         <v>15</v>
       </c>
-      <c r="I78" s="44">
-        <f t="shared" ref="I78:Y78" si="20">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I78" s="46">
+        <f t="shared" ref="I78:Y78" si="25">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1e-15</v>
       </c>
-      <c r="J78" s="44">
-        <f t="shared" si="20"/>
+      <c r="J78" s="46">
+        <f t="shared" si="25"/>
         <v>1.00000000000001e-14</v>
       </c>
-      <c r="K78" s="44">
-        <f t="shared" si="20"/>
+      <c r="K78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-13</v>
       </c>
-      <c r="L78" s="44">
-        <f t="shared" si="20"/>
+      <c r="L78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-12</v>
       </c>
-      <c r="M78" s="44">
-        <f t="shared" si="20"/>
+      <c r="M78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-11</v>
       </c>
-      <c r="N78" s="44">
-        <f t="shared" si="20"/>
+      <c r="N78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-10</v>
       </c>
-      <c r="O78" s="44">
-        <f t="shared" si="20"/>
+      <c r="O78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-9</v>
       </c>
-      <c r="P78" s="44">
-        <f t="shared" si="20"/>
+      <c r="P78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-8</v>
       </c>
-      <c r="Q78" s="44">
-        <f t="shared" si="20"/>
+      <c r="Q78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-7</v>
       </c>
-      <c r="R78" s="44">
-        <f t="shared" si="20"/>
+      <c r="R78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-6</v>
       </c>
-      <c r="S78" s="44">
-        <f t="shared" si="20"/>
+      <c r="S78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-5</v>
       </c>
-      <c r="T78" s="44">
-        <f t="shared" si="20"/>
+      <c r="T78" s="46">
+        <f t="shared" si="25"/>
         <v>0.0001</v>
       </c>
-      <c r="U78" s="44">
-        <f t="shared" si="20"/>
+      <c r="U78" s="46">
+        <f t="shared" si="25"/>
         <v>0.001</v>
       </c>
-      <c r="V78" s="44">
-        <f t="shared" si="20"/>
+      <c r="V78" s="46">
+        <f t="shared" si="25"/>
         <v>0.01</v>
       </c>
-      <c r="W78" s="44">
-        <f t="shared" si="20"/>
+      <c r="W78" s="46">
+        <f t="shared" si="25"/>
         <v>0.1</v>
       </c>
-      <c r="X78" s="44">
-        <f t="shared" si="20"/>
+      <c r="X78" s="46">
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
-      <c r="Y78" s="44">
-        <f t="shared" si="20"/>
+      <c r="Y78" s="46">
+        <f t="shared" si="25"/>
         <v>1e-15</v>
       </c>
     </row>
@@ -7167,16 +7168,16 @@
       <c r="D80" s="16"/>
       <c r="E80" s="16"/>
       <c r="F80" s="16"/>
-      <c r="G80" s="46" t="s">
+      <c r="G80" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="H80" s="46"/>
-      <c r="I80" s="46"/>
-      <c r="J80" s="46"/>
-      <c r="K80" s="46"/>
-      <c r="L80" s="46"/>
-      <c r="M80" s="46"/>
-      <c r="N80" s="46"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="49"/>
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
+      <c r="L80" s="49"/>
+      <c r="M80" s="49"/>
+      <c r="N80" s="49"/>
       <c r="O80" s="16"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="16"/>
@@ -7224,22 +7225,22 @@
       <c r="E82" s="16"/>
       <c r="F82" s="16"/>
       <c r="G82" s="16"/>
-      <c r="H82" s="30" t="s">
+      <c r="H82" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="I82" s="30">
+      <c r="I82" s="19">
         <v>1</v>
       </c>
-      <c r="J82" s="30">
+      <c r="J82" s="19">
         <v>2</v>
       </c>
-      <c r="K82" s="30">
+      <c r="K82" s="19">
         <v>3</v>
       </c>
-      <c r="L82" s="30">
+      <c r="L82" s="19">
         <v>4</v>
       </c>
-      <c r="M82" s="30">
+      <c r="M82" s="19">
         <v>5</v>
       </c>
       <c r="N82" s="16"/>
@@ -7263,27 +7264,27 @@
       <c r="E83" s="16"/>
       <c r="F83" s="16"/>
       <c r="G83" s="16"/>
-      <c r="H83" s="30">
+      <c r="H83" s="19">
         <v>0</v>
       </c>
-      <c r="I83" s="47">
-        <f t="shared" ref="I83:I98" si="21">I63</f>
+      <c r="I83" s="50">
+        <f t="shared" ref="I83:I98" si="26">I63</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J83" s="44">
-        <f ca="1" t="shared" ref="J83:J98" si="22">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,J$82-2,$H83+1,1))</f>
+      <c r="J83" s="46">
+        <f ca="1" t="shared" ref="J83:J98" si="27">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,J$82-2,$H83+1,1))</f>
         <v>0.0423911582752162</v>
       </c>
-      <c r="K83" s="44">
-        <f ca="1" t="shared" ref="K83:K98" si="23">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,K$82-2,$H83+1,1))</f>
+      <c r="K83" s="46">
+        <f ca="1" t="shared" ref="K83:K98" si="28">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,K$82-2,$H83+1,1))</f>
         <v>0.00872796356808771</v>
       </c>
-      <c r="L83" s="44">
-        <f ca="1" t="shared" ref="L83:L98" si="24">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,L$82-2,$H83+1,1))</f>
+      <c r="L83" s="46">
+        <f ca="1" t="shared" ref="L83:L98" si="29">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,L$82-2,$H83+1,1))</f>
         <v>0.00179701029991443</v>
       </c>
-      <c r="M83" s="44">
-        <f ca="1" t="shared" ref="M83:M98" si="25">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,M$82-2,$H83+1,1))</f>
+      <c r="M83" s="46">
+        <f ca="1" t="shared" ref="M83:M98" si="30">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,M$82-2,$H83+1,1))</f>
         <v>0.000369988485035127</v>
       </c>
       <c r="N83" s="16"/>
@@ -7307,27 +7308,27 @@
       <c r="E84" s="16"/>
       <c r="F84" s="16"/>
       <c r="G84" s="16"/>
-      <c r="H84" s="30">
+      <c r="H84" s="19">
         <v>1</v>
       </c>
-      <c r="I84" s="47">
-        <f t="shared" si="21"/>
+      <c r="I84" s="50">
+        <f t="shared" si="26"/>
         <v>0.343151886824415</v>
       </c>
-      <c r="J84" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J84" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.149154075412798</v>
       </c>
-      <c r="K84" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K84" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.0486682742171146</v>
       </c>
-      <c r="L84" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L84" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.0141287572505847</v>
       </c>
-      <c r="M84" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M84" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.00384885394774005</v>
       </c>
       <c r="N84" s="16"/>
@@ -7351,27 +7352,27 @@
       <c r="E85" s="16"/>
       <c r="F85" s="16"/>
       <c r="G85" s="16"/>
-      <c r="H85" s="30">
+      <c r="H85" s="19">
         <v>2</v>
       </c>
-      <c r="I85" s="47">
-        <f t="shared" si="21"/>
+      <c r="I85" s="50">
+        <f t="shared" si="26"/>
         <v>0.266895911974545</v>
       </c>
-      <c r="J85" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J85" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.244907309011137</v>
       </c>
-      <c r="K85" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K85" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.126644329478555</v>
       </c>
-      <c r="L85" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L85" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.0518398983833752</v>
       </c>
-      <c r="M85" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M85" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.0186844980625806</v>
       </c>
       <c r="N85" s="16"/>
@@ -7395,28 +7396,28 @@
       <c r="E86" s="16"/>
       <c r="F86" s="16"/>
       <c r="G86" s="16"/>
-      <c r="H86" s="30">
+      <c r="H86" s="19">
         <v>3</v>
       </c>
-      <c r="I86" s="47">
-        <f t="shared" si="21"/>
+      <c r="I86" s="50">
+        <f t="shared" si="26"/>
         <v>0.128505439098855</v>
       </c>
-      <c r="J86" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J86" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.248938705044242</v>
       </c>
-      <c r="K86" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K86" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.204009132488774</v>
       </c>
-      <c r="L86" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L86" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.117746600468707</v>
       </c>
-      <c r="M86" s="44">
-        <f ca="1" t="shared" si="25"/>
-        <v>0.0561507417121914</v>
+      <c r="M86" s="46">
+        <f ca="1" t="shared" si="30"/>
+        <v>0.0561507417121915</v>
       </c>
       <c r="N86" s="16"/>
       <c r="O86" s="16"/>
@@ -7439,27 +7440,27 @@
       <c r="E87" s="16"/>
       <c r="F87" s="16"/>
       <c r="G87" s="16"/>
-      <c r="H87" s="30">
+      <c r="H87" s="19">
         <v>4</v>
       </c>
-      <c r="I87" s="47">
-        <f t="shared" si="21"/>
+      <c r="I87" s="50">
+        <f t="shared" si="26"/>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J87" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J87" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.175179088734837</v>
       </c>
-      <c r="K87" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K87" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.227516357631513</v>
       </c>
-      <c r="L87" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L87" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.185153433475941</v>
       </c>
-      <c r="M87" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M87" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.116823097284761</v>
       </c>
       <c r="N87" s="16"/>
@@ -7483,27 +7484,27 @@
       <c r="E88" s="16"/>
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
-      <c r="H88" s="30">
+      <c r="H88" s="19">
         <v>5</v>
       </c>
-      <c r="I88" s="47">
-        <f t="shared" si="21"/>
+      <c r="I88" s="50">
+        <f t="shared" si="26"/>
         <v>0.010470813556203</v>
       </c>
-      <c r="J88" s="48">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J88" s="51">
+        <f ca="1" t="shared" si="27"/>
         <v>0.0904010606063728</v>
       </c>
-      <c r="K88" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K88" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.186070305102755</v>
       </c>
-      <c r="L88" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L88" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.213509197834518</v>
       </c>
-      <c r="M88" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M88" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.178239256298975</v>
       </c>
       <c r="N88" s="16"/>
@@ -7527,27 +7528,27 @@
       <c r="E89" s="16"/>
       <c r="F89" s="16"/>
       <c r="G89" s="16"/>
-      <c r="H89" s="30">
+      <c r="H89" s="19">
         <v>6</v>
       </c>
-      <c r="I89" s="44">
-        <f t="shared" si="21"/>
+      <c r="I89" s="46">
+        <f t="shared" si="26"/>
         <v>0.001939039547445</v>
       </c>
-      <c r="J89" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J89" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.0353419784263597</v>
       </c>
-      <c r="K89" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K89" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.115283613815378</v>
       </c>
-      <c r="L89" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L89" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.186520888927731</v>
       </c>
-      <c r="M89" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M89" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.206017482223783</v>
       </c>
       <c r="N89" s="16"/>
@@ -7571,27 +7572,27 @@
       <c r="E90" s="16"/>
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
-      <c r="H90" s="30">
+      <c r="H90" s="19">
         <v>7</v>
       </c>
-      <c r="I90" s="44">
-        <f t="shared" si="21"/>
+      <c r="I90" s="46">
+        <f t="shared" si="26"/>
         <v>0.000277005649635</v>
       </c>
-      <c r="J90" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J90" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.0106586919063625</v>
       </c>
-      <c r="K90" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K90" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.0551002810299252</v>
       </c>
-      <c r="L90" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L90" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.125699654521354</v>
       </c>
-      <c r="M90" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M90" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.183696342337757</v>
       </c>
       <c r="N90" s="16"/>
@@ -7615,27 +7616,27 @@
       <c r="E91" s="16"/>
       <c r="F91" s="16"/>
       <c r="G91" s="16"/>
-      <c r="H91" s="30">
+      <c r="H91" s="19">
         <v>8</v>
       </c>
-      <c r="I91" s="44">
-        <f t="shared" si="21"/>
+      <c r="I91" s="46">
+        <f t="shared" si="26"/>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J91" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J91" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.00250018699038132</v>
       </c>
-      <c r="K91" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K91" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.0204830948684633</v>
       </c>
-      <c r="L91" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L91" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.0658864672914092</v>
       </c>
-      <c r="M91" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M91" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.127395026419981</v>
       </c>
       <c r="N91" s="16"/>
@@ -7659,27 +7660,27 @@
       <c r="E92" s="16"/>
       <c r="F92" s="16"/>
       <c r="G92" s="16"/>
-      <c r="H92" s="30">
+      <c r="H92" s="19">
         <v>9</v>
       </c>
-      <c r="I92" s="44">
-        <f t="shared" si="21"/>
+      <c r="I92" s="46">
+        <f t="shared" si="26"/>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J92" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J92" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>0.00045613836724378</v>
       </c>
-      <c r="K92" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K92" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.00592233363290273</v>
       </c>
-      <c r="L92" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L92" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.0268604875121694</v>
       </c>
-      <c r="M92" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M92" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.0687163318006563</v>
       </c>
       <c r="N92" s="16"/>
@@ -7703,27 +7704,27 @@
       <c r="E93" s="16"/>
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
-      <c r="H93" s="30">
+      <c r="H93" s="19">
         <v>10</v>
       </c>
-      <c r="I93" s="44">
-        <f t="shared" si="21"/>
+      <c r="I93" s="46">
+        <f t="shared" si="26"/>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J93" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J93" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>6.41972516861615e-5</v>
       </c>
-      <c r="K93" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K93" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.00132094848931411</v>
       </c>
-      <c r="L93" s="44">
-        <f ca="1" t="shared" si="24"/>
-        <v>0.0084474820808734</v>
-      </c>
-      <c r="M93" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="L93" s="46">
+        <f ca="1" t="shared" si="29"/>
+        <v>0.00844748208087341</v>
+      </c>
+      <c r="M93" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.0285932276946469</v>
       </c>
       <c r="N93" s="16"/>
@@ -7747,28 +7748,28 @@
       <c r="E94" s="16"/>
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
-      <c r="H94" s="30">
+      <c r="H94" s="19">
         <v>11</v>
       </c>
-      <c r="I94" s="44">
-        <f t="shared" si="21"/>
+      <c r="I94" s="46">
+        <f t="shared" si="26"/>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J94" s="44">
-        <f ca="1" t="shared" si="22"/>
-        <v>6.84482481502283e-6</v>
-      </c>
-      <c r="K94" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="J94" s="46">
+        <f ca="1" t="shared" si="27"/>
+        <v>6.84482481502284e-6</v>
+      </c>
+      <c r="K94" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>0.000223205537226664</v>
       </c>
-      <c r="L94" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L94" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.00201264295050115</v>
       </c>
-      <c r="M94" s="44">
-        <f ca="1" t="shared" si="25"/>
-        <v>0.00901347930858259</v>
+      <c r="M94" s="46">
+        <f ca="1" t="shared" si="30"/>
+        <v>0.0090134793085826</v>
       </c>
       <c r="N94" s="16"/>
       <c r="O94" s="16"/>
@@ -7791,27 +7792,27 @@
       <c r="E95" s="16"/>
       <c r="F95" s="16"/>
       <c r="G95" s="16"/>
-      <c r="H95" s="30">
+      <c r="H95" s="19">
         <v>12</v>
       </c>
-      <c r="I95" s="44">
-        <f t="shared" si="21"/>
+      <c r="I95" s="46">
+        <f t="shared" si="26"/>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J95" s="44">
-        <f ca="1" t="shared" si="22"/>
-        <v>5.35192063726065e-7</v>
-      </c>
-      <c r="K95" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="J95" s="46">
+        <f ca="1" t="shared" si="27"/>
+        <v>5.35192063726066e-7</v>
+      </c>
+      <c r="K95" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>2.76582993088367e-5</v>
       </c>
-      <c r="L95" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L95" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>0.000351647569312272</v>
       </c>
-      <c r="M95" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M95" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.00208364234881633</v>
       </c>
       <c r="N95" s="16"/>
@@ -7835,27 +7836,27 @@
       <c r="E96" s="16"/>
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
-      <c r="H96" s="30">
+      <c r="H96" s="19">
         <v>13</v>
       </c>
-      <c r="I96" s="44">
-        <f t="shared" si="21"/>
+      <c r="I96" s="46">
+        <f t="shared" si="26"/>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J96" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J96" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>2.89705105720662e-8</v>
       </c>
-      <c r="K96" s="44">
-        <f ca="1" t="shared" si="23"/>
-        <v>2.3727126029423e-6</v>
-      </c>
-      <c r="L96" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="K96" s="46">
+        <f ca="1" t="shared" si="28"/>
+        <v>2.37271260294231e-6</v>
+      </c>
+      <c r="L96" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>4.25351197940594e-5</v>
       </c>
-      <c r="M96" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M96" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>0.000333467138086273</v>
       </c>
       <c r="N96" s="16"/>
@@ -7879,27 +7880,27 @@
       <c r="E97" s="16"/>
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
-      <c r="H97" s="30">
+      <c r="H97" s="19">
         <v>14</v>
       </c>
-      <c r="I97" s="44">
-        <f t="shared" si="21"/>
+      <c r="I97" s="46">
+        <f t="shared" si="26"/>
         <v>1.35e-13</v>
       </c>
-      <c r="J97" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J97" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>9.70793123226205e-10</v>
       </c>
-      <c r="K97" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K97" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>1.26005313618923e-7</v>
       </c>
-      <c r="L97" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L97" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>3.18501702640648e-6</v>
       </c>
-      <c r="M97" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M97" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>3.30374840550607e-5</v>
       </c>
       <c r="N97" s="16"/>
@@ -7923,27 +7924,27 @@
       <c r="E98" s="16"/>
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
-      <c r="H98" s="30">
+      <c r="H98" s="19">
         <v>15</v>
       </c>
-      <c r="I98" s="44">
-        <f t="shared" si="21"/>
+      <c r="I98" s="46">
+        <f t="shared" si="26"/>
         <v>1e-15</v>
       </c>
-      <c r="J98" s="44">
-        <f ca="1" t="shared" si="22"/>
+      <c r="J98" s="46">
+        <f ca="1" t="shared" si="27"/>
         <v>1.51811270298748e-11</v>
       </c>
-      <c r="K98" s="44">
-        <f ca="1" t="shared" si="23"/>
+      <c r="K98" s="46">
+        <f ca="1" t="shared" si="28"/>
         <v>3.12276543125086e-9</v>
       </c>
-      <c r="L98" s="44">
-        <f ca="1" t="shared" si="24"/>
+      <c r="L98" s="46">
+        <f ca="1" t="shared" si="29"/>
         <v>1.11296789654137e-7</v>
       </c>
-      <c r="M98" s="44">
-        <f ca="1" t="shared" si="25"/>
+      <c r="M98" s="46">
+        <f ca="1" t="shared" si="30"/>
         <v>1.52745235260974e-6</v>
       </c>
       <c r="N98" s="16"/>
@@ -7967,26 +7968,26 @@
       <c r="E99" s="16"/>
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
-      <c r="H99" s="30" t="s">
+      <c r="H99" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="I99" s="44">
+      <c r="I99" s="46">
         <f>SUM(I83:I98)</f>
         <v>1</v>
       </c>
-      <c r="J99" s="44">
+      <c r="J99" s="46">
         <f ca="1">SUM(J83:J98)</f>
         <v>1</v>
       </c>
-      <c r="K99" s="44">
+      <c r="K99" s="46">
         <f ca="1">SUM(K83:K98)</f>
         <v>1</v>
       </c>
-      <c r="L99" s="44">
+      <c r="L99" s="46">
         <f ca="1">SUM(L83:L98)</f>
         <v>1</v>
       </c>
-      <c r="M99" s="44">
+      <c r="M99" s="46">
         <f ca="1">SUM(M83:M98)</f>
         <v>1</v>
       </c>
@@ -8030,11 +8031,11 @@
       <c r="X100" s="16"/>
       <c r="Y100" s="16"/>
     </row>
-    <row r="101" ht="60" customHeight="1" spans="1:25">
-      <c r="A101" s="49" t="s">
+    <row r="101" ht="102" customHeight="1" spans="1:25">
+      <c r="A101" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="B101" s="44">
+      <c r="B101" s="46">
         <f ca="1">SUM(M88:M98)</f>
         <v>0.804122820507692</v>
       </c>
@@ -8085,7 +8086,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A36:Y101 A1:Y3 A4:F4 H4:Y4 A5:Y5 A6:F6 H6:Y6 A7 C7:Y7 A8:Y22 A23 C23:Y23 A24:Y27 A28:G34 A35:C35 E35:G35 S28:Y35" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="S28:Y35 E35:G35 A35:C35 A28:G34 A24:Y27 C23:Y23 A23 A8:Y22 C7:Y7 A7 H6:Y6 A6:F6 A5:Y5 H4:Y4 A4:F4 A1:Y3 A36:Y101" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/游戏设计王/老虎机数学专题-二项分配机率.xlsx
+++ b/游戏设计王/老虎机数学专题-二项分配机率.xlsx
@@ -1386,7 +1386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1499,9 +1499,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1563,6 +1560,23 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" applyNumberFormat="1" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2155,44 +2169,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A3" s="55"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:10">
       <c r="A4" s="29" t="s">
@@ -2200,56 +2214,56 @@
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A5" s="55"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="54"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="54"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2260,64 +2274,64 @@
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
     </row>
     <row r="10" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A10" s="55"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A13" s="55"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:10">
       <c r="A14" s="29" t="s">
@@ -2328,1210 +2342,1210 @@
       <c r="D14" s="29"/>
       <c r="E14" s="29"/>
       <c r="F14" s="29"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="54"/>
-      <c r="J14" s="54"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A15" s="55"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
+      <c r="A15" s="54"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="53"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:10">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
     </row>
     <row r="18" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A18" s="59"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
+      <c r="A18" s="58"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A20" s="60" t="s">
+      <c r="A20" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
     </row>
     <row r="22" ht="33" customHeight="1" spans="1:10">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A23" s="62" t="s">
+      <c r="A23" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A24" s="59"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A27" s="63" t="s">
+      <c r="A27" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A28" s="63" t="s">
+      <c r="A28" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:10">
-      <c r="A30" s="64" t="s">
+      <c r="A30" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="65" t="s">
+      <c r="B30" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="67" t="s">
+      <c r="B31" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="58"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="57"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="67"/>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="58"/>
+      <c r="C32" s="66"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="67" t="s">
+      <c r="B33" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="67"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="67" t="s">
+      <c r="B34" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="67"/>
-      <c r="D34" s="67"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
     </row>
     <row r="35" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A35" s="59"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
     </row>
     <row r="37" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A37" s="59"/>
-      <c r="B37" s="58"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="58"/>
+      <c r="A37" s="58"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="63" t="s">
+      <c r="A38" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:10">
-      <c r="A39" s="64" t="s">
+      <c r="A39" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="65" t="s">
+      <c r="B39" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="65" t="s">
+      <c r="C39" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="65" t="s">
+      <c r="D39" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="65" t="s">
+      <c r="E39" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="65" t="s">
+      <c r="F39" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="58"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="68">
+      <c r="B40" s="67">
         <v>0.1</v>
       </c>
-      <c r="C40" s="68">
+      <c r="C40" s="67">
         <v>0.15</v>
       </c>
-      <c r="D40" s="68">
+      <c r="D40" s="67">
         <v>0.2</v>
       </c>
-      <c r="E40" s="68">
+      <c r="E40" s="67">
         <v>0.25</v>
       </c>
-      <c r="F40" s="68">
+      <c r="F40" s="67">
         <v>0.3</v>
       </c>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
     </row>
     <row r="41" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A41" s="59"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
+      <c r="A41" s="58"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="63" t="s">
+      <c r="A42" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="58"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A43" s="62" t="s">
+      <c r="A43" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
-      <c r="J43" s="58"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
     </row>
     <row r="44" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A44" s="59"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
-      <c r="J44" s="58"/>
+      <c r="A44" s="58"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
     </row>
     <row r="45" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="61" t="s">
+      <c r="A45" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="61"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
-      <c r="J45" s="58"/>
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="63" t="s">
+      <c r="A46" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
-      <c r="J46" s="58"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A47" s="63" t="s">
+      <c r="A47" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="58"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
     </row>
     <row r="48" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A48" s="69" t="s">
+      <c r="A48" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="69"/>
-      <c r="C48" s="69"/>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="69"/>
-      <c r="I48" s="69"/>
-      <c r="J48" s="69"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="68"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="68"/>
+      <c r="J48" s="68"/>
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A49" s="62" t="s">
+      <c r="A49" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="58"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="57"/>
     </row>
     <row r="50" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A50" s="59"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="58"/>
+      <c r="A50" s="58"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="57"/>
     </row>
     <row r="51" ht="33" customHeight="1" spans="1:10">
-      <c r="A51" s="61" t="s">
+      <c r="A51" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="58"/>
+      <c r="B51" s="60"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="60"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A52" s="63" t="s">
+      <c r="A52" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
-      <c r="J52" s="58"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A53" s="63" t="s">
+      <c r="A53" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
-      <c r="J53" s="58"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A54" s="63" t="s">
+      <c r="A54" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="58"/>
-      <c r="I54" s="58"/>
-      <c r="J54" s="58"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="57"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="58"/>
-      <c r="H55" s="58"/>
-      <c r="I55" s="58"/>
-      <c r="J55" s="58"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A56" s="62" t="s">
+      <c r="A56" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="58"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
-      <c r="F56" s="58"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="58"/>
-      <c r="J56" s="58"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
     </row>
     <row r="57" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A57" s="59"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="58"/>
-      <c r="G57" s="58"/>
-      <c r="H57" s="58"/>
-      <c r="I57" s="58"/>
-      <c r="J57" s="58"/>
+      <c r="A57" s="58"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
     </row>
     <row r="58" ht="33" customHeight="1" spans="1:10">
-      <c r="A58" s="61" t="s">
+      <c r="A58" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="58"/>
-      <c r="G58" s="58"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="58"/>
-      <c r="J58" s="58"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A59" s="63" t="s">
+      <c r="A59" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="58"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="58"/>
-      <c r="F59" s="58"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="58"/>
-      <c r="I59" s="58"/>
-      <c r="J59" s="58"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A60" s="61" t="s">
+      <c r="A60" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="61"/>
-      <c r="C60" s="61"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="58"/>
-      <c r="I60" s="58"/>
-      <c r="J60" s="58"/>
+      <c r="B60" s="60"/>
+      <c r="C60" s="60"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A61" s="63" t="s">
+      <c r="A61" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="58"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="58"/>
-      <c r="I61" s="58"/>
-      <c r="J61" s="58"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A62" s="63" t="s">
+      <c r="A62" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
-      <c r="J62" s="58"/>
+      <c r="B62" s="57"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="57"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A63" s="63" t="s">
+      <c r="A63" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="58"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="58"/>
-      <c r="J63" s="58"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="57"/>
+      <c r="J63" s="57"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A64" s="63" t="s">
+      <c r="A64" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="B64" s="58"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58"/>
-      <c r="I64" s="58"/>
-      <c r="J64" s="58"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
+      <c r="J64" s="57"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A65" s="63" t="s">
+      <c r="A65" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="B65" s="58"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
-      <c r="J65" s="58"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="57"/>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:22">
-      <c r="A66" s="70" t="s">
+      <c r="A66" s="69" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A67" s="63" t="s">
+      <c r="A67" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="58"/>
-      <c r="J67" s="58"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
+      <c r="J67" s="57"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A68" s="63" t="s">
+      <c r="A68" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="58"/>
-      <c r="J68" s="58"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
+      <c r="J68" s="57"/>
     </row>
     <row r="69" ht="33" customHeight="1" spans="1:22">
-      <c r="A69" s="61" t="s">
+      <c r="A69" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58"/>
-      <c r="I69" s="58"/>
-      <c r="J69" s="58"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="57"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="57"/>
+      <c r="J69" s="57"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A70" s="63" t="s">
+      <c r="A70" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="58"/>
-      <c r="J70" s="58"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
+      <c r="J70" s="57"/>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:22">
-      <c r="A71" s="71" t="s">
+      <c r="A71" s="70" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A72" s="62" t="s">
+      <c r="A72" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="58"/>
-      <c r="C72" s="58"/>
-      <c r="D72" s="58"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="58"/>
-      <c r="G72" s="58"/>
-      <c r="H72" s="58"/>
-      <c r="I72" s="58"/>
-      <c r="J72" s="58"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="57"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
     </row>
     <row r="73" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A73" s="59"/>
-      <c r="B73" s="58"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
-      <c r="J73" s="58"/>
+      <c r="A73" s="58"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="57"/>
+      <c r="F73" s="57"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
+      <c r="J73" s="57"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A74" s="63" t="s">
+      <c r="A74" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="58"/>
-      <c r="C74" s="58"/>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="58"/>
-      <c r="H74" s="58"/>
-      <c r="I74" s="58"/>
-      <c r="J74" s="58"/>
+      <c r="B74" s="57"/>
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="57"/>
+      <c r="J74" s="57"/>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:22">
-      <c r="A75" s="64" t="s">
+      <c r="A75" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="58"/>
-      <c r="D75" s="58"/>
-      <c r="E75" s="58"/>
-      <c r="F75" s="58"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="58"/>
-      <c r="I75" s="58"/>
-      <c r="J75" s="58"/>
+      <c r="C75" s="57"/>
+      <c r="D75" s="57"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="57"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
+      <c r="J75" s="57"/>
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:22">
-      <c r="A76" s="66" t="s">
+      <c r="A76" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="B76" s="67" t="s">
+      <c r="B76" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="C76" s="67"/>
-      <c r="D76" s="58"/>
-      <c r="E76" s="58"/>
-      <c r="F76" s="58"/>
-      <c r="G76" s="58"/>
-      <c r="H76" s="58"/>
-      <c r="I76" s="58"/>
-      <c r="J76" s="58"/>
+      <c r="C76" s="66"/>
+      <c r="D76" s="57"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="57"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="57"/>
+      <c r="I76" s="57"/>
+      <c r="J76" s="57"/>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:22">
-      <c r="A77" s="66" t="s">
+      <c r="A77" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="72" t="s">
+      <c r="B77" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="72"/>
-      <c r="D77" s="72"/>
-      <c r="E77" s="72"/>
-      <c r="F77" s="72"/>
-      <c r="G77" s="72"/>
-      <c r="H77" s="72"/>
-      <c r="I77" s="72"/>
-      <c r="J77" s="72"/>
-      <c r="K77" s="72"/>
-      <c r="L77" s="72"/>
-      <c r="M77" s="72"/>
-      <c r="N77" s="72"/>
-      <c r="O77" s="72"/>
-      <c r="P77" s="72"/>
-      <c r="Q77" s="72"/>
-      <c r="R77" s="72"/>
-      <c r="S77" s="72"/>
-      <c r="T77" s="72"/>
-      <c r="U77" s="72"/>
-      <c r="V77" s="72"/>
+      <c r="C77" s="71"/>
+      <c r="D77" s="71"/>
+      <c r="E77" s="71"/>
+      <c r="F77" s="71"/>
+      <c r="G77" s="71"/>
+      <c r="H77" s="71"/>
+      <c r="I77" s="71"/>
+      <c r="J77" s="71"/>
+      <c r="K77" s="71"/>
+      <c r="L77" s="71"/>
+      <c r="M77" s="71"/>
+      <c r="N77" s="71"/>
+      <c r="O77" s="71"/>
+      <c r="P77" s="71"/>
+      <c r="Q77" s="71"/>
+      <c r="R77" s="71"/>
+      <c r="S77" s="71"/>
+      <c r="T77" s="71"/>
+      <c r="U77" s="71"/>
+      <c r="V77" s="71"/>
     </row>
     <row r="78" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A78" s="59"/>
-      <c r="B78" s="58"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="58"/>
-      <c r="G78" s="58"/>
-      <c r="H78" s="58"/>
-      <c r="I78" s="58"/>
-      <c r="J78" s="58"/>
+      <c r="A78" s="58"/>
+      <c r="B78" s="57"/>
+      <c r="C78" s="57"/>
+      <c r="D78" s="57"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="57"/>
+      <c r="J78" s="57"/>
     </row>
     <row r="79" ht="33" customHeight="1" spans="1:22">
-      <c r="A79" s="61" t="s">
+      <c r="A79" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="58"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="58"/>
-      <c r="I79" s="58"/>
-      <c r="J79" s="58"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="60"/>
+      <c r="E79" s="60"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
+      <c r="J79" s="57"/>
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="58"/>
-      <c r="C80" s="58"/>
-      <c r="D80" s="58"/>
-      <c r="E80" s="58"/>
-      <c r="F80" s="58"/>
-      <c r="G80" s="58"/>
-      <c r="H80" s="58"/>
-      <c r="I80" s="58"/>
-      <c r="J80" s="58"/>
+      <c r="B80" s="57"/>
+      <c r="C80" s="57"/>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="57"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="57"/>
+      <c r="I80" s="57"/>
+      <c r="J80" s="57"/>
     </row>
     <row r="81" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A81" s="59"/>
-      <c r="B81" s="58"/>
-      <c r="C81" s="58"/>
-      <c r="D81" s="58"/>
-      <c r="E81" s="58"/>
-      <c r="F81" s="58"/>
-      <c r="G81" s="58"/>
-      <c r="H81" s="58"/>
-      <c r="I81" s="58"/>
-      <c r="J81" s="58"/>
+      <c r="A81" s="58"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
+      <c r="G81" s="57"/>
+      <c r="H81" s="57"/>
+      <c r="I81" s="57"/>
+      <c r="J81" s="57"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A82" s="63" t="s">
+      <c r="A82" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="58"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="58"/>
-      <c r="F82" s="58"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="58"/>
-      <c r="I82" s="58"/>
-      <c r="J82" s="58"/>
+      <c r="B82" s="57"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="57"/>
+      <c r="G82" s="57"/>
+      <c r="H82" s="57"/>
+      <c r="I82" s="57"/>
+      <c r="J82" s="57"/>
     </row>
     <row r="83" ht="33" customHeight="1" spans="1:10">
-      <c r="A83" s="61" t="s">
+      <c r="A83" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="58"/>
-      <c r="J83" s="58"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="57"/>
+      <c r="G83" s="57"/>
+      <c r="H83" s="57"/>
+      <c r="I83" s="57"/>
+      <c r="J83" s="57"/>
     </row>
     <row r="84" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A84" s="61" t="s">
+      <c r="A84" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="B84" s="61"/>
-      <c r="C84" s="61"/>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
-      <c r="I84" s="61"/>
-      <c r="J84" s="58"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="60"/>
+      <c r="D84" s="60"/>
+      <c r="E84" s="60"/>
+      <c r="F84" s="60"/>
+      <c r="G84" s="60"/>
+      <c r="H84" s="60"/>
+      <c r="I84" s="60"/>
+      <c r="J84" s="57"/>
     </row>
     <row r="85" ht="33" customHeight="1" spans="1:10">
-      <c r="A85" s="61" t="s">
+      <c r="A85" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="B85" s="61"/>
-      <c r="C85" s="61"/>
-      <c r="D85" s="61"/>
-      <c r="E85" s="61"/>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="58"/>
-      <c r="I85" s="58"/>
-      <c r="J85" s="58"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="60"/>
+      <c r="H85" s="57"/>
+      <c r="I85" s="57"/>
+      <c r="J85" s="57"/>
     </row>
     <row r="86" ht="33" customHeight="1" spans="1:10">
-      <c r="A86" s="61" t="s">
+      <c r="A86" s="60" t="s">
         <v>81</v>
       </c>
-      <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
-      <c r="D86" s="61"/>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
-      <c r="J86" s="58"/>
+      <c r="B86" s="60"/>
+      <c r="C86" s="60"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A87" s="62" t="s">
+      <c r="A87" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="B87" s="58"/>
-      <c r="C87" s="58"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58"/>
-      <c r="I87" s="58"/>
-      <c r="J87" s="58"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="57"/>
+      <c r="G87" s="57"/>
+      <c r="H87" s="57"/>
+      <c r="I87" s="57"/>
+      <c r="J87" s="57"/>
     </row>
     <row r="88" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A88" s="59"/>
-      <c r="B88" s="58"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
-      <c r="E88" s="58"/>
-      <c r="F88" s="58"/>
-      <c r="G88" s="58"/>
-      <c r="H88" s="58"/>
-      <c r="I88" s="58"/>
-      <c r="J88" s="58"/>
+      <c r="A88" s="58"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="57"/>
+      <c r="H88" s="57"/>
+      <c r="I88" s="57"/>
+      <c r="J88" s="57"/>
     </row>
     <row r="89" ht="18" customHeight="1" spans="1:10">
-      <c r="A89" s="64" t="s">
+      <c r="A89" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="65" t="s">
+      <c r="B89" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="C89" s="58"/>
-      <c r="D89" s="58"/>
-      <c r="E89" s="58"/>
-      <c r="F89" s="58"/>
-      <c r="G89" s="58"/>
-      <c r="H89" s="58"/>
-      <c r="I89" s="58"/>
-      <c r="J89" s="58"/>
+      <c r="C89" s="57"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="57"/>
+      <c r="G89" s="57"/>
+      <c r="H89" s="57"/>
+      <c r="I89" s="57"/>
+      <c r="J89" s="57"/>
     </row>
     <row r="90" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A90" s="66" t="s">
+      <c r="A90" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="73" t="s">
+      <c r="B90" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
-      <c r="E90" s="58"/>
-      <c r="F90" s="58"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="58"/>
-      <c r="I90" s="58"/>
-      <c r="J90" s="58"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="57"/>
+      <c r="G90" s="57"/>
+      <c r="H90" s="57"/>
+      <c r="I90" s="57"/>
+      <c r="J90" s="57"/>
     </row>
     <row r="91" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A91" s="66" t="s">
+      <c r="A91" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B91" s="67" t="s">
+      <c r="B91" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C91" s="67"/>
-      <c r="D91" s="58"/>
-      <c r="E91" s="58"/>
-      <c r="F91" s="58"/>
-      <c r="G91" s="58"/>
-      <c r="H91" s="58"/>
-      <c r="I91" s="58"/>
-      <c r="J91" s="58"/>
+      <c r="C91" s="66"/>
+      <c r="D91" s="57"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="57"/>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57"/>
+      <c r="I91" s="57"/>
+      <c r="J91" s="57"/>
     </row>
     <row r="92" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A92" s="66" t="s">
+      <c r="A92" s="65" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="67" t="s">
+      <c r="B92" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="67"/>
-      <c r="D92" s="58"/>
-      <c r="E92" s="58"/>
-      <c r="F92" s="58"/>
-      <c r="G92" s="58"/>
-      <c r="H92" s="58"/>
-      <c r="I92" s="58"/>
-      <c r="J92" s="58"/>
+      <c r="C92" s="66"/>
+      <c r="D92" s="57"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="57"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="57"/>
+      <c r="J92" s="57"/>
     </row>
     <row r="93" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A93" s="66" t="s">
+      <c r="A93" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="B93" s="67" t="s">
+      <c r="B93" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="67"/>
-      <c r="D93" s="58"/>
-      <c r="E93" s="58"/>
-      <c r="F93" s="58"/>
-      <c r="G93" s="58"/>
-      <c r="H93" s="58"/>
-      <c r="I93" s="58"/>
-      <c r="J93" s="58"/>
+      <c r="C93" s="66"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
+      <c r="J93" s="57"/>
     </row>
     <row r="94" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A94" s="66" t="s">
+      <c r="A94" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="67" t="s">
+      <c r="B94" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="67"/>
-      <c r="D94" s="58"/>
-      <c r="E94" s="58"/>
-      <c r="F94" s="58"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="58"/>
-      <c r="I94" s="58"/>
-      <c r="J94" s="58"/>
+      <c r="C94" s="66"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="57"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57"/>
+      <c r="I94" s="57"/>
+      <c r="J94" s="57"/>
     </row>
     <row r="95" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A95" s="66" t="s">
+      <c r="A95" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="67" t="s">
+      <c r="B95" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="67"/>
-      <c r="D95" s="58"/>
-      <c r="E95" s="58"/>
-      <c r="F95" s="58"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="58"/>
-      <c r="I95" s="58"/>
-      <c r="J95" s="58"/>
+      <c r="C95" s="66"/>
+      <c r="D95" s="57"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="57"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="57"/>
+      <c r="I95" s="57"/>
+      <c r="J95" s="57"/>
     </row>
     <row r="96" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A96" s="66" t="s">
+      <c r="A96" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="67" t="s">
+      <c r="B96" s="66" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="67"/>
-      <c r="D96" s="58"/>
-      <c r="E96" s="58"/>
-      <c r="F96" s="58"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="58"/>
-      <c r="I96" s="58"/>
-      <c r="J96" s="58"/>
+      <c r="C96" s="66"/>
+      <c r="D96" s="57"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
+      <c r="G96" s="57"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="57"/>
+      <c r="J96" s="57"/>
     </row>
     <row r="97" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A97" s="66" t="s">
+      <c r="A97" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="B97" s="67" t="s">
+      <c r="B97" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="C97" s="67"/>
-      <c r="D97" s="58"/>
-      <c r="E97" s="58"/>
-      <c r="F97" s="58"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="58"/>
-      <c r="I97" s="58"/>
-      <c r="J97" s="58"/>
+      <c r="C97" s="66"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="57"/>
+      <c r="J97" s="57"/>
     </row>
     <row r="98" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A98" s="66" t="s">
+      <c r="A98" s="65" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="67" t="s">
+      <c r="B98" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="C98" s="67"/>
-      <c r="D98" s="58"/>
-      <c r="E98" s="58"/>
-      <c r="F98" s="58"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="58"/>
-      <c r="I98" s="58"/>
-      <c r="J98" s="58"/>
+      <c r="C98" s="66"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="57"/>
+      <c r="J98" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -3570,7 +3584,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A3:V98 B2:V2 A1:V1" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:V1 B2:V2 A3:V98" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4513,23 +4527,23 @@
       <c r="A23" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="77">
         <f>SUM(B7:B22)</f>
         <v>1</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="77">
         <f>SUM(C7:C22)</f>
         <v>1</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="77">
         <f>SUM(D7:D22)</f>
         <v>1</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="77">
         <f>SUM(E7:E22)</f>
         <v>1</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="77">
         <f>SUM(F7:F22)</f>
         <v>1</v>
       </c>
@@ -5754,10 +5768,10 @@
     <row r="62" ht="16.5" customHeight="1" spans="1:25">
       <c r="A62" s="16"/>
       <c r="B62" s="43"/>
-      <c r="C62" s="44" t="s">
+      <c r="C62" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="38" t="s">
         <v>39</v>
       </c>
       <c r="E62" s="16"/>
@@ -5826,7 +5840,7 @@
       <c r="C63" s="43">
         <v>10</v>
       </c>
-      <c r="D63" s="45">
+      <c r="D63" s="44">
         <v>0.1</v>
       </c>
       <c r="E63" s="16"/>
@@ -5837,71 +5851,71 @@
       <c r="H63" s="19">
         <v>0</v>
       </c>
-      <c r="I63" s="46">
+      <c r="I63" s="45">
         <f t="shared" ref="I63:Y63" si="10">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J63" s="47" t="str">
+      <c r="J63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="K63" s="47" t="str">
+      <c r="K63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="L63" s="47" t="str">
+      <c r="L63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M63" s="47" t="str">
+      <c r="M63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N63" s="47" t="str">
+      <c r="N63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O63" s="47" t="str">
+      <c r="O63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P63" s="47" t="str">
+      <c r="P63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q63" s="47" t="str">
+      <c r="Q63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="R63" s="47" t="str">
+      <c r="R63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="S63" s="47" t="str">
+      <c r="S63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="T63" s="47" t="str">
+      <c r="T63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="U63" s="47" t="str">
+      <c r="U63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V63" s="47" t="str">
+      <c r="V63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="W63" s="47" t="str">
+      <c r="W63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="X63" s="47" t="str">
+      <c r="X63" s="80" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Y63" s="46">
+      <c r="Y63" s="45">
         <f t="shared" si="10"/>
         <v>0.205891132094649</v>
       </c>
@@ -5914,7 +5928,7 @@
       <c r="C64" s="43">
         <v>15</v>
       </c>
-      <c r="D64" s="45">
+      <c r="D64" s="44">
         <v>0.15</v>
       </c>
       <c r="E64" s="16"/>
@@ -5923,71 +5937,71 @@
       <c r="H64" s="19">
         <v>1</v>
       </c>
-      <c r="I64" s="46">
+      <c r="I64" s="45">
         <f t="shared" ref="I64:Y64" si="11">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.343151886824415</v>
       </c>
-      <c r="J64" s="46">
+      <c r="J64" s="45">
         <f t="shared" si="11"/>
         <v>0.22876792454961</v>
       </c>
-      <c r="K64" s="46" t="str">
+      <c r="K64" s="45" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="L64" s="46" t="str">
+      <c r="L64" s="45" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="M64" s="46" t="str">
+      <c r="M64" s="45" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="N64" s="47" t="str">
+      <c r="N64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O64" s="47" t="str">
+      <c r="O64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="P64" s="47" t="str">
+      <c r="P64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q64" s="47" t="str">
+      <c r="Q64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="R64" s="47" t="str">
+      <c r="R64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="S64" s="47" t="str">
+      <c r="S64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="T64" s="47" t="str">
+      <c r="T64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="U64" s="47" t="str">
+      <c r="U64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="V64" s="47" t="str">
+      <c r="V64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="W64" s="47" t="str">
+      <c r="W64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="X64" s="47" t="str">
+      <c r="X64" s="80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Y64" s="46">
+      <c r="Y64" s="45">
         <f t="shared" si="11"/>
         <v>0.343151886824415</v>
       </c>
@@ -6000,7 +6014,7 @@
       <c r="C65" s="43">
         <v>20</v>
       </c>
-      <c r="D65" s="45">
+      <c r="D65" s="44">
         <v>0.2</v>
       </c>
       <c r="E65" s="16"/>
@@ -6009,71 +6023,71 @@
       <c r="H65" s="19">
         <v>2</v>
       </c>
-      <c r="I65" s="46">
+      <c r="I65" s="45">
         <f t="shared" ref="I65:Y65" si="12">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.266895911974545</v>
       </c>
-      <c r="J65" s="46">
+      <c r="J65" s="45">
         <f t="shared" si="12"/>
         <v>0.35586121596606</v>
       </c>
-      <c r="K65" s="46">
+      <c r="K65" s="45">
         <f t="shared" si="12"/>
         <v>0.2541865828329</v>
       </c>
-      <c r="L65" s="46" t="str">
+      <c r="L65" s="45" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="M65" s="46" t="str">
+      <c r="M65" s="45" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N65" s="47" t="str">
+      <c r="N65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="O65" s="47" t="str">
+      <c r="O65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="P65" s="47" t="str">
+      <c r="P65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="Q65" s="47" t="str">
+      <c r="Q65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="R65" s="47" t="str">
+      <c r="R65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="S65" s="47" t="str">
+      <c r="S65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T65" s="47" t="str">
+      <c r="T65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="U65" s="47" t="str">
+      <c r="U65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="V65" s="47" t="str">
+      <c r="V65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="W65" s="47" t="str">
+      <c r="W65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="X65" s="47" t="str">
+      <c r="X65" s="80" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="Y65" s="46">
+      <c r="Y65" s="45">
         <f t="shared" si="12"/>
         <v>0.266895911974545</v>
       </c>
@@ -6086,7 +6100,7 @@
       <c r="C66" s="43">
         <v>25</v>
       </c>
-      <c r="D66" s="45">
+      <c r="D66" s="44">
         <v>0.25</v>
       </c>
       <c r="E66" s="16"/>
@@ -6095,71 +6109,71 @@
       <c r="H66" s="19">
         <v>3</v>
       </c>
-      <c r="I66" s="46">
+      <c r="I66" s="45">
         <f t="shared" ref="I66:Y66" si="13">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.128505439098855</v>
       </c>
-      <c r="J66" s="46">
+      <c r="J66" s="45">
         <f t="shared" si="13"/>
         <v>0.25701087819771</v>
       </c>
-      <c r="K66" s="46">
+      <c r="K66" s="45">
         <f t="shared" si="13"/>
         <v>0.3671583974253</v>
       </c>
-      <c r="L66" s="46">
+      <c r="L66" s="45">
         <f t="shared" si="13"/>
         <v>0.282429536481</v>
       </c>
-      <c r="M66" s="46" t="str">
+      <c r="M66" s="45" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N66" s="47" t="str">
+      <c r="N66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="O66" s="47" t="str">
+      <c r="O66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="P66" s="47" t="str">
+      <c r="P66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q66" s="47" t="str">
+      <c r="Q66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="R66" s="47" t="str">
+      <c r="R66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="S66" s="47" t="str">
+      <c r="S66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="T66" s="47" t="str">
+      <c r="T66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="U66" s="47" t="str">
+      <c r="U66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V66" s="47" t="str">
+      <c r="V66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="W66" s="47" t="str">
+      <c r="W66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="X66" s="47" t="str">
+      <c r="X66" s="80" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Y66" s="46">
+      <c r="Y66" s="45">
         <f t="shared" si="13"/>
         <v>0.128505439098855</v>
       </c>
@@ -6172,7 +6186,7 @@
       <c r="C67" s="43">
         <v>30</v>
       </c>
-      <c r="D67" s="45">
+      <c r="D67" s="44">
         <v>0.3</v>
       </c>
       <c r="E67" s="16"/>
@@ -6181,71 +6195,71 @@
       <c r="H67" s="19">
         <v>4</v>
       </c>
-      <c r="I67" s="46">
+      <c r="I67" s="45">
         <f t="shared" ref="I67:Y67" si="14">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J67" s="46">
+      <c r="J67" s="45">
         <f t="shared" si="14"/>
         <v>0.11422705697676</v>
       </c>
-      <c r="K67" s="46">
+      <c r="K67" s="45">
         <f t="shared" si="14"/>
         <v>0.2447722649502</v>
       </c>
-      <c r="L67" s="46">
+      <c r="L67" s="45">
         <f t="shared" si="14"/>
         <v>0.376572715308</v>
       </c>
-      <c r="M67" s="46">
+      <c r="M67" s="45">
         <f t="shared" si="14"/>
         <v>0.31381059609</v>
       </c>
-      <c r="N67" s="47" t="str">
+      <c r="N67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O67" s="47" t="str">
+      <c r="O67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P67" s="47" t="str">
+      <c r="P67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q67" s="47" t="str">
+      <c r="Q67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="R67" s="47" t="str">
+      <c r="R67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="S67" s="47" t="str">
+      <c r="S67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="T67" s="47" t="str">
+      <c r="T67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="U67" s="47" t="str">
+      <c r="U67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V67" s="47" t="str">
+      <c r="V67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="W67" s="47" t="str">
+      <c r="W67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="X67" s="47" t="str">
+      <c r="X67" s="80" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Y67" s="46">
+      <c r="Y67" s="45">
         <f t="shared" si="14"/>
         <v>0.0428351463662851</v>
       </c>
@@ -6265,71 +6279,71 @@
       <c r="H68" s="19">
         <v>5</v>
       </c>
-      <c r="I68" s="48">
+      <c r="I68" s="47">
         <f t="shared" ref="I68:Y68" si="15">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.010470813556203</v>
       </c>
-      <c r="J68" s="48">
+      <c r="J68" s="47">
         <f t="shared" si="15"/>
         <v>0.03490271185401</v>
       </c>
-      <c r="K68" s="48">
+      <c r="K68" s="47">
         <f t="shared" si="15"/>
         <v>0.0997220338686001</v>
       </c>
-      <c r="L68" s="48">
+      <c r="L68" s="47">
         <f t="shared" si="15"/>
         <v>0.230127770466</v>
       </c>
-      <c r="M68" s="48">
+      <c r="M68" s="47">
         <f t="shared" si="15"/>
         <v>0.38354628411</v>
       </c>
-      <c r="N68" s="48">
+      <c r="N68" s="47">
         <f t="shared" si="15"/>
         <v>0.3486784401</v>
       </c>
-      <c r="O68" s="47" t="str">
+      <c r="O68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="P68" s="47" t="str">
+      <c r="P68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="Q68" s="47" t="str">
+      <c r="Q68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="R68" s="47" t="str">
+      <c r="R68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="S68" s="47" t="str">
+      <c r="S68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="T68" s="47" t="str">
+      <c r="T68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="U68" s="47" t="str">
+      <c r="U68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="V68" s="47" t="str">
+      <c r="V68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W68" s="47" t="str">
+      <c r="W68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="X68" s="47" t="str">
+      <c r="X68" s="80" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="Y68" s="46">
+      <c r="Y68" s="45">
         <f t="shared" si="15"/>
         <v>0.010470813556203</v>
       </c>
@@ -6345,71 +6359,71 @@
       <c r="H69" s="19">
         <v>6</v>
       </c>
-      <c r="I69" s="46">
+      <c r="I69" s="45">
         <f t="shared" ref="I69:Y69" si="16">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.001939039547445</v>
       </c>
-      <c r="J69" s="46">
+      <c r="J69" s="45">
         <f t="shared" si="16"/>
         <v>0.00775615818978</v>
       </c>
-      <c r="K69" s="46">
+      <c r="K69" s="45">
         <f t="shared" si="16"/>
         <v>0.0277005649635</v>
       </c>
-      <c r="L69" s="46">
+      <c r="L69" s="45">
         <f t="shared" si="16"/>
         <v>0.08523250758</v>
       </c>
-      <c r="M69" s="46">
+      <c r="M69" s="45">
         <f t="shared" si="16"/>
         <v>0.21308126895</v>
       </c>
-      <c r="N69" s="46">
+      <c r="N69" s="45">
         <f t="shared" si="16"/>
         <v>0.387420489</v>
       </c>
-      <c r="O69" s="46">
+      <c r="O69" s="45">
         <f t="shared" si="16"/>
         <v>0.387420489</v>
       </c>
-      <c r="P69" s="46" t="str">
+      <c r="P69" s="45" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q69" s="46" t="str">
+      <c r="Q69" s="45" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="R69" s="46" t="str">
+      <c r="R69" s="45" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="S69" s="46" t="str">
+      <c r="S69" s="45" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="T69" s="47" t="str">
+      <c r="T69" s="80" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="U69" s="47" t="str">
+      <c r="U69" s="80" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="V69" s="47" t="str">
+      <c r="V69" s="80" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="W69" s="47" t="str">
+      <c r="W69" s="80" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="X69" s="47" t="str">
+      <c r="X69" s="80" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y69" s="46">
+      <c r="Y69" s="45">
         <f t="shared" si="16"/>
         <v>0.001939039547445</v>
       </c>
@@ -6425,71 +6439,71 @@
       <c r="H70" s="19">
         <v>7</v>
       </c>
-      <c r="I70" s="46">
+      <c r="I70" s="45">
         <f t="shared" ref="I70:Y70" si="17">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.000277005649635</v>
       </c>
-      <c r="J70" s="46">
+      <c r="J70" s="45">
         <f t="shared" si="17"/>
         <v>0.00129269303163</v>
       </c>
-      <c r="K70" s="46">
+      <c r="K70" s="45">
         <f t="shared" si="17"/>
         <v>0.0055401129927</v>
       </c>
-      <c r="L70" s="46">
+      <c r="L70" s="45">
         <f t="shared" si="17"/>
         <v>0.021308126895</v>
       </c>
-      <c r="M70" s="46">
+      <c r="M70" s="45">
         <f t="shared" si="17"/>
         <v>0.07102708965</v>
       </c>
-      <c r="N70" s="46">
+      <c r="N70" s="45">
         <f t="shared" si="17"/>
         <v>0.1937102445</v>
       </c>
-      <c r="O70" s="46">
+      <c r="O70" s="45">
         <f t="shared" si="17"/>
         <v>0.387420489</v>
       </c>
-      <c r="P70" s="46">
+      <c r="P70" s="45">
         <f t="shared" si="17"/>
         <v>0.43046721</v>
       </c>
-      <c r="Q70" s="46" t="str">
+      <c r="Q70" s="45" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="R70" s="46" t="str">
+      <c r="R70" s="45" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="S70" s="46" t="str">
+      <c r="S70" s="45" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="T70" s="47" t="str">
+      <c r="T70" s="80" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="U70" s="47" t="str">
+      <c r="U70" s="80" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="V70" s="47" t="str">
+      <c r="V70" s="80" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="W70" s="47" t="str">
+      <c r="W70" s="80" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="X70" s="47" t="str">
+      <c r="X70" s="80" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="Y70" s="46">
+      <c r="Y70" s="45">
         <f t="shared" si="17"/>
         <v>0.000277005649635</v>
       </c>
@@ -6505,71 +6519,71 @@
       <c r="H71" s="19">
         <v>8</v>
       </c>
-      <c r="I71" s="46">
+      <c r="I71" s="45">
         <f t="shared" ref="I71:Y71" si="18">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J71" s="46">
+      <c r="J71" s="45">
         <f t="shared" si="18"/>
         <v>0.00016415149608</v>
       </c>
-      <c r="K71" s="46">
+      <c r="K71" s="45">
         <f t="shared" si="18"/>
         <v>0.0008207574804</v>
       </c>
-      <c r="L71" s="46">
+      <c r="L71" s="45">
         <f t="shared" si="18"/>
         <v>0.003788111448</v>
       </c>
-      <c r="M71" s="46">
+      <c r="M71" s="45">
         <f t="shared" si="18"/>
         <v>0.0157837977</v>
       </c>
-      <c r="N71" s="46">
+      <c r="N71" s="45">
         <f t="shared" si="18"/>
         <v>0.057395628</v>
       </c>
-      <c r="O71" s="46">
+      <c r="O71" s="45">
         <f t="shared" si="18"/>
         <v>0.172186884</v>
       </c>
-      <c r="P71" s="46">
+      <c r="P71" s="45">
         <f t="shared" si="18"/>
         <v>0.38263752</v>
       </c>
-      <c r="Q71" s="46">
+      <c r="Q71" s="45">
         <f t="shared" si="18"/>
         <v>0.4782969</v>
       </c>
-      <c r="R71" s="46" t="str">
+      <c r="R71" s="45" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="S71" s="46" t="str">
+      <c r="S71" s="45" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="T71" s="47" t="str">
+      <c r="T71" s="80" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="U71" s="47" t="str">
+      <c r="U71" s="80" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="V71" s="47" t="str">
+      <c r="V71" s="80" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="W71" s="47" t="str">
+      <c r="W71" s="80" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="X71" s="47" t="str">
+      <c r="X71" s="80" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Y71" s="46">
+      <c r="Y71" s="45">
         <f t="shared" si="18"/>
         <v>3.0778405515e-5</v>
       </c>
@@ -6585,71 +6599,71 @@
       <c r="H72" s="19">
         <v>9</v>
       </c>
-      <c r="I72" s="46">
+      <c r="I72" s="45">
         <f t="shared" ref="I72:Y72" si="19">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J72" s="46">
+      <c r="J72" s="45">
         <f t="shared" si="19"/>
         <v>1.595917323e-5</v>
       </c>
-      <c r="K72" s="46">
+      <c r="K72" s="45">
         <f t="shared" si="19"/>
         <v>9.11952756e-5</v>
       </c>
-      <c r="L72" s="46">
+      <c r="L72" s="45">
         <f t="shared" si="19"/>
         <v>0.000491051484000001</v>
       </c>
-      <c r="M72" s="46">
+      <c r="M72" s="45">
         <f t="shared" si="19"/>
         <v>0.00245525742</v>
       </c>
-      <c r="N72" s="46">
+      <c r="N72" s="45">
         <f t="shared" si="19"/>
         <v>0.011160261</v>
       </c>
-      <c r="O72" s="46">
+      <c r="O72" s="45">
         <f t="shared" si="19"/>
         <v>0.044641044</v>
       </c>
-      <c r="P72" s="46">
+      <c r="P72" s="45">
         <f t="shared" si="19"/>
         <v>0.14880348</v>
       </c>
-      <c r="Q72" s="46">
+      <c r="Q72" s="45">
         <f t="shared" si="19"/>
         <v>0.3720087</v>
       </c>
-      <c r="R72" s="46">
+      <c r="R72" s="45">
         <f t="shared" si="19"/>
         <v>0.531441</v>
       </c>
-      <c r="S72" s="46" t="str">
+      <c r="S72" s="45" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="T72" s="47" t="str">
+      <c r="T72" s="80" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="U72" s="47" t="str">
+      <c r="U72" s="80" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V72" s="47" t="str">
+      <c r="V72" s="80" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="W72" s="47" t="str">
+      <c r="W72" s="80" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="X72" s="47" t="str">
+      <c r="X72" s="80" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Y72" s="46">
+      <c r="Y72" s="45">
         <f t="shared" si="19"/>
         <v>2.659862205e-6</v>
       </c>
@@ -6665,71 +6679,71 @@
       <c r="H73" s="19">
         <v>10</v>
       </c>
-      <c r="I73" s="46">
+      <c r="I73" s="45">
         <f t="shared" ref="I73:Y73" si="20">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J73" s="46">
+      <c r="J73" s="45">
         <f t="shared" si="20"/>
         <v>1.18216098e-6</v>
       </c>
-      <c r="K73" s="46">
+      <c r="K73" s="45">
         <f t="shared" si="20"/>
         <v>7.5996063e-6</v>
       </c>
-      <c r="L73" s="46">
+      <c r="L73" s="45">
         <f t="shared" si="20"/>
         <v>4.6766808e-5</v>
       </c>
-      <c r="M73" s="46">
+      <c r="M73" s="45">
         <f t="shared" si="20"/>
         <v>0.00027280638</v>
       </c>
-      <c r="N73" s="46">
+      <c r="N73" s="45">
         <f t="shared" si="20"/>
         <v>0.0014880348</v>
       </c>
-      <c r="O73" s="46">
+      <c r="O73" s="45">
         <f t="shared" si="20"/>
         <v>0.00744017399999999</v>
       </c>
-      <c r="P73" s="46">
+      <c r="P73" s="45">
         <f t="shared" si="20"/>
         <v>0.03306744</v>
       </c>
-      <c r="Q73" s="46">
+      <c r="Q73" s="45">
         <f t="shared" si="20"/>
         <v>0.1240029</v>
       </c>
-      <c r="R73" s="46">
+      <c r="R73" s="45">
         <f t="shared" si="20"/>
         <v>0.354294</v>
       </c>
-      <c r="S73" s="46">
+      <c r="S73" s="45">
         <f t="shared" si="20"/>
         <v>0.59049</v>
       </c>
-      <c r="T73" s="47" t="str">
+      <c r="T73" s="80" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="U73" s="47" t="str">
+      <c r="U73" s="80" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="V73" s="47" t="str">
+      <c r="V73" s="80" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W73" s="47" t="str">
+      <c r="W73" s="80" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="X73" s="47" t="str">
+      <c r="X73" s="80" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Y73" s="46">
+      <c r="Y73" s="45">
         <f t="shared" si="20"/>
         <v>1.77324147e-7</v>
       </c>
@@ -6745,71 +6759,71 @@
       <c r="H74" s="19">
         <v>11</v>
       </c>
-      <c r="I74" s="46">
+      <c r="I74" s="45">
         <f t="shared" ref="I74:Y74" si="21">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J74" s="46">
+      <c r="J74" s="45">
         <f t="shared" si="21"/>
         <v>6.56756100000002e-8</v>
       </c>
-      <c r="K74" s="46">
+      <c r="K74" s="45">
         <f t="shared" si="21"/>
         <v>4.69111499999999e-7</v>
       </c>
-      <c r="L74" s="46">
+      <c r="L74" s="45">
         <f t="shared" si="21"/>
         <v>3.247695e-6</v>
       </c>
-      <c r="M74" s="46">
+      <c r="M74" s="45">
         <f t="shared" si="21"/>
         <v>2.16512999999999e-5</v>
       </c>
-      <c r="N74" s="46">
+      <c r="N74" s="45">
         <f t="shared" si="21"/>
         <v>0.000137781</v>
       </c>
-      <c r="O74" s="46">
+      <c r="O74" s="45">
         <f t="shared" si="21"/>
         <v>0.000826686</v>
       </c>
-      <c r="P74" s="46">
+      <c r="P74" s="45">
         <f t="shared" si="21"/>
         <v>0.0045927</v>
       </c>
-      <c r="Q74" s="46">
+      <c r="Q74" s="45">
         <f t="shared" si="21"/>
         <v>0.0229635</v>
       </c>
-      <c r="R74" s="46">
+      <c r="R74" s="45">
         <f t="shared" si="21"/>
         <v>0.0984150000000001</v>
       </c>
-      <c r="S74" s="46">
+      <c r="S74" s="45">
         <f t="shared" si="21"/>
         <v>0.32805</v>
       </c>
-      <c r="T74" s="46">
+      <c r="T74" s="45">
         <f t="shared" si="21"/>
         <v>0.6561</v>
       </c>
-      <c r="U74" s="46" t="str">
+      <c r="U74" s="45" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="V74" s="46" t="str">
+      <c r="V74" s="45" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="W74" s="46" t="str">
+      <c r="W74" s="45" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X74" s="46" t="str">
+      <c r="X74" s="45" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="Y74" s="46">
+      <c r="Y74" s="45">
         <f t="shared" si="21"/>
         <v>8.95576499999999e-9</v>
       </c>
@@ -6825,71 +6839,71 @@
       <c r="H75" s="19">
         <v>12</v>
       </c>
-      <c r="I75" s="46">
+      <c r="I75" s="45">
         <f t="shared" ref="I75:Y75" si="22">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J75" s="46">
+      <c r="J75" s="45">
         <f t="shared" si="22"/>
         <v>2.65356e-9</v>
       </c>
-      <c r="K75" s="46">
+      <c r="K75" s="45">
         <f t="shared" si="22"/>
         <v>2.08494e-8</v>
       </c>
-      <c r="L75" s="46">
+      <c r="L75" s="45">
         <f t="shared" si="22"/>
         <v>1.6038e-7</v>
       </c>
-      <c r="M75" s="46">
+      <c r="M75" s="45">
         <f t="shared" si="22"/>
         <v>1.20285e-6</v>
       </c>
-      <c r="N75" s="46">
+      <c r="N75" s="45">
         <f t="shared" si="22"/>
         <v>8.74800000000001e-6</v>
       </c>
-      <c r="O75" s="46">
+      <c r="O75" s="45">
         <f t="shared" si="22"/>
         <v>6.1236e-5</v>
       </c>
-      <c r="P75" s="46">
+      <c r="P75" s="45">
         <f t="shared" si="22"/>
         <v>0.00040824</v>
       </c>
-      <c r="Q75" s="46">
+      <c r="Q75" s="45">
         <f t="shared" si="22"/>
         <v>0.0025515</v>
       </c>
-      <c r="R75" s="46">
+      <c r="R75" s="45">
         <f t="shared" si="22"/>
         <v>0.01458</v>
       </c>
-      <c r="S75" s="46">
+      <c r="S75" s="45">
         <f t="shared" si="22"/>
         <v>0.0729</v>
       </c>
-      <c r="T75" s="46">
+      <c r="T75" s="45">
         <f t="shared" si="22"/>
         <v>0.2916</v>
       </c>
-      <c r="U75" s="46">
+      <c r="U75" s="45">
         <f t="shared" si="22"/>
         <v>0.729</v>
       </c>
-      <c r="V75" s="46" t="str">
+      <c r="V75" s="45" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="W75" s="46" t="str">
+      <c r="W75" s="45" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="X75" s="46" t="str">
+      <c r="X75" s="45" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y75" s="46">
+      <c r="Y75" s="45">
         <f t="shared" si="22"/>
         <v>3.31695000000002e-10</v>
       </c>
@@ -6905,71 +6919,71 @@
       <c r="H76" s="19">
         <v>13</v>
       </c>
-      <c r="I76" s="46">
+      <c r="I76" s="45">
         <f t="shared" ref="I76:Y76" si="23">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J76" s="46">
+      <c r="J76" s="45">
         <f t="shared" si="23"/>
         <v>7.37100000000002e-11</v>
       </c>
-      <c r="K76" s="46">
+      <c r="K76" s="45">
         <f t="shared" si="23"/>
         <v>6.318e-10</v>
       </c>
-      <c r="L76" s="46">
+      <c r="L76" s="45">
         <f t="shared" si="23"/>
         <v>5.34599999999998e-9</v>
       </c>
-      <c r="M76" s="46">
+      <c r="M76" s="45">
         <f t="shared" si="23"/>
         <v>4.455e-8</v>
       </c>
-      <c r="N76" s="46">
+      <c r="N76" s="45">
         <f t="shared" si="23"/>
         <v>3.64500000000001e-7</v>
       </c>
-      <c r="O76" s="46">
+      <c r="O76" s="45">
         <f t="shared" si="23"/>
         <v>2.916e-6</v>
       </c>
-      <c r="P76" s="46">
+      <c r="P76" s="45">
         <f t="shared" si="23"/>
         <v>2.268e-5</v>
       </c>
-      <c r="Q76" s="46">
+      <c r="Q76" s="45">
         <f t="shared" si="23"/>
         <v>0.0001701</v>
       </c>
-      <c r="R76" s="46">
+      <c r="R76" s="45">
         <f t="shared" si="23"/>
         <v>0.001215</v>
       </c>
-      <c r="S76" s="46">
+      <c r="S76" s="45">
         <f t="shared" si="23"/>
         <v>0.0081</v>
       </c>
-      <c r="T76" s="46">
+      <c r="T76" s="45">
         <f t="shared" si="23"/>
         <v>0.0486</v>
       </c>
-      <c r="U76" s="46">
+      <c r="U76" s="45">
         <f t="shared" si="23"/>
         <v>0.243</v>
       </c>
-      <c r="V76" s="46">
+      <c r="V76" s="45">
         <f t="shared" si="23"/>
         <v>0.81</v>
       </c>
-      <c r="W76" s="46" t="str">
+      <c r="W76" s="45" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="X76" s="46" t="str">
+      <c r="X76" s="45" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Y76" s="46">
+      <c r="Y76" s="45">
         <f t="shared" si="23"/>
         <v>8.50500000000002e-12</v>
       </c>
@@ -6985,71 +6999,71 @@
       <c r="H77" s="19">
         <v>14</v>
       </c>
-      <c r="I77" s="46">
+      <c r="I77" s="45">
         <f t="shared" ref="I77:Y77" si="24">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.35e-13</v>
       </c>
-      <c r="J77" s="46">
+      <c r="J77" s="45">
         <f t="shared" si="24"/>
         <v>1.26000000000001e-12</v>
       </c>
-      <c r="K77" s="46">
+      <c r="K77" s="45">
         <f t="shared" si="24"/>
         <v>1.17e-11</v>
       </c>
-      <c r="L77" s="46">
+      <c r="L77" s="45">
         <f t="shared" si="24"/>
         <v>1.08e-10</v>
       </c>
-      <c r="M77" s="46">
+      <c r="M77" s="45">
         <f t="shared" si="24"/>
         <v>9.89999999999998e-10</v>
       </c>
-      <c r="N77" s="46">
+      <c r="N77" s="45">
         <f t="shared" si="24"/>
         <v>9e-9</v>
       </c>
-      <c r="O77" s="46">
+      <c r="O77" s="45">
         <f t="shared" si="24"/>
         <v>8.10000000000002e-8</v>
       </c>
-      <c r="P77" s="46">
+      <c r="P77" s="45">
         <f t="shared" si="24"/>
         <v>7.19999999999999e-7</v>
       </c>
-      <c r="Q77" s="46">
+      <c r="Q77" s="45">
         <f t="shared" si="24"/>
         <v>6.30000000000001e-6</v>
       </c>
-      <c r="R77" s="46">
+      <c r="R77" s="45">
         <f t="shared" si="24"/>
         <v>5.39999999999999e-5</v>
       </c>
-      <c r="S77" s="46">
+      <c r="S77" s="45">
         <f t="shared" si="24"/>
         <v>0.000450000000000001</v>
       </c>
-      <c r="T77" s="46">
+      <c r="T77" s="45">
         <f t="shared" si="24"/>
         <v>0.0036</v>
       </c>
-      <c r="U77" s="46">
+      <c r="U77" s="45">
         <f t="shared" si="24"/>
         <v>0.027</v>
       </c>
-      <c r="V77" s="46">
+      <c r="V77" s="45">
         <f t="shared" si="24"/>
         <v>0.18</v>
       </c>
-      <c r="W77" s="46">
+      <c r="W77" s="45">
         <f t="shared" si="24"/>
         <v>0.9</v>
       </c>
-      <c r="X77" s="46" t="str">
+      <c r="X77" s="45" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="Y77" s="46">
+      <c r="Y77" s="45">
         <f t="shared" si="24"/>
         <v>1.35e-13</v>
       </c>
@@ -7065,71 +7079,71 @@
       <c r="H78" s="19">
         <v>15</v>
       </c>
-      <c r="I78" s="46">
+      <c r="I78" s="45">
         <f t="shared" ref="I78:Y78" si="25">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1e-15</v>
       </c>
-      <c r="J78" s="46">
+      <c r="J78" s="45">
         <f t="shared" si="25"/>
         <v>1.00000000000001e-14</v>
       </c>
-      <c r="K78" s="46">
+      <c r="K78" s="45">
         <f t="shared" si="25"/>
         <v>1e-13</v>
       </c>
-      <c r="L78" s="46">
+      <c r="L78" s="45">
         <f t="shared" si="25"/>
         <v>1e-12</v>
       </c>
-      <c r="M78" s="46">
+      <c r="M78" s="45">
         <f t="shared" si="25"/>
         <v>1e-11</v>
       </c>
-      <c r="N78" s="46">
+      <c r="N78" s="45">
         <f t="shared" si="25"/>
         <v>1e-10</v>
       </c>
-      <c r="O78" s="46">
+      <c r="O78" s="45">
         <f t="shared" si="25"/>
         <v>1e-9</v>
       </c>
-      <c r="P78" s="46">
+      <c r="P78" s="45">
         <f t="shared" si="25"/>
         <v>1e-8</v>
       </c>
-      <c r="Q78" s="46">
+      <c r="Q78" s="45">
         <f t="shared" si="25"/>
         <v>1e-7</v>
       </c>
-      <c r="R78" s="46">
+      <c r="R78" s="45">
         <f t="shared" si="25"/>
         <v>1e-6</v>
       </c>
-      <c r="S78" s="46">
+      <c r="S78" s="45">
         <f t="shared" si="25"/>
         <v>1e-5</v>
       </c>
-      <c r="T78" s="46">
+      <c r="T78" s="45">
         <f t="shared" si="25"/>
         <v>0.0001</v>
       </c>
-      <c r="U78" s="46">
+      <c r="U78" s="45">
         <f t="shared" si="25"/>
         <v>0.001</v>
       </c>
-      <c r="V78" s="46">
+      <c r="V78" s="45">
         <f t="shared" si="25"/>
         <v>0.01</v>
       </c>
-      <c r="W78" s="46">
+      <c r="W78" s="45">
         <f t="shared" si="25"/>
         <v>0.1</v>
       </c>
-      <c r="X78" s="46">
+      <c r="X78" s="45">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
-      <c r="Y78" s="46">
+      <c r="Y78" s="45">
         <f t="shared" si="25"/>
         <v>1e-15</v>
       </c>
@@ -7168,16 +7182,16 @@
       <c r="D80" s="16"/>
       <c r="E80" s="16"/>
       <c r="F80" s="16"/>
-      <c r="G80" s="49" t="s">
+      <c r="G80" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="H80" s="49"/>
-      <c r="I80" s="49"/>
-      <c r="J80" s="49"/>
-      <c r="K80" s="49"/>
-      <c r="L80" s="49"/>
-      <c r="M80" s="49"/>
-      <c r="N80" s="49"/>
+      <c r="H80" s="48"/>
+      <c r="I80" s="48"/>
+      <c r="J80" s="48"/>
+      <c r="K80" s="48"/>
+      <c r="L80" s="48"/>
+      <c r="M80" s="48"/>
+      <c r="N80" s="48"/>
       <c r="O80" s="16"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="16"/>
@@ -7267,23 +7281,23 @@
       <c r="H83" s="19">
         <v>0</v>
       </c>
-      <c r="I83" s="50">
+      <c r="I83" s="49">
         <f t="shared" ref="I83:I98" si="26">I63</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J83" s="46">
+      <c r="J83" s="45">
         <f ca="1" t="shared" ref="J83:J98" si="27">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,J$82-2,$H83+1,1))</f>
         <v>0.0423911582752162</v>
       </c>
-      <c r="K83" s="46">
+      <c r="K83" s="45">
         <f ca="1" t="shared" ref="K83:K98" si="28">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,K$82-2,$H83+1,1))</f>
         <v>0.00872796356808771</v>
       </c>
-      <c r="L83" s="46">
+      <c r="L83" s="45">
         <f ca="1" t="shared" ref="L83:L98" si="29">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,L$82-2,$H83+1,1))</f>
         <v>0.00179701029991443</v>
       </c>
-      <c r="M83" s="46">
+      <c r="M83" s="45">
         <f ca="1" t="shared" ref="M83:M98" si="30">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,M$82-2,$H83+1,1))</f>
         <v>0.000369988485035127</v>
       </c>
@@ -7311,23 +7325,23 @@
       <c r="H84" s="19">
         <v>1</v>
       </c>
-      <c r="I84" s="50">
+      <c r="I84" s="49">
         <f t="shared" si="26"/>
         <v>0.343151886824415</v>
       </c>
-      <c r="J84" s="46">
+      <c r="J84" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.149154075412798</v>
       </c>
-      <c r="K84" s="46">
+      <c r="K84" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.0486682742171146</v>
       </c>
-      <c r="L84" s="46">
+      <c r="L84" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.0141287572505847</v>
       </c>
-      <c r="M84" s="46">
+      <c r="M84" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.00384885394774005</v>
       </c>
@@ -7355,23 +7369,23 @@
       <c r="H85" s="19">
         <v>2</v>
       </c>
-      <c r="I85" s="50">
+      <c r="I85" s="49">
         <f t="shared" si="26"/>
         <v>0.266895911974545</v>
       </c>
-      <c r="J85" s="46">
+      <c r="J85" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.244907309011137</v>
       </c>
-      <c r="K85" s="46">
+      <c r="K85" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.126644329478555</v>
       </c>
-      <c r="L85" s="46">
+      <c r="L85" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.0518398983833752</v>
       </c>
-      <c r="M85" s="46">
+      <c r="M85" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.0186844980625806</v>
       </c>
@@ -7399,25 +7413,25 @@
       <c r="H86" s="19">
         <v>3</v>
       </c>
-      <c r="I86" s="50">
+      <c r="I86" s="49">
         <f t="shared" si="26"/>
         <v>0.128505439098855</v>
       </c>
-      <c r="J86" s="46">
+      <c r="J86" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.248938705044242</v>
       </c>
-      <c r="K86" s="46">
+      <c r="K86" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.204009132488774</v>
       </c>
-      <c r="L86" s="46">
+      <c r="L86" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.117746600468707</v>
       </c>
-      <c r="M86" s="46">
+      <c r="M86" s="45">
         <f ca="1" t="shared" si="30"/>
-        <v>0.0561507417121915</v>
+        <v>0.0561507417121914</v>
       </c>
       <c r="N86" s="16"/>
       <c r="O86" s="16"/>
@@ -7443,23 +7457,23 @@
       <c r="H87" s="19">
         <v>4</v>
       </c>
-      <c r="I87" s="50">
+      <c r="I87" s="49">
         <f t="shared" si="26"/>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J87" s="46">
+      <c r="J87" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.175179088734837</v>
       </c>
-      <c r="K87" s="46">
+      <c r="K87" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.227516357631513</v>
       </c>
-      <c r="L87" s="46">
+      <c r="L87" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.185153433475941</v>
       </c>
-      <c r="M87" s="46">
+      <c r="M87" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.116823097284761</v>
       </c>
@@ -7487,23 +7501,23 @@
       <c r="H88" s="19">
         <v>5</v>
       </c>
-      <c r="I88" s="50">
+      <c r="I88" s="49">
         <f t="shared" si="26"/>
         <v>0.010470813556203</v>
       </c>
-      <c r="J88" s="51">
+      <c r="J88" s="50">
         <f ca="1" t="shared" si="27"/>
         <v>0.0904010606063728</v>
       </c>
-      <c r="K88" s="46">
+      <c r="K88" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.186070305102755</v>
       </c>
-      <c r="L88" s="46">
+      <c r="L88" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.213509197834518</v>
       </c>
-      <c r="M88" s="46">
+      <c r="M88" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.178239256298975</v>
       </c>
@@ -7531,23 +7545,23 @@
       <c r="H89" s="19">
         <v>6</v>
       </c>
-      <c r="I89" s="46">
+      <c r="I89" s="45">
         <f t="shared" si="26"/>
         <v>0.001939039547445</v>
       </c>
-      <c r="J89" s="46">
+      <c r="J89" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.0353419784263597</v>
       </c>
-      <c r="K89" s="46">
+      <c r="K89" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.115283613815378</v>
       </c>
-      <c r="L89" s="46">
+      <c r="L89" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.186520888927731</v>
       </c>
-      <c r="M89" s="46">
+      <c r="M89" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.206017482223783</v>
       </c>
@@ -7575,23 +7589,23 @@
       <c r="H90" s="19">
         <v>7</v>
       </c>
-      <c r="I90" s="46">
+      <c r="I90" s="45">
         <f t="shared" si="26"/>
         <v>0.000277005649635</v>
       </c>
-      <c r="J90" s="46">
+      <c r="J90" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.0106586919063625</v>
       </c>
-      <c r="K90" s="46">
+      <c r="K90" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.0551002810299252</v>
       </c>
-      <c r="L90" s="46">
+      <c r="L90" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.125699654521354</v>
       </c>
-      <c r="M90" s="46">
+      <c r="M90" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.183696342337757</v>
       </c>
@@ -7619,23 +7633,23 @@
       <c r="H91" s="19">
         <v>8</v>
       </c>
-      <c r="I91" s="46">
+      <c r="I91" s="45">
         <f t="shared" si="26"/>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J91" s="46">
+      <c r="J91" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.00250018699038132</v>
       </c>
-      <c r="K91" s="46">
+      <c r="K91" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.0204830948684633</v>
       </c>
-      <c r="L91" s="46">
+      <c r="L91" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.0658864672914092</v>
       </c>
-      <c r="M91" s="46">
+      <c r="M91" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.127395026419981</v>
       </c>
@@ -7663,23 +7677,23 @@
       <c r="H92" s="19">
         <v>9</v>
       </c>
-      <c r="I92" s="46">
+      <c r="I92" s="45">
         <f t="shared" si="26"/>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J92" s="46">
+      <c r="J92" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>0.00045613836724378</v>
       </c>
-      <c r="K92" s="46">
+      <c r="K92" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.00592233363290273</v>
       </c>
-      <c r="L92" s="46">
+      <c r="L92" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.0268604875121694</v>
       </c>
-      <c r="M92" s="46">
+      <c r="M92" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.0687163318006563</v>
       </c>
@@ -7707,23 +7721,23 @@
       <c r="H93" s="19">
         <v>10</v>
       </c>
-      <c r="I93" s="46">
+      <c r="I93" s="45">
         <f t="shared" si="26"/>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J93" s="46">
+      <c r="J93" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>6.41972516861615e-5</v>
       </c>
-      <c r="K93" s="46">
+      <c r="K93" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.00132094848931411</v>
       </c>
-      <c r="L93" s="46">
+      <c r="L93" s="45">
         <f ca="1" t="shared" si="29"/>
-        <v>0.00844748208087341</v>
-      </c>
-      <c r="M93" s="46">
+        <v>0.0084474820808734</v>
+      </c>
+      <c r="M93" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.0285932276946469</v>
       </c>
@@ -7751,25 +7765,25 @@
       <c r="H94" s="19">
         <v>11</v>
       </c>
-      <c r="I94" s="46">
+      <c r="I94" s="45">
         <f t="shared" si="26"/>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J94" s="46">
+      <c r="J94" s="45">
         <f ca="1" t="shared" si="27"/>
-        <v>6.84482481502284e-6</v>
-      </c>
-      <c r="K94" s="46">
+        <v>6.84482481502283e-6</v>
+      </c>
+      <c r="K94" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>0.000223205537226664</v>
       </c>
-      <c r="L94" s="46">
+      <c r="L94" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.00201264295050115</v>
       </c>
-      <c r="M94" s="46">
+      <c r="M94" s="45">
         <f ca="1" t="shared" si="30"/>
-        <v>0.0090134793085826</v>
+        <v>0.00901347930858259</v>
       </c>
       <c r="N94" s="16"/>
       <c r="O94" s="16"/>
@@ -7795,23 +7809,23 @@
       <c r="H95" s="19">
         <v>12</v>
       </c>
-      <c r="I95" s="46">
+      <c r="I95" s="45">
         <f t="shared" si="26"/>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J95" s="46">
+      <c r="J95" s="45">
         <f ca="1" t="shared" si="27"/>
-        <v>5.35192063726066e-7</v>
-      </c>
-      <c r="K95" s="46">
+        <v>5.35192063726065e-7</v>
+      </c>
+      <c r="K95" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>2.76582993088367e-5</v>
       </c>
-      <c r="L95" s="46">
+      <c r="L95" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>0.000351647569312272</v>
       </c>
-      <c r="M95" s="46">
+      <c r="M95" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.00208364234881633</v>
       </c>
@@ -7839,23 +7853,23 @@
       <c r="H96" s="19">
         <v>13</v>
       </c>
-      <c r="I96" s="46">
+      <c r="I96" s="45">
         <f t="shared" si="26"/>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J96" s="46">
+      <c r="J96" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>2.89705105720662e-8</v>
       </c>
-      <c r="K96" s="46">
+      <c r="K96" s="45">
         <f ca="1" t="shared" si="28"/>
-        <v>2.37271260294231e-6</v>
-      </c>
-      <c r="L96" s="46">
+        <v>2.3727126029423e-6</v>
+      </c>
+      <c r="L96" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>4.25351197940594e-5</v>
       </c>
-      <c r="M96" s="46">
+      <c r="M96" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>0.000333467138086273</v>
       </c>
@@ -7883,23 +7897,23 @@
       <c r="H97" s="19">
         <v>14</v>
       </c>
-      <c r="I97" s="46">
+      <c r="I97" s="45">
         <f t="shared" si="26"/>
         <v>1.35e-13</v>
       </c>
-      <c r="J97" s="46">
+      <c r="J97" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>9.70793123226205e-10</v>
       </c>
-      <c r="K97" s="46">
+      <c r="K97" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>1.26005313618923e-7</v>
       </c>
-      <c r="L97" s="46">
+      <c r="L97" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>3.18501702640648e-6</v>
       </c>
-      <c r="M97" s="46">
+      <c r="M97" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>3.30374840550607e-5</v>
       </c>
@@ -7927,23 +7941,23 @@
       <c r="H98" s="19">
         <v>15</v>
       </c>
-      <c r="I98" s="46">
+      <c r="I98" s="45">
         <f t="shared" si="26"/>
         <v>1e-15</v>
       </c>
-      <c r="J98" s="46">
+      <c r="J98" s="45">
         <f ca="1" t="shared" si="27"/>
         <v>1.51811270298748e-11</v>
       </c>
-      <c r="K98" s="46">
+      <c r="K98" s="45">
         <f ca="1" t="shared" si="28"/>
         <v>3.12276543125086e-9</v>
       </c>
-      <c r="L98" s="46">
+      <c r="L98" s="45">
         <f ca="1" t="shared" si="29"/>
         <v>1.11296789654137e-7</v>
       </c>
-      <c r="M98" s="46">
+      <c r="M98" s="45">
         <f ca="1" t="shared" si="30"/>
         <v>1.52745235260974e-6</v>
       </c>
@@ -7971,23 +7985,23 @@
       <c r="H99" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="I99" s="46">
+      <c r="I99" s="45">
         <f>SUM(I83:I98)</f>
         <v>1</v>
       </c>
-      <c r="J99" s="46">
+      <c r="J99" s="45">
         <f ca="1">SUM(J83:J98)</f>
         <v>1</v>
       </c>
-      <c r="K99" s="46">
+      <c r="K99" s="45">
         <f ca="1">SUM(K83:K98)</f>
         <v>1</v>
       </c>
-      <c r="L99" s="46">
+      <c r="L99" s="45">
         <f ca="1">SUM(L83:L98)</f>
         <v>1</v>
       </c>
-      <c r="M99" s="46">
+      <c r="M99" s="45">
         <f ca="1">SUM(M83:M98)</f>
         <v>1</v>
       </c>
@@ -8032,10 +8046,10 @@
       <c r="Y100" s="16"/>
     </row>
     <row r="101" ht="102" customHeight="1" spans="1:25">
-      <c r="A101" s="52" t="s">
+      <c r="A101" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="B101" s="46">
+      <c r="B101" s="45">
         <f ca="1">SUM(M88:M98)</f>
         <v>0.804122820507692</v>
       </c>
@@ -8086,7 +8100,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="S28:Y35 E35:G35 A35:C35 A28:G34 A24:Y27 C23:Y23 A23 A8:Y22 C7:Y7 A7 H6:Y6 A6:F6 A5:Y5 H4:Y4 A4:F4 A1:Y3 A36:Y101" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A36:Y101 A1:Y3 A4:F4 H4:Y4 A5:Y5 A6:F6 H6:Y6 A7 C7:Y7 A8:Y22 A23 C23:Y23 A24:Y27 A28:G34 A35:C35 E35:G35 S28:Y35" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8238,7 +8252,7 @@
       <c r="A18" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="74">
         <f>BINOMDIST($B$15,$B$13,$B$14,FALSE)</f>
         <v>0.00360966796875</v>
       </c>
@@ -8250,7 +8264,7 @@
       <c r="A19" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="75">
         <f>BINOMDIST($B$13,$B$13,$B$14,FALSE)</f>
         <v>2.373046875e-6</v>
       </c>
@@ -8262,7 +8276,7 @@
       <c r="A20" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="74">
         <f>1-BINOMDIST($B$15-1,$B$13,$B$14,TRUE)</f>
         <v>0.00375837890624997</v>
       </c>
@@ -8368,7 +8382,7 @@
       <c r="A32" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="74">
         <f>1-BINOMDIST($B$29-1,$B$27,$B$28,TRUE)</f>
         <v>0.000602214399999967</v>
       </c>
@@ -8380,7 +8394,7 @@
       <c r="A33" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="75">
         <f>1-BINOMDIST(1,$B$27,$B$28,TRUE)</f>
         <v>0.0147579904</v>
       </c>
@@ -8421,7 +8435,7 @@
       <c r="A38" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="75">
         <f>1-BINOMDIST(2,5,0.05,TRUE)</f>
         <v>0.00115812500000001</v>
       </c>
@@ -8433,7 +8447,7 @@
       <c r="A39" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="74">
         <f>1-BINOMDIST(2,15,0.05,TRUE)</f>
         <v>0.0362002386427291</v>
       </c>

--- a/游戏设计王/老虎机数学专题-二项分配机率.xlsx
+++ b/游戏设计王/老虎机数学专题-二项分配机率.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="211">
   <si>
     <t>二项分配机率（Binomial Distribution）计算模型</t>
   </si>
@@ -394,16 +394,76 @@
     <t>问3：只搜集 B1（非 B1 的箱子关起来可重开，共 5 轮）</t>
   </si>
   <si>
+    <t>[空内容]J63 = 列头 J62=1、行头 H63=0 → 开始1个、结束0个。 开始已经有 1 个 B1，它不会消失，结束时不可能变 0，所以概率 = 0（显示为空）——正确。</t>
+  </si>
+  <si>
     <t>每轮开始时有 i 个 B1，剩下 15-i 个箱子重开，每箱再开出 B1 的机率 = Table1 中 B1 的机率</t>
   </si>
   <si>
-    <t>Table 4：单轮转移机率 P(开始 i 个 -&gt; 结束 j 个) = IFERROR(BINOM.DIST(j-i, 15-i, B1机率, FALSE), "")</t>
-  </si>
-  <si>
-    <t>结束\开始</t>
+    <t>Table 4：单轮转移机率 P(开始 i 个 -&gt; 结束 j 个) = IFERROR(BINOM.DIST(j-i, 15-i, B1机率, FALSE), "")  把开始数作为列，结束数作为行就得到一张 16×16 的表格 转移概率</t>
+  </si>
+  <si>
+    <t>i=0</t>
+  </si>
+  <si>
+    <t>i=1</t>
+  </si>
+  <si>
+    <t>i=2</t>
+  </si>
+  <si>
+    <t>i=3</t>
+  </si>
+  <si>
+    <t>结束(j行-向下)\开始(列-向右)</t>
+  </si>
+  <si>
+    <t>j=0</t>
+  </si>
+  <si>
+    <t>j=1</t>
+  </si>
+  <si>
+    <t>j=2</t>
+  </si>
+  <si>
+    <t>“已知开始是s个，结束变成t个”的转移概率</t>
   </si>
   <si>
     <t>Table 5：只收集 B1，每轮结束后 B1 的个数分布（第1轮 = Table4 开始=0 那一列；第2~5轮 = MMULT 迭代）</t>
+  </si>
+  <si>
+    <t>Table5 算法 (Markov 马可夫链迭代)</t>
+  </si>
+  <si>
+    <t>1) 状态 = 已搜集的 B1 个数，取值 0~15</t>
+  </si>
+  <si>
+    <t>2) 转移矩阵 T = Table4；T(i-&gt;j)=本轮「开始 i 个 -&gt; 结束 j 个」的机率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    只有 结束&gt;=开始 才有值（B1 不会消失）-&gt; T 为上三角矩阵</t>
+  </si>
+  <si>
+    <t>3) 初始：第1轮确定从 0 个 B1 出发 -&gt; d1 = T 的第0行 = Table4「开始=0」那一列 (I列)</t>
+  </si>
+  <si>
+    <t>4) 每多开一轮，把上一轮分布再乘一次 T：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    d2 = d1*T，d3 = d2*T，…，d5 = e0*T^5 （e0=[1,0,0,…] 起点在0）</t>
+  </si>
+  <si>
+    <t>5) Table5 第 n 列 = 初始0个在 T^n 的第 0 行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    （J/K/L/M 列 = T^2 / T^3 / T^4 / T^5 的行0）</t>
+  </si>
+  <si>
+    <t>6) 单格算法（结束=j）：取 Table4 第 j 行(开始0~j) 点乘 上一轮分布列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    -&gt; 即 J83 的 MMULT：行向量 1*(j+1) x 列向量 (j+1)*1 = 标量</t>
   </si>
   <si>
     <t>第5轮结束后开出 5 个以上 B1 的机率</t>
@@ -615,7 +675,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000000000%"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +731,13 @@
       <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -877,6 +944,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -884,12 +957,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1256,137 +1323,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1415,10 +1482,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1454,7 +1521,7 @@
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1497,17 +1564,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1518,7 +1603,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1528,55 +1613,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2169,44 +2237,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A3" s="54"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:10">
       <c r="A4" s="29" t="s">
@@ -2214,56 +2282,56 @@
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A5" s="54"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:10">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="59" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2274,64 +2342,64 @@
       <c r="B9" s="29"/>
       <c r="C9" s="29"/>
       <c r="D9" s="29"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
     </row>
     <row r="10" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A10" s="54"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A13" s="54"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:10">
       <c r="A14" s="29" t="s">
@@ -2342,1210 +2410,1210 @@
       <c r="D14" s="29"/>
       <c r="E14" s="29"/>
       <c r="F14" s="29"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A15" s="54"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="53"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
     </row>
     <row r="16" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="53"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:10">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A18" s="58"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
+      <c r="A18" s="64"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="57"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="63"/>
     </row>
     <row r="22" ht="33" customHeight="1" spans="1:10">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="63"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="57"/>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
     </row>
     <row r="24" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A24" s="58"/>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A25" s="62" t="s">
+      <c r="A25" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="63"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A27" s="62" t="s">
+      <c r="A27" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
+      <c r="B27" s="63"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A28" s="62" t="s">
+      <c r="A28" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:10">
-      <c r="A30" s="63" t="s">
+      <c r="A30" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="64" t="s">
+      <c r="B30" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="66" t="s">
+      <c r="B31" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="66"/>
-      <c r="J31" s="57"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="63"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A32" s="65" t="s">
+      <c r="A32" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="66" t="s">
+      <c r="B32" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="57"/>
-      <c r="J32" s="57"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A33" s="65" t="s">
+      <c r="A33" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="66" t="s">
+      <c r="B33" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="66"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="57"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="63"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="66" t="s">
+      <c r="B34" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="66"/>
-      <c r="D34" s="66"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="57"/>
-      <c r="J34" s="57"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="63"/>
     </row>
     <row r="35" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A35" s="58"/>
-      <c r="B35" s="57"/>
-      <c r="C35" s="57"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
-      <c r="I35" s="57"/>
-      <c r="J35" s="57"/>
+      <c r="A35" s="64"/>
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A36" s="61" t="s">
+      <c r="A36" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
+      <c r="B36" s="63"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
     </row>
     <row r="37" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A37" s="58"/>
-      <c r="B37" s="57"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="57"/>
-      <c r="J37" s="57"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="62" t="s">
+      <c r="A38" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="57"/>
-      <c r="J38" s="57"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="63"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:10">
-      <c r="A39" s="63" t="s">
+      <c r="A39" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="64" t="s">
+      <c r="B39" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="64" t="s">
+      <c r="C39" s="70" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="64" t="s">
+      <c r="D39" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="64" t="s">
+      <c r="E39" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="64" t="s">
+      <c r="F39" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="57"/>
-      <c r="J39" s="57"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A40" s="65" t="s">
+      <c r="A40" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="67">
+      <c r="B40" s="73">
         <v>0.1</v>
       </c>
-      <c r="C40" s="67">
+      <c r="C40" s="73">
         <v>0.15</v>
       </c>
-      <c r="D40" s="67">
+      <c r="D40" s="73">
         <v>0.2</v>
       </c>
-      <c r="E40" s="67">
+      <c r="E40" s="73">
         <v>0.25</v>
       </c>
-      <c r="F40" s="67">
+      <c r="F40" s="73">
         <v>0.3</v>
       </c>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="57"/>
-      <c r="J40" s="57"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="63"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
     </row>
     <row r="41" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A41" s="58"/>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="57"/>
-      <c r="J41" s="57"/>
+      <c r="A41" s="64"/>
+      <c r="B41" s="63"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="63"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="62" t="s">
+      <c r="A42" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="63"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="63"/>
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
+      <c r="J43" s="63"/>
     </row>
     <row r="44" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A44" s="58"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="57"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="63"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="63"/>
     </row>
     <row r="45" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="60" t="s">
+      <c r="A45" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="60"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="57"/>
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="63"/>
+      <c r="I45" s="63"/>
+      <c r="J45" s="63"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="62" t="s">
+      <c r="A46" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="57"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="57"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="57"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="63"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="63"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A47" s="62" t="s">
+      <c r="A47" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="57"/>
-      <c r="C47" s="57"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="57"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="63"/>
+      <c r="I47" s="63"/>
+      <c r="J47" s="63"/>
     </row>
     <row r="48" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A48" s="68" t="s">
+      <c r="A48" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="68"/>
-      <c r="C48" s="68"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
+      <c r="B48" s="74"/>
+      <c r="C48" s="74"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="74"/>
+      <c r="J48" s="74"/>
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A49" s="61" t="s">
+      <c r="A49" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="57"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="57"/>
-      <c r="E49" s="57"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
-      <c r="I49" s="57"/>
-      <c r="J49" s="57"/>
+      <c r="B49" s="63"/>
+      <c r="C49" s="63"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63"/>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="63"/>
+      <c r="J49" s="63"/>
     </row>
     <row r="50" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A50" s="58"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="57"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
-      <c r="I50" s="57"/>
-      <c r="J50" s="57"/>
+      <c r="A50" s="64"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="J50" s="63"/>
     </row>
     <row r="51" ht="33" customHeight="1" spans="1:10">
-      <c r="A51" s="60" t="s">
+      <c r="A51" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="60"/>
-      <c r="C51" s="60"/>
-      <c r="D51" s="60"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="57"/>
-      <c r="J51" s="57"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A52" s="62" t="s">
+      <c r="A52" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="B52" s="57"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="57"/>
-      <c r="J52" s="57"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A53" s="62" t="s">
+      <c r="A53" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="57"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="57"/>
-      <c r="E53" s="57"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="57"/>
-      <c r="J53" s="57"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="63"/>
+      <c r="I53" s="63"/>
+      <c r="J53" s="63"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A54" s="62" t="s">
+      <c r="A54" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="B54" s="57"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="57"/>
-      <c r="E54" s="57"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="57"/>
-      <c r="J54" s="57"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="63"/>
+      <c r="I54" s="63"/>
+      <c r="J54" s="63"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A55" s="62" t="s">
+      <c r="A55" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="57"/>
-      <c r="C55" s="57"/>
-      <c r="D55" s="57"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="57"/>
-      <c r="J55" s="57"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A56" s="61" t="s">
+      <c r="A56" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="57"/>
-      <c r="C56" s="57"/>
-      <c r="D56" s="57"/>
-      <c r="E56" s="57"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="57"/>
-      <c r="J56" s="57"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="63"/>
+      <c r="I56" s="63"/>
+      <c r="J56" s="63"/>
     </row>
     <row r="57" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A57" s="58"/>
-      <c r="B57" s="57"/>
-      <c r="C57" s="57"/>
-      <c r="D57" s="57"/>
-      <c r="E57" s="57"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-      <c r="H57" s="57"/>
-      <c r="I57" s="57"/>
-      <c r="J57" s="57"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="63"/>
+      <c r="H57" s="63"/>
+      <c r="I57" s="63"/>
+      <c r="J57" s="63"/>
     </row>
     <row r="58" ht="33" customHeight="1" spans="1:10">
-      <c r="A58" s="60" t="s">
+      <c r="A58" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="B58" s="60"/>
-      <c r="C58" s="60"/>
-      <c r="D58" s="60"/>
-      <c r="E58" s="60"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="57"/>
-      <c r="I58" s="57"/>
-      <c r="J58" s="57"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="63"/>
+      <c r="J58" s="63"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A59" s="62" t="s">
+      <c r="A59" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="B59" s="57"/>
-      <c r="C59" s="57"/>
-      <c r="D59" s="57"/>
-      <c r="E59" s="57"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="57"/>
-      <c r="J59" s="57"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="63"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A60" s="60" t="s">
+      <c r="A60" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="60"/>
-      <c r="C60" s="60"/>
-      <c r="D60" s="57"/>
-      <c r="E60" s="57"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="57"/>
-      <c r="H60" s="57"/>
-      <c r="I60" s="57"/>
-      <c r="J60" s="57"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="63"/>
+      <c r="I60" s="63"/>
+      <c r="J60" s="63"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="57"/>
-      <c r="I61" s="57"/>
-      <c r="J61" s="57"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="63"/>
+      <c r="I61" s="63"/>
+      <c r="J61" s="63"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A62" s="62" t="s">
+      <c r="A62" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="B62" s="57"/>
-      <c r="C62" s="57"/>
-      <c r="D62" s="57"/>
-      <c r="E62" s="57"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="57"/>
-      <c r="I62" s="57"/>
-      <c r="J62" s="57"/>
+      <c r="B62" s="63"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+      <c r="J62" s="63"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A63" s="62" t="s">
+      <c r="A63" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="57"/>
-      <c r="C63" s="57"/>
-      <c r="D63" s="57"/>
-      <c r="E63" s="57"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
-      <c r="I63" s="57"/>
-      <c r="J63" s="57"/>
+      <c r="B63" s="63"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="63"/>
+      <c r="H63" s="63"/>
+      <c r="I63" s="63"/>
+      <c r="J63" s="63"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A64" s="62" t="s">
+      <c r="A64" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="B64" s="57"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
-      <c r="I64" s="57"/>
-      <c r="J64" s="57"/>
+      <c r="B64" s="63"/>
+      <c r="C64" s="63"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="63"/>
+      <c r="G64" s="63"/>
+      <c r="H64" s="63"/>
+      <c r="I64" s="63"/>
+      <c r="J64" s="63"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A65" s="62" t="s">
+      <c r="A65" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="B65" s="57"/>
-      <c r="C65" s="57"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="57"/>
-      <c r="F65" s="57"/>
-      <c r="G65" s="57"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="57"/>
-      <c r="J65" s="57"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63"/>
+      <c r="H65" s="63"/>
+      <c r="I65" s="63"/>
+      <c r="J65" s="63"/>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:22">
-      <c r="A66" s="69" t="s">
+      <c r="A66" s="75" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A67" s="62" t="s">
+      <c r="A67" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="B67" s="57"/>
-      <c r="C67" s="57"/>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="57"/>
-      <c r="J67" s="57"/>
+      <c r="B67" s="63"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="63"/>
+      <c r="I67" s="63"/>
+      <c r="J67" s="63"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A68" s="62" t="s">
+      <c r="A68" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="B68" s="57"/>
-      <c r="C68" s="57"/>
-      <c r="D68" s="57"/>
-      <c r="E68" s="57"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
-      <c r="I68" s="57"/>
-      <c r="J68" s="57"/>
+      <c r="B68" s="63"/>
+      <c r="C68" s="63"/>
+      <c r="D68" s="63"/>
+      <c r="E68" s="63"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="63"/>
+      <c r="H68" s="63"/>
+      <c r="I68" s="63"/>
+      <c r="J68" s="63"/>
     </row>
     <row r="69" ht="33" customHeight="1" spans="1:22">
-      <c r="A69" s="60" t="s">
+      <c r="A69" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="B69" s="60"/>
-      <c r="C69" s="60"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="60"/>
-      <c r="F69" s="60"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="57"/>
-      <c r="J69" s="57"/>
+      <c r="B69" s="66"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="63"/>
+      <c r="J69" s="63"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A70" s="62" t="s">
+      <c r="A70" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="57"/>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
-      <c r="E70" s="57"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
-      <c r="I70" s="57"/>
-      <c r="J70" s="57"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="63"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="63"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="63"/>
+      <c r="J70" s="63"/>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:22">
-      <c r="A71" s="70" t="s">
+      <c r="A71" s="76" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A72" s="61" t="s">
+      <c r="A72" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="57"/>
-      <c r="C72" s="57"/>
-      <c r="D72" s="57"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
+      <c r="B72" s="63"/>
+      <c r="C72" s="63"/>
+      <c r="D72" s="63"/>
+      <c r="E72" s="63"/>
+      <c r="F72" s="63"/>
+      <c r="G72" s="63"/>
+      <c r="H72" s="63"/>
+      <c r="I72" s="63"/>
+      <c r="J72" s="63"/>
     </row>
     <row r="73" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A73" s="58"/>
-      <c r="B73" s="57"/>
-      <c r="C73" s="57"/>
-      <c r="D73" s="57"/>
-      <c r="E73" s="57"/>
-      <c r="F73" s="57"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="57"/>
-      <c r="J73" s="57"/>
+      <c r="A73" s="64"/>
+      <c r="B73" s="63"/>
+      <c r="C73" s="63"/>
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
+      <c r="F73" s="63"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="63"/>
+      <c r="I73" s="63"/>
+      <c r="J73" s="63"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A74" s="62" t="s">
+      <c r="A74" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="57"/>
-      <c r="C74" s="57"/>
-      <c r="D74" s="57"/>
-      <c r="E74" s="57"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
+      <c r="B74" s="63"/>
+      <c r="C74" s="63"/>
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="F74" s="63"/>
+      <c r="G74" s="63"/>
+      <c r="H74" s="63"/>
+      <c r="I74" s="63"/>
+      <c r="J74" s="63"/>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:22">
-      <c r="A75" s="63" t="s">
+      <c r="A75" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="64" t="s">
+      <c r="B75" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="C75" s="57"/>
-      <c r="D75" s="57"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
+      <c r="C75" s="63"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="63"/>
+      <c r="F75" s="63"/>
+      <c r="G75" s="63"/>
+      <c r="H75" s="63"/>
+      <c r="I75" s="63"/>
+      <c r="J75" s="63"/>
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:22">
-      <c r="A76" s="65" t="s">
+      <c r="A76" s="71" t="s">
         <v>71</v>
       </c>
-      <c r="B76" s="66" t="s">
+      <c r="B76" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C76" s="66"/>
-      <c r="D76" s="57"/>
-      <c r="E76" s="57"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="57"/>
+      <c r="C76" s="72"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="63"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="63"/>
+      <c r="I76" s="63"/>
+      <c r="J76" s="63"/>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:22">
-      <c r="A77" s="65" t="s">
+      <c r="A77" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="71" t="s">
+      <c r="B77" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="71"/>
-      <c r="D77" s="71"/>
-      <c r="E77" s="71"/>
-      <c r="F77" s="71"/>
-      <c r="G77" s="71"/>
-      <c r="H77" s="71"/>
-      <c r="I77" s="71"/>
-      <c r="J77" s="71"/>
-      <c r="K77" s="71"/>
-      <c r="L77" s="71"/>
-      <c r="M77" s="71"/>
-      <c r="N77" s="71"/>
-      <c r="O77" s="71"/>
-      <c r="P77" s="71"/>
-      <c r="Q77" s="71"/>
-      <c r="R77" s="71"/>
-      <c r="S77" s="71"/>
-      <c r="T77" s="71"/>
-      <c r="U77" s="71"/>
-      <c r="V77" s="71"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="77"/>
+      <c r="E77" s="77"/>
+      <c r="F77" s="77"/>
+      <c r="G77" s="77"/>
+      <c r="H77" s="77"/>
+      <c r="I77" s="77"/>
+      <c r="J77" s="77"/>
+      <c r="K77" s="77"/>
+      <c r="L77" s="77"/>
+      <c r="M77" s="77"/>
+      <c r="N77" s="77"/>
+      <c r="O77" s="77"/>
+      <c r="P77" s="77"/>
+      <c r="Q77" s="77"/>
+      <c r="R77" s="77"/>
+      <c r="S77" s="77"/>
+      <c r="T77" s="77"/>
+      <c r="U77" s="77"/>
+      <c r="V77" s="77"/>
     </row>
     <row r="78" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A78" s="58"/>
-      <c r="B78" s="57"/>
-      <c r="C78" s="57"/>
-      <c r="D78" s="57"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="57"/>
+      <c r="A78" s="64"/>
+      <c r="B78" s="63"/>
+      <c r="C78" s="63"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="63"/>
+      <c r="F78" s="63"/>
+      <c r="G78" s="63"/>
+      <c r="H78" s="63"/>
+      <c r="I78" s="63"/>
+      <c r="J78" s="63"/>
     </row>
     <row r="79" ht="33" customHeight="1" spans="1:22">
-      <c r="A79" s="60" t="s">
+      <c r="A79" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="B79" s="60"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="60"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57"/>
-      <c r="I79" s="57"/>
-      <c r="J79" s="57"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="63"/>
+      <c r="G79" s="63"/>
+      <c r="H79" s="63"/>
+      <c r="I79" s="63"/>
+      <c r="J79" s="63"/>
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A80" s="61" t="s">
+      <c r="A80" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="B80" s="57"/>
-      <c r="C80" s="57"/>
-      <c r="D80" s="57"/>
-      <c r="E80" s="57"/>
-      <c r="F80" s="57"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="57"/>
-      <c r="I80" s="57"/>
-      <c r="J80" s="57"/>
+      <c r="B80" s="63"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
+      <c r="F80" s="63"/>
+      <c r="G80" s="63"/>
+      <c r="H80" s="63"/>
+      <c r="I80" s="63"/>
+      <c r="J80" s="63"/>
     </row>
     <row r="81" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A81" s="58"/>
-      <c r="B81" s="57"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
-      <c r="E81" s="57"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
+      <c r="A81" s="64"/>
+      <c r="B81" s="63"/>
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="63"/>
+      <c r="J81" s="63"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A82" s="62" t="s">
+      <c r="A82" s="68" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="57"/>
-      <c r="D82" s="57"/>
-      <c r="E82" s="57"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57"/>
-      <c r="I82" s="57"/>
-      <c r="J82" s="57"/>
+      <c r="B82" s="63"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="63"/>
+      <c r="J82" s="63"/>
     </row>
     <row r="83" ht="33" customHeight="1" spans="1:10">
-      <c r="A83" s="60" t="s">
+      <c r="A83" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="B83" s="60"/>
-      <c r="C83" s="60"/>
-      <c r="D83" s="60"/>
-      <c r="E83" s="57"/>
-      <c r="F83" s="57"/>
-      <c r="G83" s="57"/>
-      <c r="H83" s="57"/>
-      <c r="I83" s="57"/>
-      <c r="J83" s="57"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="66"/>
+      <c r="D83" s="66"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
+      <c r="I83" s="63"/>
+      <c r="J83" s="63"/>
     </row>
     <row r="84" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A84" s="60" t="s">
+      <c r="A84" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="B84" s="60"/>
-      <c r="C84" s="60"/>
-      <c r="D84" s="60"/>
-      <c r="E84" s="60"/>
-      <c r="F84" s="60"/>
-      <c r="G84" s="60"/>
-      <c r="H84" s="60"/>
-      <c r="I84" s="60"/>
-      <c r="J84" s="57"/>
+      <c r="B84" s="66"/>
+      <c r="C84" s="66"/>
+      <c r="D84" s="66"/>
+      <c r="E84" s="66"/>
+      <c r="F84" s="66"/>
+      <c r="G84" s="66"/>
+      <c r="H84" s="66"/>
+      <c r="I84" s="66"/>
+      <c r="J84" s="63"/>
     </row>
     <row r="85" ht="33" customHeight="1" spans="1:10">
-      <c r="A85" s="60" t="s">
+      <c r="A85" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="B85" s="60"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="60"/>
-      <c r="H85" s="57"/>
-      <c r="I85" s="57"/>
-      <c r="J85" s="57"/>
+      <c r="B85" s="66"/>
+      <c r="C85" s="66"/>
+      <c r="D85" s="66"/>
+      <c r="E85" s="66"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="66"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="63"/>
+      <c r="J85" s="63"/>
     </row>
     <row r="86" ht="33" customHeight="1" spans="1:10">
-      <c r="A86" s="60" t="s">
+      <c r="A86" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="B86" s="60"/>
-      <c r="C86" s="60"/>
-      <c r="D86" s="60"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="57"/>
-      <c r="I86" s="57"/>
-      <c r="J86" s="57"/>
+      <c r="B86" s="66"/>
+      <c r="C86" s="66"/>
+      <c r="D86" s="66"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="63"/>
+      <c r="J86" s="63"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A87" s="61" t="s">
+      <c r="A87" s="67" t="s">
         <v>82</v>
       </c>
-      <c r="B87" s="57"/>
-      <c r="C87" s="57"/>
-      <c r="D87" s="57"/>
-      <c r="E87" s="57"/>
-      <c r="F87" s="57"/>
-      <c r="G87" s="57"/>
-      <c r="H87" s="57"/>
-      <c r="I87" s="57"/>
-      <c r="J87" s="57"/>
+      <c r="B87" s="63"/>
+      <c r="C87" s="63"/>
+      <c r="D87" s="63"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="63"/>
+      <c r="J87" s="63"/>
     </row>
     <row r="88" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A88" s="58"/>
-      <c r="B88" s="57"/>
-      <c r="C88" s="57"/>
-      <c r="D88" s="57"/>
-      <c r="E88" s="57"/>
-      <c r="F88" s="57"/>
-      <c r="G88" s="57"/>
-      <c r="H88" s="57"/>
-      <c r="I88" s="57"/>
-      <c r="J88" s="57"/>
+      <c r="A88" s="64"/>
+      <c r="B88" s="63"/>
+      <c r="C88" s="63"/>
+      <c r="D88" s="63"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="63"/>
+      <c r="I88" s="63"/>
+      <c r="J88" s="63"/>
     </row>
     <row r="89" ht="18" customHeight="1" spans="1:10">
-      <c r="A89" s="63" t="s">
+      <c r="A89" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="64" t="s">
+      <c r="B89" s="70" t="s">
         <v>71</v>
       </c>
-      <c r="C89" s="57"/>
-      <c r="D89" s="57"/>
-      <c r="E89" s="57"/>
-      <c r="F89" s="57"/>
-      <c r="G89" s="57"/>
-      <c r="H89" s="57"/>
-      <c r="I89" s="57"/>
-      <c r="J89" s="57"/>
+      <c r="C89" s="63"/>
+      <c r="D89" s="63"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63"/>
+      <c r="J89" s="63"/>
     </row>
     <row r="90" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A90" s="65" t="s">
+      <c r="A90" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="72" t="s">
+      <c r="B90" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="C90" s="57"/>
-      <c r="D90" s="57"/>
-      <c r="E90" s="57"/>
-      <c r="F90" s="57"/>
-      <c r="G90" s="57"/>
-      <c r="H90" s="57"/>
-      <c r="I90" s="57"/>
-      <c r="J90" s="57"/>
+      <c r="C90" s="63"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63"/>
+      <c r="J90" s="63"/>
     </row>
     <row r="91" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A91" s="65" t="s">
+      <c r="A91" s="71" t="s">
         <v>86</v>
       </c>
-      <c r="B91" s="66" t="s">
+      <c r="B91" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="C91" s="66"/>
-      <c r="D91" s="57"/>
-      <c r="E91" s="57"/>
-      <c r="F91" s="57"/>
-      <c r="G91" s="57"/>
-      <c r="H91" s="57"/>
-      <c r="I91" s="57"/>
-      <c r="J91" s="57"/>
+      <c r="C91" s="72"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="63"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="63"/>
+      <c r="J91" s="63"/>
     </row>
     <row r="92" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A92" s="65" t="s">
+      <c r="A92" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="B92" s="66" t="s">
+      <c r="B92" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="C92" s="66"/>
-      <c r="D92" s="57"/>
-      <c r="E92" s="57"/>
-      <c r="F92" s="57"/>
-      <c r="G92" s="57"/>
-      <c r="H92" s="57"/>
-      <c r="I92" s="57"/>
-      <c r="J92" s="57"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="63"/>
+      <c r="J92" s="63"/>
     </row>
     <row r="93" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A93" s="65" t="s">
+      <c r="A93" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="B93" s="66" t="s">
+      <c r="B93" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="66"/>
-      <c r="D93" s="57"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="57"/>
-      <c r="H93" s="57"/>
-      <c r="I93" s="57"/>
-      <c r="J93" s="57"/>
+      <c r="C93" s="72"/>
+      <c r="D93" s="63"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="63"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="63"/>
+      <c r="J93" s="63"/>
     </row>
     <row r="94" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A94" s="65" t="s">
+      <c r="A94" s="71" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="66" t="s">
+      <c r="B94" s="72" t="s">
         <v>93</v>
       </c>
-      <c r="C94" s="66"/>
-      <c r="D94" s="57"/>
-      <c r="E94" s="57"/>
-      <c r="F94" s="57"/>
-      <c r="G94" s="57"/>
-      <c r="H94" s="57"/>
-      <c r="I94" s="57"/>
-      <c r="J94" s="57"/>
+      <c r="C94" s="72"/>
+      <c r="D94" s="63"/>
+      <c r="E94" s="63"/>
+      <c r="F94" s="63"/>
+      <c r="G94" s="63"/>
+      <c r="H94" s="63"/>
+      <c r="I94" s="63"/>
+      <c r="J94" s="63"/>
     </row>
     <row r="95" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A95" s="65" t="s">
+      <c r="A95" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="66" t="s">
+      <c r="B95" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="66"/>
-      <c r="D95" s="57"/>
-      <c r="E95" s="57"/>
-      <c r="F95" s="57"/>
-      <c r="G95" s="57"/>
-      <c r="H95" s="57"/>
-      <c r="I95" s="57"/>
-      <c r="J95" s="57"/>
+      <c r="C95" s="72"/>
+      <c r="D95" s="63"/>
+      <c r="E95" s="63"/>
+      <c r="F95" s="63"/>
+      <c r="G95" s="63"/>
+      <c r="H95" s="63"/>
+      <c r="I95" s="63"/>
+      <c r="J95" s="63"/>
     </row>
     <row r="96" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A96" s="65" t="s">
+      <c r="A96" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="B96" s="66" t="s">
+      <c r="B96" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="C96" s="66"/>
-      <c r="D96" s="57"/>
-      <c r="E96" s="57"/>
-      <c r="F96" s="57"/>
-      <c r="G96" s="57"/>
-      <c r="H96" s="57"/>
-      <c r="I96" s="57"/>
-      <c r="J96" s="57"/>
+      <c r="C96" s="72"/>
+      <c r="D96" s="63"/>
+      <c r="E96" s="63"/>
+      <c r="F96" s="63"/>
+      <c r="G96" s="63"/>
+      <c r="H96" s="63"/>
+      <c r="I96" s="63"/>
+      <c r="J96" s="63"/>
     </row>
     <row r="97" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A97" s="65" t="s">
+      <c r="A97" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="B97" s="66" t="s">
+      <c r="B97" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="C97" s="66"/>
-      <c r="D97" s="57"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="57"/>
-      <c r="J97" s="57"/>
+      <c r="C97" s="72"/>
+      <c r="D97" s="63"/>
+      <c r="E97" s="63"/>
+      <c r="F97" s="63"/>
+      <c r="G97" s="63"/>
+      <c r="H97" s="63"/>
+      <c r="I97" s="63"/>
+      <c r="J97" s="63"/>
     </row>
     <row r="98" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A98" s="65" t="s">
+      <c r="A98" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="66" t="s">
+      <c r="B98" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="C98" s="66"/>
-      <c r="D98" s="57"/>
-      <c r="E98" s="57"/>
-      <c r="F98" s="57"/>
-      <c r="G98" s="57"/>
-      <c r="H98" s="57"/>
-      <c r="I98" s="57"/>
-      <c r="J98" s="57"/>
+      <c r="C98" s="72"/>
+      <c r="D98" s="63"/>
+      <c r="E98" s="63"/>
+      <c r="F98" s="63"/>
+      <c r="G98" s="63"/>
+      <c r="H98" s="63"/>
+      <c r="I98" s="63"/>
+      <c r="J98" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -3598,12 +3666,12 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="28.2857142857143" customWidth="1"/>
-    <col min="3" max="3" width="17.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="19.3392857142857" customWidth="1"/>
     <col min="4" max="4" width="19.7857142857143" customWidth="1"/>
     <col min="5" max="5" width="18.5982142857143" customWidth="1"/>
     <col min="6" max="6" width="21.5714285714286" customWidth="1"/>
     <col min="7" max="7" width="9.28571428571429" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="8" max="8" width="26.6339285714286" customWidth="1"/>
     <col min="9" max="9" width="21.4285714285714" customWidth="1"/>
     <col min="10" max="10" width="19.4285714285714" customWidth="1"/>
     <col min="11" max="11" width="24.5714285714286" customWidth="1"/>
@@ -4527,23 +4595,23 @@
       <c r="A23" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="77">
+      <c r="B23" s="27">
         <f>SUM(B7:B22)</f>
         <v>1</v>
       </c>
-      <c r="C23" s="77">
+      <c r="C23" s="27">
         <f>SUM(C7:C22)</f>
         <v>1</v>
       </c>
-      <c r="D23" s="77">
+      <c r="D23" s="27">
         <f>SUM(D7:D22)</f>
         <v>1</v>
       </c>
-      <c r="E23" s="77">
+      <c r="E23" s="27">
         <f>SUM(E7:E22)</f>
         <v>1</v>
       </c>
-      <c r="F23" s="77">
+      <c r="F23" s="27">
         <f>SUM(F7:F22)</f>
         <v>1</v>
       </c>
@@ -4767,23 +4835,23 @@
         <v>0</v>
       </c>
       <c r="I30" s="40">
-        <f t="shared" ref="I30:I35" si="5">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
-        <v>0.98727951635875</v>
+        <f>_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
+        <v>0.987279516358749</v>
       </c>
       <c r="J30" s="40">
-        <f t="shared" ref="J30:J35" si="6">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
+        <f t="shared" ref="J30:J35" si="5">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(J$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.93829461326294</v>
       </c>
       <c r="K30" s="40">
-        <f t="shared" ref="K30:K35" si="7">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
+        <f t="shared" ref="K30:K35" si="6">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(K$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.835766276063232</v>
       </c>
       <c r="L30" s="40">
-        <f t="shared" ref="L30:L35" si="8">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
+        <f t="shared" ref="L30:L35" si="7">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(L$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.686485941521823</v>
       </c>
       <c r="M30" s="40">
-        <f t="shared" ref="M30:M35" si="9">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
+        <f t="shared" ref="M30:M35" si="8">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(M$29,$B$30:$D$35,3,FALSE),$H30,IF($H30=15,15,$H31-1))</f>
         <v>0.515491059226843</v>
       </c>
       <c r="S30" s="16"/>
@@ -4814,23 +4882,23 @@
         <v>5</v>
       </c>
       <c r="I31" s="40">
+        <f t="shared" ref="I30:I35" si="9">_xlfn.BINOM.DIST.RANGE($F$45,VLOOKUP(I$29,$B$30:$D$35,3,FALSE),$H31,IF($H31=15,15,$H32-1))</f>
+        <v>0.012717637158798</v>
+      </c>
+      <c r="J31" s="40">
         <f t="shared" si="5"/>
-        <v>0.012717637158798</v>
-      </c>
-      <c r="J31" s="40">
+        <v>0.0616244821124746</v>
+      </c>
+      <c r="K31" s="40">
         <f t="shared" si="6"/>
-        <v>0.0616244821124746</v>
-      </c>
-      <c r="K31" s="40">
+        <v>0.163448738545664</v>
+      </c>
+      <c r="L31" s="40">
         <f t="shared" si="7"/>
-        <v>0.163448738545664</v>
-      </c>
-      <c r="L31" s="40">
+        <v>0.309321044012904</v>
+      </c>
+      <c r="M31" s="40">
         <f t="shared" si="8"/>
-        <v>0.309321044012904</v>
-      </c>
-      <c r="M31" s="40">
-        <f t="shared" si="9"/>
         <v>0.469266415003386</v>
       </c>
       <c r="S31" s="16"/>
@@ -4861,23 +4929,23 @@
         <v>9</v>
       </c>
       <c r="I32" s="40">
+        <f t="shared" si="9"/>
+        <v>2.846142117e-6</v>
+      </c>
+      <c r="J32" s="40">
         <f t="shared" si="5"/>
-        <v>2.846142117e-6</v>
-      </c>
-      <c r="J32" s="40">
+        <v>8.08668558803214e-5</v>
+      </c>
+      <c r="K32" s="40">
         <f t="shared" si="6"/>
-        <v>8.08668558803214e-5</v>
-      </c>
-      <c r="K32" s="40">
+        <v>0.000783974137856</v>
+      </c>
+      <c r="L32" s="40">
         <f t="shared" si="7"/>
-        <v>0.000783974137856</v>
-      </c>
-      <c r="L32" s="40">
+        <v>0.00418065022677183</v>
+      </c>
+      <c r="M32" s="40">
         <f t="shared" si="8"/>
-        <v>0.00418065022677183</v>
-      </c>
-      <c r="M32" s="40">
-        <f t="shared" si="9"/>
         <v>0.015150867077619</v>
       </c>
       <c r="S32" s="16"/>
@@ -4908,23 +4976,23 @@
         <v>12</v>
       </c>
       <c r="I33" s="40">
+        <f t="shared" si="9"/>
+        <v>3.40200000000002e-10</v>
+      </c>
+      <c r="J33" s="40">
         <f t="shared" si="5"/>
-        <v>3.40200000000002e-10</v>
-      </c>
-      <c r="J33" s="40">
+        <v>3.77310459732056e-8</v>
+      </c>
+      <c r="K33" s="40">
         <f t="shared" si="6"/>
-        <v>3.77310459732056e-8</v>
-      </c>
-      <c r="K33" s="40">
+        <v>1.0092544e-6</v>
+      </c>
+      <c r="L33" s="40">
         <f t="shared" si="7"/>
-        <v>1.0092544e-6</v>
-      </c>
-      <c r="L33" s="40">
+        <v>1.23213976621628e-5</v>
+      </c>
+      <c r="M33" s="40">
         <f t="shared" si="8"/>
-        <v>1.23213976621628e-5</v>
-      </c>
-      <c r="M33" s="40">
-        <f t="shared" si="9"/>
         <v>9.11421315000001e-5</v>
       </c>
       <c r="S33" s="16"/>
@@ -4955,23 +5023,23 @@
         <v>14</v>
       </c>
       <c r="I34" s="40">
+        <f t="shared" si="9"/>
+        <v>1.35e-13</v>
+      </c>
+      <c r="J34" s="40">
         <f t="shared" si="5"/>
-        <v>1.35e-13</v>
-      </c>
-      <c r="J34" s="40">
+        <v>3.7220980682373e-11</v>
+      </c>
+      <c r="K34" s="40">
         <f t="shared" si="6"/>
-        <v>3.7220980682373e-11</v>
-      </c>
-      <c r="K34" s="40">
+        <v>1.96607999999999e-9</v>
+      </c>
+      <c r="L34" s="40">
         <f t="shared" si="7"/>
-        <v>1.96607999999999e-9</v>
-      </c>
-      <c r="L34" s="40">
+        <v>4.19095158576965e-8</v>
+      </c>
+      <c r="M34" s="40">
         <f t="shared" si="8"/>
-        <v>4.19095158576965e-8</v>
-      </c>
-      <c r="M34" s="40">
-        <f t="shared" si="9"/>
         <v>5.02211745e-7</v>
       </c>
       <c r="S34" s="16"/>
@@ -5000,23 +5068,23 @@
         <v>15</v>
       </c>
       <c r="I35" s="40">
+        <f t="shared" si="9"/>
+        <v>1e-15</v>
+      </c>
+      <c r="J35" s="40">
         <f t="shared" si="5"/>
-        <v>1e-15</v>
-      </c>
-      <c r="J35" s="40">
+        <v>4.3789389038086e-13</v>
+      </c>
+      <c r="K35" s="40">
         <f t="shared" si="6"/>
-        <v>4.3789389038086e-13</v>
-      </c>
-      <c r="K35" s="40">
+        <v>3.2768e-11</v>
+      </c>
+      <c r="L35" s="40">
         <f t="shared" si="7"/>
-        <v>3.2768e-11</v>
-      </c>
-      <c r="L35" s="40">
+        <v>9.31322574615479e-10</v>
+      </c>
+      <c r="M35" s="40">
         <f t="shared" si="8"/>
-        <v>9.31322574615479e-10</v>
-      </c>
-      <c r="M35" s="40">
-        <f t="shared" si="9"/>
         <v>1.4348907e-8</v>
       </c>
       <c r="S35" s="16"/>
@@ -5685,17 +5753,19 @@
       <c r="D59" s="29"/>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
-      <c r="P59" s="16"/>
-      <c r="Q59" s="16"/>
+      <c r="G59" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
+      <c r="L59" s="42"/>
+      <c r="M59" s="42"/>
+      <c r="N59" s="42"/>
+      <c r="O59" s="42"/>
+      <c r="P59" s="42"/>
+      <c r="Q59" s="42"/>
       <c r="R59" s="16"/>
       <c r="S59" s="16"/>
       <c r="T59" s="16"/>
@@ -5707,7 +5777,7 @@
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:25">
       <c r="A60" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -5715,7 +5785,7 @@
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
@@ -5738,19 +5808,27 @@
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:25">
       <c r="A61" s="16"/>
-      <c r="B61" s="42" t="s">
+      <c r="B61" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="C61" s="43"/>
-      <c r="D61" s="43"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="45"/>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
       <c r="G61" s="16"/>
       <c r="H61" s="16"/>
-      <c r="I61" s="16"/>
-      <c r="J61" s="16"/>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
+      <c r="I61" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="J61" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>127</v>
+      </c>
       <c r="M61" s="16"/>
       <c r="N61" s="16"/>
       <c r="O61" s="16"/>
@@ -5767,7 +5845,7 @@
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:25">
       <c r="A62" s="16"/>
-      <c r="B62" s="43"/>
+      <c r="B62" s="46"/>
       <c r="C62" s="38" t="s">
         <v>113</v>
       </c>
@@ -5775,12 +5853,12 @@
         <v>39</v>
       </c>
       <c r="E62" s="16"/>
-      <c r="F62" s="16" t="s">
+      <c r="F62" s="47" t="s">
         <v>104</v>
       </c>
       <c r="G62" s="16"/>
       <c r="H62" s="19" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="I62" s="19">
         <v>0</v>
@@ -5834,273 +5912,279 @@
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:25">
       <c r="A63" s="16"/>
-      <c r="B63" s="43" t="s">
+      <c r="B63" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C63" s="43">
+      <c r="C63" s="38">
         <v>10</v>
       </c>
-      <c r="D63" s="44">
+      <c r="D63" s="39">
         <v>0.1</v>
       </c>
       <c r="E63" s="16"/>
-      <c r="F63" s="16" t="s">
+      <c r="F63" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="G63" s="16"/>
+      <c r="G63" s="16" t="s">
+        <v>129</v>
+      </c>
       <c r="H63" s="19">
         <v>0</v>
       </c>
-      <c r="I63" s="45">
-        <f t="shared" ref="I63:Y63" si="10">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I63" s="49">
+        <f>IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J63" s="80" t="str">
+      <c r="J63" s="49" t="str">
+        <f t="shared" ref="I63:Y63" si="10">IFERROR(BINOMDIST($H63-J$62,15-J$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+        <v/>
+      </c>
+      <c r="K63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="K63" s="80" t="str">
+      <c r="L63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="L63" s="80" t="str">
+      <c r="M63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M63" s="80" t="str">
+      <c r="N63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N63" s="80" t="str">
+      <c r="O63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O63" s="80" t="str">
+      <c r="P63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P63" s="80" t="str">
+      <c r="Q63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q63" s="80" t="str">
+      <c r="R63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="R63" s="80" t="str">
+      <c r="S63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="S63" s="80" t="str">
+      <c r="T63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="T63" s="80" t="str">
+      <c r="U63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="U63" s="80" t="str">
+      <c r="V63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V63" s="80" t="str">
+      <c r="W63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="W63" s="80" t="str">
+      <c r="X63" s="49" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="X63" s="80" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="Y63" s="45">
+      <c r="Y63" s="49">
         <f t="shared" si="10"/>
         <v>0.205891132094649</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:25">
       <c r="A64" s="16"/>
-      <c r="B64" s="43" t="s">
+      <c r="B64" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C64" s="43">
+      <c r="C64" s="38">
         <v>15</v>
       </c>
-      <c r="D64" s="44">
+      <c r="D64" s="39">
         <v>0.15</v>
       </c>
       <c r="E64" s="16"/>
       <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+      <c r="G64" s="16" t="s">
+        <v>130</v>
+      </c>
       <c r="H64" s="19">
         <v>1</v>
       </c>
-      <c r="I64" s="45">
-        <f t="shared" ref="I64:Y64" si="11">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I64" s="49">
+        <f>IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.343151886824415</v>
       </c>
-      <c r="J64" s="45">
+      <c r="J64" s="49">
+        <f t="shared" ref="I64:Y64" si="11">IFERROR(BINOMDIST($H64-J$62,15-J$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+        <v>0.22876792454961</v>
+      </c>
+      <c r="K64" s="49" t="str">
         <f t="shared" si="11"/>
-        <v>0.22876792454961</v>
-      </c>
-      <c r="K64" s="45" t="str">
+        <v/>
+      </c>
+      <c r="L64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="L64" s="45" t="str">
+      <c r="M64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="M64" s="45" t="str">
+      <c r="N64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="N64" s="80" t="str">
+      <c r="O64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O64" s="80" t="str">
+      <c r="P64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="P64" s="80" t="str">
+      <c r="Q64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="Q64" s="80" t="str">
+      <c r="R64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="R64" s="80" t="str">
+      <c r="S64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="S64" s="80" t="str">
+      <c r="T64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="T64" s="80" t="str">
+      <c r="U64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="U64" s="80" t="str">
+      <c r="V64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="V64" s="80" t="str">
+      <c r="W64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="W64" s="80" t="str">
+      <c r="X64" s="49" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="X64" s="80" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Y64" s="45">
+      <c r="Y64" s="49">
         <f t="shared" si="11"/>
         <v>0.343151886824415</v>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:25">
       <c r="A65" s="16"/>
-      <c r="B65" s="43" t="s">
+      <c r="B65" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="43">
+      <c r="C65" s="38">
         <v>20</v>
       </c>
-      <c r="D65" s="44">
+      <c r="D65" s="39">
         <v>0.2</v>
       </c>
       <c r="E65" s="16"/>
       <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+      <c r="G65" s="16" t="s">
+        <v>131</v>
+      </c>
       <c r="H65" s="19">
         <v>2</v>
       </c>
-      <c r="I65" s="45">
+      <c r="I65" s="49">
         <f t="shared" ref="I65:Y65" si="12">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.266895911974545</v>
       </c>
-      <c r="J65" s="45">
+      <c r="J65" s="49">
         <f t="shared" si="12"/>
         <v>0.35586121596606</v>
       </c>
-      <c r="K65" s="45">
+      <c r="K65" s="49">
         <f t="shared" si="12"/>
         <v>0.2541865828329</v>
       </c>
-      <c r="L65" s="45" t="str">
+      <c r="L65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="M65" s="45" t="str">
+      <c r="M65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="N65" s="80" t="str">
+      <c r="N65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="O65" s="80" t="str">
+      <c r="O65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="P65" s="80" t="str">
+      <c r="P65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="Q65" s="80" t="str">
+      <c r="Q65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="R65" s="80" t="str">
+      <c r="R65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="S65" s="80" t="str">
+      <c r="S65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="T65" s="80" t="str">
+      <c r="T65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="U65" s="80" t="str">
+      <c r="U65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="V65" s="80" t="str">
+      <c r="V65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="W65" s="80" t="str">
+      <c r="W65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="X65" s="80" t="str">
+      <c r="X65" s="49" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="Y65" s="45">
+      <c r="Y65" s="49">
         <f t="shared" si="12"/>
         <v>0.266895911974545</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:25">
       <c r="A66" s="16"/>
-      <c r="B66" s="43" t="s">
+      <c r="B66" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C66" s="43">
+      <c r="C66" s="38">
         <v>25</v>
       </c>
-      <c r="D66" s="44">
+      <c r="D66" s="39">
         <v>0.25</v>
       </c>
       <c r="E66" s="16"/>
@@ -6109,84 +6193,84 @@
       <c r="H66" s="19">
         <v>3</v>
       </c>
-      <c r="I66" s="45">
+      <c r="I66" s="49">
         <f t="shared" ref="I66:Y66" si="13">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.128505439098855</v>
       </c>
-      <c r="J66" s="45">
+      <c r="J66" s="49">
         <f t="shared" si="13"/>
         <v>0.25701087819771</v>
       </c>
-      <c r="K66" s="45">
+      <c r="K66" s="49">
         <f t="shared" si="13"/>
         <v>0.3671583974253</v>
       </c>
-      <c r="L66" s="45">
+      <c r="L66" s="49">
         <f t="shared" si="13"/>
         <v>0.282429536481</v>
       </c>
-      <c r="M66" s="45" t="str">
+      <c r="M66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="N66" s="80" t="str">
+      <c r="N66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="O66" s="80" t="str">
+      <c r="O66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="P66" s="80" t="str">
+      <c r="P66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q66" s="80" t="str">
+      <c r="Q66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="R66" s="80" t="str">
+      <c r="R66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="S66" s="80" t="str">
+      <c r="S66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="T66" s="80" t="str">
+      <c r="T66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="U66" s="80" t="str">
+      <c r="U66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="V66" s="80" t="str">
+      <c r="V66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="W66" s="80" t="str">
+      <c r="W66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="X66" s="80" t="str">
+      <c r="X66" s="49" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Y66" s="45">
+      <c r="Y66" s="49">
         <f t="shared" si="13"/>
         <v>0.128505439098855</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:25">
       <c r="A67" s="16"/>
-      <c r="B67" s="43" t="s">
+      <c r="B67" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="43">
+      <c r="C67" s="38">
         <v>30</v>
       </c>
-      <c r="D67" s="44">
+      <c r="D67" s="39">
         <v>0.3</v>
       </c>
       <c r="E67" s="16"/>
@@ -6195,155 +6279,155 @@
       <c r="H67" s="19">
         <v>4</v>
       </c>
-      <c r="I67" s="45">
+      <c r="I67" s="49">
         <f t="shared" ref="I67:Y67" si="14">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J67" s="45">
+      <c r="J67" s="49">
         <f t="shared" si="14"/>
         <v>0.11422705697676</v>
       </c>
-      <c r="K67" s="45">
+      <c r="K67" s="49">
         <f t="shared" si="14"/>
         <v>0.2447722649502</v>
       </c>
-      <c r="L67" s="45">
+      <c r="L67" s="49">
         <f t="shared" si="14"/>
         <v>0.376572715308</v>
       </c>
-      <c r="M67" s="45">
+      <c r="M67" s="49">
         <f t="shared" si="14"/>
         <v>0.31381059609</v>
       </c>
-      <c r="N67" s="80" t="str">
+      <c r="N67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O67" s="80" t="str">
+      <c r="O67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P67" s="80" t="str">
+      <c r="P67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q67" s="80" t="str">
+      <c r="Q67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="R67" s="80" t="str">
+      <c r="R67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="S67" s="80" t="str">
+      <c r="S67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="T67" s="80" t="str">
+      <c r="T67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="U67" s="80" t="str">
+      <c r="U67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="V67" s="80" t="str">
+      <c r="V67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="W67" s="80" t="str">
+      <c r="W67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="X67" s="80" t="str">
+      <c r="X67" s="49" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Y67" s="45">
+      <c r="Y67" s="49">
         <f t="shared" si="14"/>
         <v>0.0428351463662851</v>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:25">
       <c r="A68" s="16"/>
-      <c r="B68" s="43" t="s">
+      <c r="B68" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="C68" s="43">
+      <c r="C68" s="38">
         <v>100</v>
       </c>
-      <c r="D68" s="43"/>
+      <c r="D68" s="38"/>
       <c r="E68" s="16"/>
       <c r="F68" s="16"/>
       <c r="G68" s="16"/>
       <c r="H68" s="19">
         <v>5</v>
       </c>
-      <c r="I68" s="47">
-        <f t="shared" ref="I68:Y68" si="15">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
+      <c r="I68" s="50">
+        <f>IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.010470813556203</v>
       </c>
-      <c r="J68" s="47">
-        <f t="shared" si="15"/>
+      <c r="J68" s="50">
+        <f>IFERROR(BINOMDIST($H68-J$62,15-J$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.03490271185401</v>
       </c>
-      <c r="K68" s="47">
-        <f t="shared" si="15"/>
+      <c r="K68" s="50">
+        <f t="shared" ref="I68:Y68" si="15">IFERROR(BINOMDIST($H68-K$62,15-K$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.0997220338686001</v>
       </c>
-      <c r="L68" s="47">
+      <c r="L68" s="50">
         <f t="shared" si="15"/>
         <v>0.230127770466</v>
       </c>
-      <c r="M68" s="47">
+      <c r="M68" s="50">
         <f t="shared" si="15"/>
         <v>0.38354628411</v>
       </c>
-      <c r="N68" s="47">
+      <c r="N68" s="50">
         <f t="shared" si="15"/>
         <v>0.3486784401</v>
       </c>
-      <c r="O68" s="80" t="str">
+      <c r="O68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="P68" s="80" t="str">
+      <c r="P68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="Q68" s="80" t="str">
+      <c r="Q68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="R68" s="80" t="str">
+      <c r="R68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="S68" s="80" t="str">
+      <c r="S68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="T68" s="80" t="str">
+      <c r="T68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="U68" s="80" t="str">
+      <c r="U68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="V68" s="80" t="str">
+      <c r="V68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="W68" s="80" t="str">
+      <c r="W68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="X68" s="80" t="str">
+      <c r="X68" s="49" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="Y68" s="45">
+      <c r="Y68" s="49">
         <f t="shared" si="15"/>
         <v>0.010470813556203</v>
       </c>
@@ -6359,71 +6443,71 @@
       <c r="H69" s="19">
         <v>6</v>
       </c>
-      <c r="I69" s="45">
+      <c r="I69" s="49">
         <f t="shared" ref="I69:Y69" si="16">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.001939039547445</v>
       </c>
-      <c r="J69" s="45">
+      <c r="J69" s="49">
         <f t="shared" si="16"/>
         <v>0.00775615818978</v>
       </c>
-      <c r="K69" s="45">
+      <c r="K69" s="49">
         <f t="shared" si="16"/>
         <v>0.0277005649635</v>
       </c>
-      <c r="L69" s="45">
+      <c r="L69" s="49">
         <f t="shared" si="16"/>
         <v>0.08523250758</v>
       </c>
-      <c r="M69" s="45">
+      <c r="M69" s="49">
         <f t="shared" si="16"/>
         <v>0.21308126895</v>
       </c>
-      <c r="N69" s="45">
+      <c r="N69" s="49">
         <f t="shared" si="16"/>
         <v>0.387420489</v>
       </c>
-      <c r="O69" s="45">
+      <c r="O69" s="49">
         <f t="shared" si="16"/>
         <v>0.387420489</v>
       </c>
-      <c r="P69" s="45" t="str">
+      <c r="P69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Q69" s="45" t="str">
+      <c r="Q69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="R69" s="45" t="str">
+      <c r="R69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="S69" s="45" t="str">
+      <c r="S69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="T69" s="80" t="str">
+      <c r="T69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="U69" s="80" t="str">
+      <c r="U69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="V69" s="80" t="str">
+      <c r="V69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="W69" s="80" t="str">
+      <c r="W69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="X69" s="80" t="str">
+      <c r="X69" s="49" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="Y69" s="45">
+      <c r="Y69" s="49">
         <f t="shared" si="16"/>
         <v>0.001939039547445</v>
       </c>
@@ -6439,71 +6523,71 @@
       <c r="H70" s="19">
         <v>7</v>
       </c>
-      <c r="I70" s="45">
+      <c r="I70" s="49">
         <f t="shared" ref="I70:Y70" si="17">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.000277005649635</v>
       </c>
-      <c r="J70" s="45">
+      <c r="J70" s="49">
         <f t="shared" si="17"/>
         <v>0.00129269303163</v>
       </c>
-      <c r="K70" s="45">
+      <c r="K70" s="49">
         <f t="shared" si="17"/>
         <v>0.0055401129927</v>
       </c>
-      <c r="L70" s="45">
+      <c r="L70" s="49">
         <f t="shared" si="17"/>
         <v>0.021308126895</v>
       </c>
-      <c r="M70" s="45">
+      <c r="M70" s="49">
         <f t="shared" si="17"/>
         <v>0.07102708965</v>
       </c>
-      <c r="N70" s="45">
+      <c r="N70" s="49">
         <f t="shared" si="17"/>
         <v>0.1937102445</v>
       </c>
-      <c r="O70" s="45">
+      <c r="O70" s="49">
         <f t="shared" si="17"/>
         <v>0.387420489</v>
       </c>
-      <c r="P70" s="45">
+      <c r="P70" s="49">
         <f t="shared" si="17"/>
         <v>0.43046721</v>
       </c>
-      <c r="Q70" s="45" t="str">
+      <c r="Q70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="R70" s="45" t="str">
+      <c r="R70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="S70" s="45" t="str">
+      <c r="S70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="T70" s="80" t="str">
+      <c r="T70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="U70" s="80" t="str">
+      <c r="U70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="V70" s="80" t="str">
+      <c r="V70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="W70" s="80" t="str">
+      <c r="W70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="X70" s="80" t="str">
+      <c r="X70" s="49" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="Y70" s="45">
+      <c r="Y70" s="49">
         <f t="shared" si="17"/>
         <v>0.000277005649635</v>
       </c>
@@ -6519,71 +6603,71 @@
       <c r="H71" s="19">
         <v>8</v>
       </c>
-      <c r="I71" s="45">
+      <c r="I71" s="49">
         <f t="shared" ref="I71:Y71" si="18">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J71" s="45">
+      <c r="J71" s="49">
         <f t="shared" si="18"/>
         <v>0.00016415149608</v>
       </c>
-      <c r="K71" s="45">
+      <c r="K71" s="49">
         <f t="shared" si="18"/>
         <v>0.0008207574804</v>
       </c>
-      <c r="L71" s="45">
+      <c r="L71" s="49">
         <f t="shared" si="18"/>
         <v>0.003788111448</v>
       </c>
-      <c r="M71" s="45">
+      <c r="M71" s="49">
         <f t="shared" si="18"/>
         <v>0.0157837977</v>
       </c>
-      <c r="N71" s="45">
+      <c r="N71" s="49">
         <f t="shared" si="18"/>
         <v>0.057395628</v>
       </c>
-      <c r="O71" s="45">
+      <c r="O71" s="49">
         <f t="shared" si="18"/>
         <v>0.172186884</v>
       </c>
-      <c r="P71" s="45">
+      <c r="P71" s="49">
         <f t="shared" si="18"/>
         <v>0.38263752</v>
       </c>
-      <c r="Q71" s="45">
+      <c r="Q71" s="49">
         <f t="shared" si="18"/>
         <v>0.4782969</v>
       </c>
-      <c r="R71" s="45" t="str">
+      <c r="R71" s="49" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="S71" s="45" t="str">
+      <c r="S71" s="49" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="T71" s="80" t="str">
+      <c r="T71" s="49" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="U71" s="80" t="str">
+      <c r="U71" s="49" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="V71" s="80" t="str">
+      <c r="V71" s="49" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="W71" s="80" t="str">
+      <c r="W71" s="49" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="X71" s="80" t="str">
+      <c r="X71" s="49" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Y71" s="45">
+      <c r="Y71" s="49">
         <f t="shared" si="18"/>
         <v>3.0778405515e-5</v>
       </c>
@@ -6593,77 +6677,78 @@
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
+      <c r="E72" s="51" t="s">
+        <v>132</v>
+      </c>
       <c r="G72" s="16"/>
       <c r="H72" s="19">
         <v>9</v>
       </c>
-      <c r="I72" s="45">
+      <c r="I72" s="49">
         <f t="shared" ref="I72:Y72" si="19">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J72" s="45">
+      <c r="J72" s="49">
         <f t="shared" si="19"/>
         <v>1.595917323e-5</v>
       </c>
-      <c r="K72" s="45">
+      <c r="K72" s="49">
         <f t="shared" si="19"/>
         <v>9.11952756e-5</v>
       </c>
-      <c r="L72" s="45">
+      <c r="L72" s="49">
         <f t="shared" si="19"/>
         <v>0.000491051484000001</v>
       </c>
-      <c r="M72" s="45">
+      <c r="M72" s="49">
         <f t="shared" si="19"/>
         <v>0.00245525742</v>
       </c>
-      <c r="N72" s="45">
+      <c r="N72" s="49">
         <f t="shared" si="19"/>
         <v>0.011160261</v>
       </c>
-      <c r="O72" s="45">
+      <c r="O72" s="49">
         <f t="shared" si="19"/>
         <v>0.044641044</v>
       </c>
-      <c r="P72" s="45">
+      <c r="P72" s="49">
         <f t="shared" si="19"/>
         <v>0.14880348</v>
       </c>
-      <c r="Q72" s="45">
+      <c r="Q72" s="49">
         <f t="shared" si="19"/>
         <v>0.3720087</v>
       </c>
-      <c r="R72" s="45">
+      <c r="R72" s="49">
         <f t="shared" si="19"/>
         <v>0.531441</v>
       </c>
-      <c r="S72" s="45" t="str">
+      <c r="S72" s="49" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="T72" s="80" t="str">
+      <c r="T72" s="49" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="U72" s="80" t="str">
+      <c r="U72" s="49" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="V72" s="80" t="str">
+      <c r="V72" s="49" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="W72" s="80" t="str">
+      <c r="W72" s="49" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="X72" s="80" t="str">
+      <c r="X72" s="49" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Y72" s="45">
+      <c r="Y72" s="49">
         <f t="shared" si="19"/>
         <v>2.659862205e-6</v>
       </c>
@@ -6672,78 +6757,78 @@
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
+      <c r="D73" s="51"/>
       <c r="E73" s="16"/>
       <c r="F73" s="16"/>
       <c r="G73" s="16"/>
       <c r="H73" s="19">
         <v>10</v>
       </c>
-      <c r="I73" s="45">
+      <c r="I73" s="49">
         <f t="shared" ref="I73:Y73" si="20">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J73" s="45">
+      <c r="J73" s="49">
         <f t="shared" si="20"/>
         <v>1.18216098e-6</v>
       </c>
-      <c r="K73" s="45">
+      <c r="K73" s="49">
         <f t="shared" si="20"/>
         <v>7.5996063e-6</v>
       </c>
-      <c r="L73" s="45">
+      <c r="L73" s="49">
         <f t="shared" si="20"/>
         <v>4.6766808e-5</v>
       </c>
-      <c r="M73" s="45">
+      <c r="M73" s="49">
         <f t="shared" si="20"/>
         <v>0.00027280638</v>
       </c>
-      <c r="N73" s="45">
+      <c r="N73" s="49">
         <f t="shared" si="20"/>
         <v>0.0014880348</v>
       </c>
-      <c r="O73" s="45">
+      <c r="O73" s="49">
         <f t="shared" si="20"/>
         <v>0.00744017399999999</v>
       </c>
-      <c r="P73" s="45">
+      <c r="P73" s="49">
         <f t="shared" si="20"/>
         <v>0.03306744</v>
       </c>
-      <c r="Q73" s="45">
+      <c r="Q73" s="49">
         <f t="shared" si="20"/>
         <v>0.1240029</v>
       </c>
-      <c r="R73" s="45">
+      <c r="R73" s="49">
         <f t="shared" si="20"/>
         <v>0.354294</v>
       </c>
-      <c r="S73" s="45">
+      <c r="S73" s="49">
         <f t="shared" si="20"/>
         <v>0.59049</v>
       </c>
-      <c r="T73" s="80" t="str">
+      <c r="T73" s="49" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="U73" s="80" t="str">
+      <c r="U73" s="49" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="V73" s="80" t="str">
+      <c r="V73" s="49" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="W73" s="80" t="str">
+      <c r="W73" s="49" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="X73" s="80" t="str">
+      <c r="X73" s="49" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Y73" s="45">
+      <c r="Y73" s="49">
         <f t="shared" si="20"/>
         <v>1.77324147e-7</v>
       </c>
@@ -6759,71 +6844,71 @@
       <c r="H74" s="19">
         <v>11</v>
       </c>
-      <c r="I74" s="45">
+      <c r="I74" s="49">
         <f t="shared" ref="I74:Y74" si="21">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J74" s="45">
+      <c r="J74" s="49">
         <f t="shared" si="21"/>
         <v>6.56756100000002e-8</v>
       </c>
-      <c r="K74" s="45">
+      <c r="K74" s="49">
         <f t="shared" si="21"/>
         <v>4.69111499999999e-7</v>
       </c>
-      <c r="L74" s="45">
+      <c r="L74" s="49">
         <f t="shared" si="21"/>
         <v>3.247695e-6</v>
       </c>
-      <c r="M74" s="45">
+      <c r="M74" s="49">
         <f t="shared" si="21"/>
         <v>2.16512999999999e-5</v>
       </c>
-      <c r="N74" s="45">
+      <c r="N74" s="49">
         <f t="shared" si="21"/>
         <v>0.000137781</v>
       </c>
-      <c r="O74" s="45">
+      <c r="O74" s="49">
         <f t="shared" si="21"/>
         <v>0.000826686</v>
       </c>
-      <c r="P74" s="45">
+      <c r="P74" s="49">
         <f t="shared" si="21"/>
         <v>0.0045927</v>
       </c>
-      <c r="Q74" s="45">
+      <c r="Q74" s="49">
         <f t="shared" si="21"/>
         <v>0.0229635</v>
       </c>
-      <c r="R74" s="45">
+      <c r="R74" s="49">
         <f t="shared" si="21"/>
         <v>0.0984150000000001</v>
       </c>
-      <c r="S74" s="45">
+      <c r="S74" s="49">
         <f t="shared" si="21"/>
         <v>0.32805</v>
       </c>
-      <c r="T74" s="45">
+      <c r="T74" s="49">
         <f t="shared" si="21"/>
         <v>0.6561</v>
       </c>
-      <c r="U74" s="45" t="str">
+      <c r="U74" s="49" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="V74" s="45" t="str">
+      <c r="V74" s="49" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="W74" s="45" t="str">
+      <c r="W74" s="49" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="X74" s="45" t="str">
+      <c r="X74" s="49" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="Y74" s="45">
+      <c r="Y74" s="49">
         <f t="shared" si="21"/>
         <v>8.95576499999999e-9</v>
       </c>
@@ -6839,71 +6924,71 @@
       <c r="H75" s="19">
         <v>12</v>
       </c>
-      <c r="I75" s="45">
+      <c r="I75" s="49">
         <f t="shared" ref="I75:Y75" si="22">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J75" s="45">
+      <c r="J75" s="49">
         <f t="shared" si="22"/>
         <v>2.65356e-9</v>
       </c>
-      <c r="K75" s="45">
+      <c r="K75" s="49">
         <f t="shared" si="22"/>
         <v>2.08494e-8</v>
       </c>
-      <c r="L75" s="45">
+      <c r="L75" s="49">
         <f t="shared" si="22"/>
         <v>1.6038e-7</v>
       </c>
-      <c r="M75" s="45">
+      <c r="M75" s="49">
         <f t="shared" si="22"/>
         <v>1.20285e-6</v>
       </c>
-      <c r="N75" s="45">
+      <c r="N75" s="49">
         <f t="shared" si="22"/>
         <v>8.74800000000001e-6</v>
       </c>
-      <c r="O75" s="45">
+      <c r="O75" s="49">
         <f t="shared" si="22"/>
         <v>6.1236e-5</v>
       </c>
-      <c r="P75" s="45">
+      <c r="P75" s="49">
         <f t="shared" si="22"/>
         <v>0.00040824</v>
       </c>
-      <c r="Q75" s="45">
+      <c r="Q75" s="49">
         <f t="shared" si="22"/>
         <v>0.0025515</v>
       </c>
-      <c r="R75" s="45">
+      <c r="R75" s="49">
         <f t="shared" si="22"/>
         <v>0.01458</v>
       </c>
-      <c r="S75" s="45">
+      <c r="S75" s="49">
         <f t="shared" si="22"/>
         <v>0.0729</v>
       </c>
-      <c r="T75" s="45">
+      <c r="T75" s="49">
         <f t="shared" si="22"/>
         <v>0.2916</v>
       </c>
-      <c r="U75" s="45">
+      <c r="U75" s="49">
         <f t="shared" si="22"/>
         <v>0.729</v>
       </c>
-      <c r="V75" s="45" t="str">
+      <c r="V75" s="49" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="W75" s="45" t="str">
+      <c r="W75" s="49" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="X75" s="45" t="str">
+      <c r="X75" s="49" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Y75" s="45">
+      <c r="Y75" s="49">
         <f t="shared" si="22"/>
         <v>3.31695000000002e-10</v>
       </c>
@@ -6919,71 +7004,71 @@
       <c r="H76" s="19">
         <v>13</v>
       </c>
-      <c r="I76" s="45">
+      <c r="I76" s="49">
         <f t="shared" ref="I76:Y76" si="23">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J76" s="45">
+      <c r="J76" s="49">
         <f t="shared" si="23"/>
         <v>7.37100000000002e-11</v>
       </c>
-      <c r="K76" s="45">
+      <c r="K76" s="49">
         <f t="shared" si="23"/>
         <v>6.318e-10</v>
       </c>
-      <c r="L76" s="45">
+      <c r="L76" s="49">
         <f t="shared" si="23"/>
         <v>5.34599999999998e-9</v>
       </c>
-      <c r="M76" s="45">
+      <c r="M76" s="49">
         <f t="shared" si="23"/>
         <v>4.455e-8</v>
       </c>
-      <c r="N76" s="45">
+      <c r="N76" s="49">
         <f t="shared" si="23"/>
         <v>3.64500000000001e-7</v>
       </c>
-      <c r="O76" s="45">
+      <c r="O76" s="49">
         <f t="shared" si="23"/>
         <v>2.916e-6</v>
       </c>
-      <c r="P76" s="45">
+      <c r="P76" s="49">
         <f t="shared" si="23"/>
         <v>2.268e-5</v>
       </c>
-      <c r="Q76" s="45">
+      <c r="Q76" s="49">
         <f t="shared" si="23"/>
         <v>0.0001701</v>
       </c>
-      <c r="R76" s="45">
+      <c r="R76" s="49">
         <f t="shared" si="23"/>
         <v>0.001215</v>
       </c>
-      <c r="S76" s="45">
+      <c r="S76" s="49">
         <f t="shared" si="23"/>
         <v>0.0081</v>
       </c>
-      <c r="T76" s="45">
+      <c r="T76" s="49">
         <f t="shared" si="23"/>
         <v>0.0486</v>
       </c>
-      <c r="U76" s="45">
+      <c r="U76" s="49">
         <f t="shared" si="23"/>
         <v>0.243</v>
       </c>
-      <c r="V76" s="45">
+      <c r="V76" s="49">
         <f t="shared" si="23"/>
         <v>0.81</v>
       </c>
-      <c r="W76" s="45" t="str">
+      <c r="W76" s="49" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="X76" s="45" t="str">
+      <c r="X76" s="49" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Y76" s="45">
+      <c r="Y76" s="49">
         <f t="shared" si="23"/>
         <v>8.50500000000002e-12</v>
       </c>
@@ -6999,71 +7084,71 @@
       <c r="H77" s="19">
         <v>14</v>
       </c>
-      <c r="I77" s="45">
+      <c r="I77" s="49">
         <f t="shared" ref="I77:Y77" si="24">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.35e-13</v>
       </c>
-      <c r="J77" s="45">
+      <c r="J77" s="49">
         <f t="shared" si="24"/>
         <v>1.26000000000001e-12</v>
       </c>
-      <c r="K77" s="45">
+      <c r="K77" s="49">
         <f t="shared" si="24"/>
         <v>1.17e-11</v>
       </c>
-      <c r="L77" s="45">
+      <c r="L77" s="49">
         <f t="shared" si="24"/>
         <v>1.08e-10</v>
       </c>
-      <c r="M77" s="45">
+      <c r="M77" s="49">
         <f t="shared" si="24"/>
         <v>9.89999999999998e-10</v>
       </c>
-      <c r="N77" s="45">
+      <c r="N77" s="49">
         <f t="shared" si="24"/>
         <v>9e-9</v>
       </c>
-      <c r="O77" s="45">
+      <c r="O77" s="49">
         <f t="shared" si="24"/>
         <v>8.10000000000002e-8</v>
       </c>
-      <c r="P77" s="45">
+      <c r="P77" s="49">
         <f t="shared" si="24"/>
         <v>7.19999999999999e-7</v>
       </c>
-      <c r="Q77" s="45">
+      <c r="Q77" s="49">
         <f t="shared" si="24"/>
         <v>6.30000000000001e-6</v>
       </c>
-      <c r="R77" s="45">
+      <c r="R77" s="49">
         <f t="shared" si="24"/>
         <v>5.39999999999999e-5</v>
       </c>
-      <c r="S77" s="45">
+      <c r="S77" s="49">
         <f t="shared" si="24"/>
         <v>0.000450000000000001</v>
       </c>
-      <c r="T77" s="45">
+      <c r="T77" s="49">
         <f t="shared" si="24"/>
         <v>0.0036</v>
       </c>
-      <c r="U77" s="45">
+      <c r="U77" s="49">
         <f t="shared" si="24"/>
         <v>0.027</v>
       </c>
-      <c r="V77" s="45">
+      <c r="V77" s="49">
         <f t="shared" si="24"/>
         <v>0.18</v>
       </c>
-      <c r="W77" s="45">
+      <c r="W77" s="49">
         <f t="shared" si="24"/>
         <v>0.9</v>
       </c>
-      <c r="X77" s="45" t="str">
+      <c r="X77" s="49" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="Y77" s="45">
+      <c r="Y77" s="49">
         <f t="shared" si="24"/>
         <v>1.35e-13</v>
       </c>
@@ -7079,71 +7164,71 @@
       <c r="H78" s="19">
         <v>15</v>
       </c>
-      <c r="I78" s="45">
+      <c r="I78" s="49">
         <f t="shared" ref="I78:Y78" si="25">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1e-15</v>
       </c>
-      <c r="J78" s="45">
+      <c r="J78" s="49">
         <f t="shared" si="25"/>
         <v>1.00000000000001e-14</v>
       </c>
-      <c r="K78" s="45">
+      <c r="K78" s="49">
         <f t="shared" si="25"/>
         <v>1e-13</v>
       </c>
-      <c r="L78" s="45">
+      <c r="L78" s="49">
         <f t="shared" si="25"/>
         <v>1e-12</v>
       </c>
-      <c r="M78" s="45">
+      <c r="M78" s="49">
         <f t="shared" si="25"/>
         <v>1e-11</v>
       </c>
-      <c r="N78" s="45">
+      <c r="N78" s="49">
         <f t="shared" si="25"/>
         <v>1e-10</v>
       </c>
-      <c r="O78" s="45">
+      <c r="O78" s="49">
         <f t="shared" si="25"/>
         <v>1e-9</v>
       </c>
-      <c r="P78" s="45">
+      <c r="P78" s="49">
         <f t="shared" si="25"/>
         <v>1e-8</v>
       </c>
-      <c r="Q78" s="45">
+      <c r="Q78" s="49">
         <f t="shared" si="25"/>
         <v>1e-7</v>
       </c>
-      <c r="R78" s="45">
+      <c r="R78" s="49">
         <f t="shared" si="25"/>
         <v>1e-6</v>
       </c>
-      <c r="S78" s="45">
+      <c r="S78" s="49">
         <f t="shared" si="25"/>
         <v>1e-5</v>
       </c>
-      <c r="T78" s="45">
+      <c r="T78" s="49">
         <f t="shared" si="25"/>
         <v>0.0001</v>
       </c>
-      <c r="U78" s="45">
+      <c r="U78" s="49">
         <f t="shared" si="25"/>
         <v>0.001</v>
       </c>
-      <c r="V78" s="45">
+      <c r="V78" s="49">
         <f t="shared" si="25"/>
         <v>0.01</v>
       </c>
-      <c r="W78" s="45">
+      <c r="W78" s="49">
         <f t="shared" si="25"/>
         <v>0.1</v>
       </c>
-      <c r="X78" s="45">
+      <c r="X78" s="49">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
-      <c r="Y78" s="45">
+      <c r="Y78" s="49">
         <f t="shared" si="25"/>
         <v>1e-15</v>
       </c>
@@ -7157,7 +7242,10 @@
       <c r="F79" s="16"/>
       <c r="G79" s="16"/>
       <c r="H79" s="16"/>
-      <c r="I79" s="16"/>
+      <c r="I79" s="16">
+        <f>SUM(I63:I78)</f>
+        <v>1</v>
+      </c>
       <c r="J79" s="16"/>
       <c r="K79" s="16"/>
       <c r="L79" s="16"/>
@@ -7182,16 +7270,16 @@
       <c r="D80" s="16"/>
       <c r="E80" s="16"/>
       <c r="F80" s="16"/>
-      <c r="G80" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
-      <c r="J80" s="48"/>
-      <c r="K80" s="48"/>
-      <c r="L80" s="48"/>
-      <c r="M80" s="48"/>
-      <c r="N80" s="48"/>
+      <c r="G80" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="H80" s="52"/>
+      <c r="I80" s="52"/>
+      <c r="J80" s="52"/>
+      <c r="K80" s="52"/>
+      <c r="L80" s="52"/>
+      <c r="M80" s="52"/>
+      <c r="N80" s="52"/>
       <c r="O80" s="16"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="16"/>
@@ -7218,11 +7306,13 @@
       <c r="K81" s="16"/>
       <c r="L81" s="16"/>
       <c r="M81" s="16"/>
-      <c r="N81" s="16"/>
-      <c r="O81" s="16"/>
-      <c r="P81" s="16"/>
-      <c r="Q81" s="16"/>
-      <c r="R81" s="16"/>
+      <c r="N81" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="O81" s="53"/>
+      <c r="P81" s="54"/>
+      <c r="Q81" s="54"/>
+      <c r="R81" s="54"/>
       <c r="S81" s="16"/>
       <c r="T81" s="16"/>
       <c r="U81" s="16"/>
@@ -7257,11 +7347,13 @@
       <c r="M82" s="19">
         <v>5</v>
       </c>
-      <c r="N82" s="16"/>
-      <c r="O82" s="16"/>
-      <c r="P82" s="16"/>
-      <c r="Q82" s="16"/>
-      <c r="R82" s="16"/>
+      <c r="N82" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="O82" s="53"/>
+      <c r="P82" s="53"/>
+      <c r="Q82" s="54"/>
+      <c r="R82" s="54"/>
       <c r="S82" s="16"/>
       <c r="T82" s="16"/>
       <c r="U82" s="16"/>
@@ -7281,31 +7373,33 @@
       <c r="H83" s="19">
         <v>0</v>
       </c>
-      <c r="I83" s="49">
+      <c r="I83" s="55">
         <f t="shared" ref="I83:I98" si="26">I63</f>
         <v>0.205891132094649</v>
       </c>
-      <c r="J83" s="45">
-        <f ca="1" t="shared" ref="J83:J98" si="27">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,J$82-2,$H83+1,1))</f>
+      <c r="J83" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I83),1,1,ROWS(I$83:I83)),I$83:I83)</f>
         <v>0.0423911582752162</v>
       </c>
-      <c r="K83" s="45">
-        <f ca="1" t="shared" ref="K83:K98" si="28">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,K$82-2,$H83+1,1))</f>
+      <c r="K83" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J83),1,1,ROWS(J$83:J83)),J$83:J83)</f>
         <v>0.00872796356808771</v>
       </c>
-      <c r="L83" s="45">
-        <f ca="1" t="shared" ref="L83:L98" si="29">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,L$82-2,$H83+1,1))</f>
+      <c r="L83" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K83),1,1,ROWS(K$83:K83)),K$83:K83)</f>
         <v>0.00179701029991443</v>
       </c>
-      <c r="M83" s="45">
-        <f ca="1" t="shared" ref="M83:M98" si="30">MMULT(OFFSET($H$62,$H83+1,1,1,$H83+1),OFFSET($I$83,0,M$82-2,$H83+1,1))</f>
+      <c r="M83" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L83),1,1,ROWS(L$83:L83)),L$83:L83)</f>
         <v>0.000369988485035127</v>
       </c>
-      <c r="N83" s="16"/>
-      <c r="O83" s="16"/>
-      <c r="P83" s="16"/>
-      <c r="Q83" s="16"/>
-      <c r="R83" s="16"/>
+      <c r="N83" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="O83" s="53"/>
+      <c r="P83" s="53"/>
+      <c r="Q83" s="53"/>
+      <c r="R83" s="54"/>
       <c r="S83" s="16"/>
       <c r="T83" s="16"/>
       <c r="U83" s="16"/>
@@ -7325,31 +7419,33 @@
       <c r="H84" s="19">
         <v>1</v>
       </c>
-      <c r="I84" s="49">
+      <c r="I84" s="55">
         <f t="shared" si="26"/>
         <v>0.343151886824415</v>
       </c>
-      <c r="J84" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J84" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I84),1,1,ROWS(I$83:I84)),I$83:I84)</f>
         <v>0.149154075412798</v>
       </c>
-      <c r="K84" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K84" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J84),1,1,ROWS(J$83:J84)),J$83:J84)</f>
         <v>0.0486682742171146</v>
       </c>
-      <c r="L84" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L84" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K84),1,1,ROWS(K$83:K84)),K$83:K84)</f>
         <v>0.0141287572505847</v>
       </c>
-      <c r="M84" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M84" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L84),1,1,ROWS(L$83:L84)),L$83:L84)</f>
         <v>0.00384885394774005</v>
       </c>
-      <c r="N84" s="16"/>
-      <c r="O84" s="16"/>
-      <c r="P84" s="16"/>
-      <c r="Q84" s="16"/>
-      <c r="R84" s="16"/>
+      <c r="N84" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="O84" s="53"/>
+      <c r="P84" s="53"/>
+      <c r="Q84" s="53"/>
+      <c r="R84" s="54"/>
       <c r="S84" s="16"/>
       <c r="T84" s="16"/>
       <c r="U84" s="16"/>
@@ -7369,31 +7465,33 @@
       <c r="H85" s="19">
         <v>2</v>
       </c>
-      <c r="I85" s="49">
+      <c r="I85" s="55">
         <f t="shared" si="26"/>
         <v>0.266895911974545</v>
       </c>
-      <c r="J85" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J85" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I85),1,1,ROWS(I$83:I85)),I$83:I85)</f>
         <v>0.244907309011137</v>
       </c>
-      <c r="K85" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K85" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J85),1,1,ROWS(J$83:J85)),J$83:J85)</f>
         <v>0.126644329478555</v>
       </c>
-      <c r="L85" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L85" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K85),1,1,ROWS(K$83:K85)),K$83:K85)</f>
         <v>0.0518398983833752</v>
       </c>
-      <c r="M85" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M85" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L85),1,1,ROWS(L$83:L85)),L$83:L85)</f>
         <v>0.0186844980625806</v>
       </c>
-      <c r="N85" s="16"/>
-      <c r="O85" s="16"/>
-      <c r="P85" s="16"/>
-      <c r="Q85" s="16"/>
-      <c r="R85" s="16"/>
+      <c r="N85" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="O85" s="53"/>
+      <c r="P85" s="53"/>
+      <c r="Q85" s="53"/>
+      <c r="R85" s="53"/>
       <c r="S85" s="16"/>
       <c r="T85" s="16"/>
       <c r="U85" s="16"/>
@@ -7413,31 +7511,33 @@
       <c r="H86" s="19">
         <v>3</v>
       </c>
-      <c r="I86" s="49">
+      <c r="I86" s="55">
         <f t="shared" si="26"/>
         <v>0.128505439098855</v>
       </c>
-      <c r="J86" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J86" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I86),1,1,ROWS(I$83:I86)),I$83:I86)</f>
         <v>0.248938705044242</v>
       </c>
-      <c r="K86" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K86" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J86),1,1,ROWS(J$83:J86)),J$83:J86)</f>
         <v>0.204009132488774</v>
       </c>
-      <c r="L86" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L86" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K86),1,1,ROWS(K$83:K86)),K$83:K86)</f>
         <v>0.117746600468707</v>
       </c>
-      <c r="M86" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M86" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L86),1,1,ROWS(L$83:L86)),L$83:L86)</f>
         <v>0.0561507417121914</v>
       </c>
-      <c r="N86" s="16"/>
-      <c r="O86" s="16"/>
-      <c r="P86" s="16"/>
-      <c r="Q86" s="16"/>
-      <c r="R86" s="16"/>
+      <c r="N86" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="O86" s="53"/>
+      <c r="P86" s="53"/>
+      <c r="Q86" s="53"/>
+      <c r="R86" s="53"/>
       <c r="S86" s="16"/>
       <c r="T86" s="16"/>
       <c r="U86" s="16"/>
@@ -7457,31 +7557,33 @@
       <c r="H87" s="19">
         <v>4</v>
       </c>
-      <c r="I87" s="49">
+      <c r="I87" s="55">
         <f t="shared" si="26"/>
         <v>0.0428351463662851</v>
       </c>
-      <c r="J87" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J87" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I87),1,1,ROWS(I$83:I87)),I$83:I87)</f>
         <v>0.175179088734837</v>
       </c>
-      <c r="K87" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K87" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J87),1,1,ROWS(J$83:J87)),J$83:J87)</f>
         <v>0.227516357631513</v>
       </c>
-      <c r="L87" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L87" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K87),1,1,ROWS(K$83:K87)),K$83:K87)</f>
         <v>0.185153433475941</v>
       </c>
-      <c r="M87" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M87" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L87),1,1,ROWS(L$83:L87)),L$83:L87)</f>
         <v>0.116823097284761</v>
       </c>
-      <c r="N87" s="16"/>
-      <c r="O87" s="16"/>
-      <c r="P87" s="16"/>
-      <c r="Q87" s="16"/>
-      <c r="R87" s="16"/>
+      <c r="N87" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="O87" s="53"/>
+      <c r="P87" s="53"/>
+      <c r="Q87" s="53"/>
+      <c r="R87" s="53"/>
       <c r="S87" s="16"/>
       <c r="T87" s="16"/>
       <c r="U87" s="16"/>
@@ -7501,31 +7603,33 @@
       <c r="H88" s="19">
         <v>5</v>
       </c>
-      <c r="I88" s="49">
+      <c r="I88" s="55">
         <f t="shared" si="26"/>
         <v>0.010470813556203</v>
       </c>
-      <c r="J88" s="50">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J88" s="56">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I88),1,1,ROWS(I$83:I88)),I$83:I88)</f>
         <v>0.0904010606063728</v>
       </c>
-      <c r="K88" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K88" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J88),1,1,ROWS(J$83:J88)),J$83:J88)</f>
         <v>0.186070305102755</v>
       </c>
-      <c r="L88" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L88" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K88),1,1,ROWS(K$83:K88)),K$83:K88)</f>
         <v>0.213509197834518</v>
       </c>
-      <c r="M88" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M88" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L88),1,1,ROWS(L$83:L88)),L$83:L88)</f>
         <v>0.178239256298975</v>
       </c>
-      <c r="N88" s="16"/>
-      <c r="O88" s="16"/>
-      <c r="P88" s="16"/>
-      <c r="Q88" s="16"/>
-      <c r="R88" s="16"/>
+      <c r="N88" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="O88" s="53"/>
+      <c r="P88" s="53"/>
+      <c r="Q88" s="53"/>
+      <c r="R88" s="53"/>
       <c r="S88" s="16"/>
       <c r="T88" s="16"/>
       <c r="U88" s="16"/>
@@ -7545,31 +7649,33 @@
       <c r="H89" s="19">
         <v>6</v>
       </c>
-      <c r="I89" s="45">
+      <c r="I89" s="49">
         <f t="shared" si="26"/>
         <v>0.001939039547445</v>
       </c>
-      <c r="J89" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J89" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I89),1,1,ROWS(I$83:I89)),I$83:I89)</f>
         <v>0.0353419784263597</v>
       </c>
-      <c r="K89" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K89" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J89),1,1,ROWS(J$83:J89)),J$83:J89)</f>
         <v>0.115283613815378</v>
       </c>
-      <c r="L89" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L89" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K89),1,1,ROWS(K$83:K89)),K$83:K89)</f>
         <v>0.186520888927731</v>
       </c>
-      <c r="M89" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M89" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L89),1,1,ROWS(L$83:L89)),L$83:L89)</f>
         <v>0.206017482223783</v>
       </c>
-      <c r="N89" s="16"/>
-      <c r="O89" s="16"/>
-      <c r="P89" s="16"/>
-      <c r="Q89" s="16"/>
-      <c r="R89" s="16"/>
+      <c r="N89" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="O89" s="53"/>
+      <c r="P89" s="53"/>
+      <c r="Q89" s="53"/>
+      <c r="R89" s="53"/>
       <c r="S89" s="16"/>
       <c r="T89" s="16"/>
       <c r="U89" s="16"/>
@@ -7589,31 +7695,33 @@
       <c r="H90" s="19">
         <v>7</v>
       </c>
-      <c r="I90" s="45">
+      <c r="I90" s="49">
         <f t="shared" si="26"/>
         <v>0.000277005649635</v>
       </c>
-      <c r="J90" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J90" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I90),1,1,ROWS(I$83:I90)),I$83:I90)</f>
         <v>0.0106586919063625</v>
       </c>
-      <c r="K90" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K90" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J90),1,1,ROWS(J$83:J90)),J$83:J90)</f>
         <v>0.0551002810299252</v>
       </c>
-      <c r="L90" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L90" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K90),1,1,ROWS(K$83:K90)),K$83:K90)</f>
         <v>0.125699654521354</v>
       </c>
-      <c r="M90" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M90" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L90),1,1,ROWS(L$83:L90)),L$83:L90)</f>
         <v>0.183696342337757</v>
       </c>
-      <c r="N90" s="16"/>
-      <c r="O90" s="16"/>
-      <c r="P90" s="16"/>
-      <c r="Q90" s="16"/>
-      <c r="R90" s="16"/>
+      <c r="N90" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="O90" s="53"/>
+      <c r="P90" s="53"/>
+      <c r="Q90" s="53"/>
+      <c r="R90" s="53"/>
       <c r="S90" s="16"/>
       <c r="T90" s="16"/>
       <c r="U90" s="16"/>
@@ -7633,31 +7741,33 @@
       <c r="H91" s="19">
         <v>8</v>
       </c>
-      <c r="I91" s="45">
+      <c r="I91" s="49">
         <f t="shared" si="26"/>
         <v>3.0778405515e-5</v>
       </c>
-      <c r="J91" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J91" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I91),1,1,ROWS(I$83:I91)),I$83:I91)</f>
         <v>0.00250018699038132</v>
       </c>
-      <c r="K91" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K91" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J91),1,1,ROWS(J$83:J91)),J$83:J91)</f>
         <v>0.0204830948684633</v>
       </c>
-      <c r="L91" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L91" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K91),1,1,ROWS(K$83:K91)),K$83:K91)</f>
         <v>0.0658864672914092</v>
       </c>
-      <c r="M91" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M91" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L91),1,1,ROWS(L$83:L91)),L$83:L91)</f>
         <v>0.127395026419981</v>
       </c>
-      <c r="N91" s="16"/>
-      <c r="O91" s="16"/>
-      <c r="P91" s="16"/>
-      <c r="Q91" s="16"/>
-      <c r="R91" s="16"/>
+      <c r="N91" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="O91" s="53"/>
+      <c r="P91" s="53"/>
+      <c r="Q91" s="53"/>
+      <c r="R91" s="53"/>
       <c r="S91" s="16"/>
       <c r="T91" s="16"/>
       <c r="U91" s="16"/>
@@ -7677,24 +7787,24 @@
       <c r="H92" s="19">
         <v>9</v>
       </c>
-      <c r="I92" s="45">
+      <c r="I92" s="49">
         <f t="shared" si="26"/>
         <v>2.659862205e-6</v>
       </c>
-      <c r="J92" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J92" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I92),1,1,ROWS(I$83:I92)),I$83:I92)</f>
         <v>0.00045613836724378</v>
       </c>
-      <c r="K92" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K92" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J92),1,1,ROWS(J$83:J92)),J$83:J92)</f>
         <v>0.00592233363290273</v>
       </c>
-      <c r="L92" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L92" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K92),1,1,ROWS(K$83:K92)),K$83:K92)</f>
         <v>0.0268604875121694</v>
       </c>
-      <c r="M92" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M92" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L92),1,1,ROWS(L$83:L92)),L$83:L92)</f>
         <v>0.0687163318006563</v>
       </c>
       <c r="N92" s="16"/>
@@ -7721,24 +7831,24 @@
       <c r="H93" s="19">
         <v>10</v>
       </c>
-      <c r="I93" s="45">
+      <c r="I93" s="49">
         <f t="shared" si="26"/>
         <v>1.77324147e-7</v>
       </c>
-      <c r="J93" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J93" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I93),1,1,ROWS(I$83:I93)),I$83:I93)</f>
         <v>6.41972516861615e-5</v>
       </c>
-      <c r="K93" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K93" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J93),1,1,ROWS(J$83:J93)),J$83:J93)</f>
         <v>0.00132094848931411</v>
       </c>
-      <c r="L93" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L93" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K93),1,1,ROWS(K$83:K93)),K$83:K93)</f>
         <v>0.0084474820808734</v>
       </c>
-      <c r="M93" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M93" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L93),1,1,ROWS(L$83:L93)),L$83:L93)</f>
         <v>0.0285932276946469</v>
       </c>
       <c r="N93" s="16"/>
@@ -7765,24 +7875,24 @@
       <c r="H94" s="19">
         <v>11</v>
       </c>
-      <c r="I94" s="45">
+      <c r="I94" s="49">
         <f t="shared" si="26"/>
         <v>8.95576499999999e-9</v>
       </c>
-      <c r="J94" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J94" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I94),1,1,ROWS(I$83:I94)),I$83:I94)</f>
         <v>6.84482481502283e-6</v>
       </c>
-      <c r="K94" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K94" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J94),1,1,ROWS(J$83:J94)),J$83:J94)</f>
         <v>0.000223205537226664</v>
       </c>
-      <c r="L94" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L94" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K94),1,1,ROWS(K$83:K94)),K$83:K94)</f>
         <v>0.00201264295050115</v>
       </c>
-      <c r="M94" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M94" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L94),1,1,ROWS(L$83:L94)),L$83:L94)</f>
         <v>0.00901347930858259</v>
       </c>
       <c r="N94" s="16"/>
@@ -7809,24 +7919,24 @@
       <c r="H95" s="19">
         <v>12</v>
       </c>
-      <c r="I95" s="45">
+      <c r="I95" s="49">
         <f t="shared" si="26"/>
         <v>3.31695000000002e-10</v>
       </c>
-      <c r="J95" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J95" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I95),1,1,ROWS(I$83:I95)),I$83:I95)</f>
         <v>5.35192063726065e-7</v>
       </c>
-      <c r="K95" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K95" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J95),1,1,ROWS(J$83:J95)),J$83:J95)</f>
         <v>2.76582993088367e-5</v>
       </c>
-      <c r="L95" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L95" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K95),1,1,ROWS(K$83:K95)),K$83:K95)</f>
         <v>0.000351647569312272</v>
       </c>
-      <c r="M95" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M95" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L95),1,1,ROWS(L$83:L95)),L$83:L95)</f>
         <v>0.00208364234881633</v>
       </c>
       <c r="N95" s="16"/>
@@ -7853,24 +7963,24 @@
       <c r="H96" s="19">
         <v>13</v>
       </c>
-      <c r="I96" s="45">
+      <c r="I96" s="49">
         <f t="shared" si="26"/>
         <v>8.50500000000002e-12</v>
       </c>
-      <c r="J96" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J96" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I96),1,1,ROWS(I$83:I96)),I$83:I96)</f>
         <v>2.89705105720662e-8</v>
       </c>
-      <c r="K96" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K96" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J96),1,1,ROWS(J$83:J96)),J$83:J96)</f>
         <v>2.3727126029423e-6</v>
       </c>
-      <c r="L96" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L96" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K96),1,1,ROWS(K$83:K96)),K$83:K96)</f>
         <v>4.25351197940594e-5</v>
       </c>
-      <c r="M96" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M96" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L96),1,1,ROWS(L$83:L96)),L$83:L96)</f>
         <v>0.000333467138086273</v>
       </c>
       <c r="N96" s="16"/>
@@ -7897,24 +8007,24 @@
       <c r="H97" s="19">
         <v>14</v>
       </c>
-      <c r="I97" s="45">
+      <c r="I97" s="49">
         <f t="shared" si="26"/>
         <v>1.35e-13</v>
       </c>
-      <c r="J97" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J97" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I97),1,1,ROWS(I$83:I97)),I$83:I97)</f>
         <v>9.70793123226205e-10</v>
       </c>
-      <c r="K97" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K97" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J97),1,1,ROWS(J$83:J97)),J$83:J97)</f>
         <v>1.26005313618923e-7</v>
       </c>
-      <c r="L97" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L97" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K97),1,1,ROWS(K$83:K97)),K$83:K97)</f>
         <v>3.18501702640648e-6</v>
       </c>
-      <c r="M97" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M97" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L97),1,1,ROWS(L$83:L97)),L$83:L97)</f>
         <v>3.30374840550607e-5</v>
       </c>
       <c r="N97" s="16"/>
@@ -7941,24 +8051,24 @@
       <c r="H98" s="19">
         <v>15</v>
       </c>
-      <c r="I98" s="45">
+      <c r="I98" s="49">
         <f t="shared" si="26"/>
         <v>1e-15</v>
       </c>
-      <c r="J98" s="45">
-        <f ca="1" t="shared" si="27"/>
+      <c r="J98" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(I$83:I98),1,1,ROWS(I$83:I98)),I$83:I98)</f>
         <v>1.51811270298748e-11</v>
       </c>
-      <c r="K98" s="45">
-        <f ca="1" t="shared" si="28"/>
+      <c r="K98" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(J$83:J98),1,1,ROWS(J$83:J98)),J$83:J98)</f>
         <v>3.12276543125086e-9</v>
       </c>
-      <c r="L98" s="45">
-        <f ca="1" t="shared" si="29"/>
+      <c r="L98" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(K$83:K98),1,1,ROWS(K$83:K98)),K$83:K98)</f>
         <v>1.11296789654137e-7</v>
       </c>
-      <c r="M98" s="45">
-        <f ca="1" t="shared" si="30"/>
+      <c r="M98" s="49">
+        <f ca="1">MMULT(OFFSET($H$62,ROWS(L$83:L98),1,1,ROWS(L$83:L98)),L$83:L98)</f>
         <v>1.52745235260974e-6</v>
       </c>
       <c r="N98" s="16"/>
@@ -7985,23 +8095,23 @@
       <c r="H99" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="I99" s="45">
+      <c r="I99" s="49">
         <f>SUM(I83:I98)</f>
         <v>1</v>
       </c>
-      <c r="J99" s="45">
+      <c r="J99" s="49">
         <f ca="1">SUM(J83:J98)</f>
         <v>1</v>
       </c>
-      <c r="K99" s="45">
+      <c r="K99" s="49">
         <f ca="1">SUM(K83:K98)</f>
         <v>1</v>
       </c>
-      <c r="L99" s="45">
+      <c r="L99" s="49">
         <f ca="1">SUM(L83:L98)</f>
         <v>1</v>
       </c>
-      <c r="M99" s="45">
+      <c r="M99" s="49">
         <f ca="1">SUM(M83:M98)</f>
         <v>1</v>
       </c>
@@ -8046,10 +8156,10 @@
       <c r="Y100" s="16"/>
     </row>
     <row r="101" ht="102" customHeight="1" spans="1:25">
-      <c r="A101" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="B101" s="45">
+      <c r="A101" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="B101" s="49">
         <f ca="1">SUM(M88:M98)</f>
         <v>0.804122820507692</v>
       </c>
@@ -8078,7 +8188,7 @@
       <c r="Y101" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A25:C25"/>
@@ -8090,9 +8200,22 @@
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A59:D59"/>
+    <mergeCell ref="G59:Q59"/>
     <mergeCell ref="A60:F60"/>
     <mergeCell ref="G60:N60"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="G80:N80"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="N83:Q83"/>
+    <mergeCell ref="N84:Q84"/>
+    <mergeCell ref="N85:R85"/>
+    <mergeCell ref="N86:R86"/>
+    <mergeCell ref="N87:R87"/>
+    <mergeCell ref="N88:R88"/>
+    <mergeCell ref="N89:R89"/>
+    <mergeCell ref="N90:R90"/>
+    <mergeCell ref="N91:R91"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="G6:G23"/>
   </mergeCells>
@@ -8100,7 +8223,7 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A36:Y101 A1:Y3 A4:F4 H4:Y4 A5:Y5 A6:F6 H6:Y6 A7 C7:Y7 A8:Y22 A23 C23:Y23 A24:Y27 A28:G34 A35:C35 E35:G35 S28:Y35" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A61:H61 M61:Y61 A62:G62 I62:Y62 A63:F65 H63:H64 J63:Y64 H65:Y65 A66:Y67 A68:H68 K68:Y68 A69:Y71 A72:D72 G72:Y72 A73:C73 E73:Y73 A74:Y78 A79:H79 J79:Y79 A80:Y101 H59:Y60 A59:F60 A36:Y58 A1:Y3 A4:F4 H4:Y4 A5:Y5 A6:F6 H6:Y6 A7 C7:Y7 A8:Y22 A23 C23:Y23 A24:Y27 A28:G34 A35:C35 E35:G35 S28:Y35" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8119,56 +8242,56 @@
   <sheetData>
     <row r="1" ht="21" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" ht="36.75" customHeight="1" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
     </row>
     <row r="6" ht="34" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -8180,56 +8303,56 @@
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B13" s="6">
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="B14" s="7">
         <v>0.075</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B15" s="6">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -8239,66 +8362,66 @@
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="8" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B18" s="74">
+        <v>166</v>
+      </c>
+      <c r="B18" s="10">
         <f>BINOMDIST($B$15,$B$13,$B$14,FALSE)</f>
         <v>0.00360966796875</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B19" s="75">
+        <v>168</v>
+      </c>
+      <c r="B19" s="11">
         <f>BINOMDIST($B$13,$B$13,$B$14,FALSE)</f>
         <v>2.373046875e-6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" ht="34" spans="1:3">
       <c r="A20" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="74">
+        <v>170</v>
+      </c>
+      <c r="B20" s="10">
         <f>1-BINOMDIST($B$15-1,$B$13,$B$14,TRUE)</f>
         <v>0.00375837890624997</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B21" s="12">
         <f>$B$13*$B$14</f>
         <v>0.375</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
@@ -8310,56 +8433,56 @@
     </row>
     <row r="24" ht="17" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" ht="17" spans="1:3">
       <c r="A26" s="5" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
     <row r="27" ht="17" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B27" s="6">
         <v>5</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" ht="17" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B28" s="7">
         <v>0.04</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" ht="17" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B29" s="6">
         <v>3</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8369,42 +8492,42 @@
     </row>
     <row r="31" ht="17" spans="1:3">
       <c r="A31" s="8" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" ht="34" spans="1:3">
       <c r="A32" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" s="74">
+        <v>182</v>
+      </c>
+      <c r="B32" s="10">
         <f>1-BINOMDIST($B$29-1,$B$27,$B$28,TRUE)</f>
         <v>0.000602214399999967</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" ht="17" spans="1:3">
       <c r="A33" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B33" s="75">
+        <v>183</v>
+      </c>
+      <c r="B33" s="11">
         <f>1-BINOMDIST(1,$B$27,$B$28,TRUE)</f>
         <v>0.0147579904</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" ht="17" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B34" s="12">
         <f>$B$27*$B$28</f>
@@ -8419,45 +8542,45 @@
     </row>
     <row r="36" ht="17" spans="1:3">
       <c r="A36" s="5" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="2"/>
     </row>
     <row r="38" ht="17" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B38" s="75">
+        <v>188</v>
+      </c>
+      <c r="B38" s="11">
         <f>1-BINOMDIST(2,5,0.05,TRUE)</f>
         <v>0.00115812500000001</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B39" s="74">
+        <v>190</v>
+      </c>
+      <c r="B39" s="10">
         <f>1-BINOMDIST(2,15,0.05,TRUE)</f>
         <v>0.0362002386427291</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" ht="34" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -8469,28 +8592,28 @@
     </row>
     <row r="42" ht="17" spans="1:3">
       <c r="A42" s="4" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
     </row>
     <row r="43" ht="34" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="2"/>
     </row>
     <row r="45" ht="34" spans="1:3">
       <c r="A45" s="3" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -8502,53 +8625,53 @@
     </row>
     <row r="47" ht="17" spans="1:3">
       <c r="A47" s="4" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
     </row>
     <row r="48" ht="17" spans="1:3">
       <c r="A48" s="8" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" ht="17" spans="1:3">
       <c r="A49" s="3" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" ht="17" spans="1:3">
       <c r="A50" s="3" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" ht="17" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -8558,7 +8681,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="14" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
